--- a/statistics_files/nekls_executive_board/2026/2026_next_statistics.xlsx
+++ b/statistics_files/nekls_executive_board/2026/2026_next_statistics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\nekls_executive_board\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Staff\Documents\GitHub\next_statistics\statistics_files\nekls_executive_board\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{26BBC99C-71DC-44EB-A2FD-CF5751F227CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F23601E-C71A-4FCD-ADE9-583A24B8F1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Annual totals" sheetId="1" r:id="rId1"/>
@@ -42,8 +42,17 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">October!$A$2:$D$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">September!$A$2:$D$2</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -243,9 +252,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="mmmm\ d\,\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="mmmm\ d\,\ yyyy"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -866,13 +875,13 @@
     <xf numFmtId="0" fontId="0" fillId="37" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="37" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="37" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="37" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="37" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -920,7 +929,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="98">
+  <dxfs count="97">
     <dxf>
       <font>
         <color theme="9" tint="0.59996337778862885"/>
@@ -1743,16 +1752,6 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color theme="0" tint="-0.14996795556505021"/>
       </font>
       <fill>
@@ -2070,15 +2069,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -2090,10 +2089,10 @@
       </c>
       <c r="D1" s="21">
         <f>MAX(January:December!D1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46053</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -2107,160 +2106,160 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="3">
         <f>SUM(January:December!B3)</f>
-        <v>0</v>
+        <v>5663</v>
       </c>
       <c r="C3" s="3">
         <f>SUM(January:December!C3)</f>
-        <v>0</v>
+        <v>973</v>
       </c>
       <c r="D3" s="3">
         <f>SUM(January:December!D3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2">
         <f>SUM(January:December!B4)</f>
-        <v>0</v>
+        <v>3255</v>
       </c>
       <c r="C4" s="2">
         <f>SUM(January:December!C4)</f>
-        <v>0</v>
+        <v>287</v>
       </c>
       <c r="D4" s="2">
         <f>SUM(January:December!D4)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="3">
         <f>SUM(January:December!B5)</f>
-        <v>0</v>
+        <v>9155</v>
       </c>
       <c r="C5" s="3">
         <f>SUM(January:December!C5)</f>
-        <v>0</v>
+        <v>922</v>
       </c>
       <c r="D5" s="3">
         <f>SUM(January:December!D5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="2">
         <f>SUM(January:December!B6)</f>
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2">
         <f>SUM(January:December!C6)</f>
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="D6" s="2">
         <f>SUM(January:December!D6)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="3">
         <f>SUM(January:December!B7)</f>
-        <v>0</v>
+        <v>6272</v>
       </c>
       <c r="C7" s="3">
         <f>SUM(January:December!C7)</f>
-        <v>0</v>
+        <v>894</v>
       </c>
       <c r="D7" s="3">
         <f>SUM(January:December!D7)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="2">
         <f>SUM(January:December!B8)</f>
-        <v>0</v>
+        <v>1062</v>
       </c>
       <c r="C8" s="2">
         <f>SUM(January:December!C8)</f>
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="D8" s="2">
         <f>SUM(January:December!D8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="3">
         <f>SUM(January:December!B9)</f>
-        <v>0</v>
+        <v>485</v>
       </c>
       <c r="C9" s="3">
         <f>SUM(January:December!C9)</f>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="D9" s="3">
         <f>SUM(January:December!D9)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="2">
         <f>SUM(January:December!B10)</f>
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="C10" s="2">
         <f>SUM(January:December!C10)</f>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D10" s="2">
         <f>SUM(January:December!D10)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="3">
         <f>SUM(January:December!B11)</f>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="C11" s="3">
         <f>SUM(January:December!C11)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D11" s="3">
         <f>SUM(January:December!D11)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -2277,245 +2276,245 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
       <c r="B13" s="4">
         <f>SUM(January:December!B13)</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C13" s="4">
         <f>SUM(January:December!C13)</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D13" s="4">
         <f>SUM(January:December!D13)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="5">
         <f>SUM(January:December!B14)</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="C14" s="5">
         <f>SUM(January:December!C14)</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D14" s="5">
         <f>SUM(January:December!D14)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
       <c r="B15" s="4">
         <f>SUM(January:December!B15)</f>
-        <v>0</v>
+        <v>745</v>
       </c>
       <c r="C15" s="4">
         <f>SUM(January:December!C15)</f>
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="D15" s="4">
         <f>SUM(January:December!D15)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
       <c r="B16" s="5">
         <f>SUM(January:December!B16)</f>
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="C16" s="5">
         <f>SUM(January:December!C16)</f>
-        <v>0</v>
+        <v>309</v>
       </c>
       <c r="D16" s="5">
         <f>SUM(January:December!D16)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="3">
         <f>SUM(January:December!B17)</f>
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="C17" s="3">
         <f>SUM(January:December!C17)</f>
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="D17" s="3">
         <f>SUM(January:December!D17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="2">
         <f>SUM(January:December!B18)</f>
-        <v>0</v>
+        <v>1898</v>
       </c>
       <c r="C18" s="2">
         <f>SUM(January:December!C18)</f>
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="D18" s="2">
         <f>SUM(January:December!D18)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="3">
         <f>SUM(January:December!B19)</f>
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="C19" s="3">
         <f>SUM(January:December!C19)</f>
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="D19" s="3">
         <f>SUM(January:December!D19)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="2">
         <f>SUM(January:December!B20)</f>
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="C20" s="2">
         <f>SUM(January:December!C20)</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D20" s="2">
         <f>SUM(January:December!D20)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="3">
         <f>SUM(January:December!B21)</f>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C21" s="3">
         <f>SUM(January:December!C21)</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D21" s="3">
         <f>SUM(January:December!D21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
       <c r="B22" s="2">
         <f>SUM(January:December!B22)</f>
-        <v>0</v>
+        <v>2018</v>
       </c>
       <c r="C22" s="2">
         <f>SUM(January:December!C22)</f>
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="D22" s="2">
         <f>SUM(January:December!D22)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B23" s="3">
         <f>SUM(January:December!B23)</f>
-        <v>0</v>
+        <v>313</v>
       </c>
       <c r="C23" s="3">
         <f>SUM(January:December!C23)</f>
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="D23" s="3">
         <f>SUM(January:December!D23)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
       <c r="B24" s="2">
         <f>SUM(January:December!B24)</f>
-        <v>0</v>
+        <v>2530</v>
       </c>
       <c r="C24" s="2">
         <f>SUM(January:December!C24)</f>
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="D24" s="2">
         <f>SUM(January:December!D24)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
       <c r="B25" s="3">
         <f>SUM(January:December!B25)</f>
-        <v>0</v>
+        <v>11305</v>
       </c>
       <c r="C25" s="3">
         <f>SUM(January:December!C25)</f>
-        <v>0</v>
+        <v>1184</v>
       </c>
       <c r="D25" s="3">
         <f>SUM(January:December!D25)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B26" s="2">
         <f>SUM(January:December!B26)</f>
-        <v>0</v>
+        <v>578</v>
       </c>
       <c r="C26" s="2">
         <f>SUM(January:December!C26)</f>
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="D26" s="2">
         <f>SUM(January:December!D26)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -2532,537 +2531,537 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
       <c r="B28" s="2">
         <f>SUM(January:December!B28)</f>
-        <v>0</v>
+        <v>641</v>
       </c>
       <c r="C28" s="2">
         <f>SUM(January:December!C28)</f>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="D28" s="2">
         <f>SUM(January:December!D28)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
       <c r="B29" s="3">
         <f>SUM(January:December!B29)</f>
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="C29" s="3">
         <f>SUM(January:December!C29)</f>
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="D29" s="3">
         <f>SUM(January:December!D29)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
       <c r="B30" s="2">
         <f>SUM(January:December!B30)</f>
-        <v>0</v>
+        <v>2580</v>
       </c>
       <c r="C30" s="2">
         <f>SUM(January:December!C30)</f>
-        <v>0</v>
+        <v>466</v>
       </c>
       <c r="D30" s="2">
         <f>SUM(January:December!D30)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
       <c r="B31" s="3">
         <f>SUM(January:December!B31)</f>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="C31" s="3">
         <f>SUM(January:December!C31)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D31" s="3">
         <f>SUM(January:December!D31)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B32" s="2">
         <f>SUM(January:December!B32)</f>
-        <v>0</v>
+        <v>494</v>
       </c>
       <c r="C32" s="2">
         <f>SUM(January:December!C32)</f>
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="D32" s="2">
         <f>SUM(January:December!D32)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
       <c r="B33" s="3">
         <f>SUM(January:December!B33)</f>
-        <v>0</v>
+        <v>1790</v>
       </c>
       <c r="C33" s="3">
         <f>SUM(January:December!C33)</f>
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="D33" s="3">
         <f>SUM(January:December!D33)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
       <c r="B34" s="2">
         <f>SUM(January:December!B34)</f>
-        <v>0</v>
+        <v>1061</v>
       </c>
       <c r="C34" s="2">
         <f>SUM(January:December!C34)</f>
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="D34" s="2">
         <f>SUM(January:December!D34)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
       <c r="B35" s="3">
         <f>SUM(January:December!B35)</f>
-        <v>0</v>
+        <v>645</v>
       </c>
       <c r="C35" s="3">
         <f>SUM(January:December!C35)</f>
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="D35" s="3">
         <f>SUM(January:December!D35)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
       <c r="B36" s="2">
         <f>SUM(January:December!B36)</f>
-        <v>0</v>
+        <v>6895</v>
       </c>
       <c r="C36" s="2">
         <f>SUM(January:December!C36)</f>
-        <v>0</v>
+        <v>1269</v>
       </c>
       <c r="D36" s="2">
         <f>SUM(January:December!D36)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
       <c r="B37" s="3">
         <f>SUM(January:December!B37)</f>
-        <v>0</v>
+        <v>979</v>
       </c>
       <c r="C37" s="3">
         <f>SUM(January:December!C37)</f>
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="D37" s="3">
         <f>SUM(January:December!D37)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B38" s="2">
         <f>SUM(January:December!B38)</f>
-        <v>0</v>
+        <v>3290</v>
       </c>
       <c r="C38" s="2">
         <f>SUM(January:December!C38)</f>
-        <v>0</v>
+        <v>322</v>
       </c>
       <c r="D38" s="2">
         <f>SUM(January:December!D38)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
       <c r="B39" s="3">
         <f>SUM(January:December!B39)</f>
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="C39" s="3">
         <f>SUM(January:December!C39)</f>
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="D39" s="3">
         <f>SUM(January:December!D39)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B40" s="6">
         <f>SUM(January:December!B40)</f>
-        <v>0</v>
+        <v>439</v>
       </c>
       <c r="C40" s="6">
         <f>SUM(January:December!C40)</f>
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D40" s="6">
         <f>SUM(January:December!D40)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
       <c r="B41" s="7">
         <f>SUM(January:December!B41)</f>
-        <v>0</v>
+        <v>2327</v>
       </c>
       <c r="C41" s="7">
         <f>SUM(January:December!C41)</f>
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="D41" s="7">
         <f>SUM(January:December!D41)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
       <c r="B42" s="6">
         <f>SUM(January:December!B42)</f>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="C42" s="6">
         <f>SUM(January:December!C42)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D42" s="6">
         <f>SUM(January:December!D42)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
       <c r="B43" s="7">
         <f>SUM(January:December!B43)</f>
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="C43" s="7">
         <f>SUM(January:December!C43)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D43" s="7">
         <f>SUM(January:December!D43)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B44" s="2">
         <f>SUM(January:December!B44)</f>
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="C44" s="2">
         <f>SUM(January:December!C44)</f>
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="D44" s="2">
         <f>SUM(January:December!D44)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
       <c r="B45" s="3">
         <f>SUM(January:December!B45)</f>
-        <v>0</v>
+        <v>323</v>
       </c>
       <c r="C45" s="3">
         <f>SUM(January:December!C45)</f>
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="D45" s="3">
         <f>SUM(January:December!D45)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
       <c r="B46" s="2">
         <f>SUM(January:December!B46)</f>
-        <v>0</v>
+        <v>1894</v>
       </c>
       <c r="C46" s="2">
         <f>SUM(January:December!C46)</f>
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="D46" s="2">
         <f>SUM(January:December!D46)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
       <c r="B47" s="3">
         <f>SUM(January:December!B47)</f>
-        <v>0</v>
+        <v>3565</v>
       </c>
       <c r="C47" s="3">
         <f>SUM(January:December!C47)</f>
-        <v>0</v>
+        <v>646</v>
       </c>
       <c r="D47" s="3">
         <f>SUM(January:December!D47)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
       <c r="B48" s="2">
         <f>SUM(January:December!B48)</f>
-        <v>0</v>
+        <v>1357</v>
       </c>
       <c r="C48" s="2">
         <f>SUM(January:December!C48)</f>
-        <v>0</v>
+        <v>493</v>
       </c>
       <c r="D48" s="2">
         <f>SUM(January:December!D48)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
       <c r="B49" s="3">
         <f>SUM(January:December!B49)</f>
-        <v>0</v>
+        <v>902</v>
       </c>
       <c r="C49" s="3">
         <f>SUM(January:December!C49)</f>
-        <v>0</v>
+        <v>271</v>
       </c>
       <c r="D49" s="3">
         <f>SUM(January:December!D49)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B50" s="2">
         <f>SUM(January:December!B50)</f>
-        <v>0</v>
+        <v>3880</v>
       </c>
       <c r="C50" s="2">
         <f>SUM(January:December!C50)</f>
-        <v>0</v>
+        <v>363</v>
       </c>
       <c r="D50" s="2">
         <f>SUM(January:December!D50)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B51" s="3">
         <f>SUM(January:December!B51)</f>
-        <v>0</v>
+        <v>429</v>
       </c>
       <c r="C51" s="3">
         <f>SUM(January:December!C51)</f>
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="D51" s="3">
         <f>SUM(January:December!D51)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
       <c r="B52" s="2">
         <f>SUM(January:December!B52)</f>
-        <v>0</v>
+        <v>1570</v>
       </c>
       <c r="C52" s="2">
         <f>SUM(January:December!C52)</f>
-        <v>0</v>
+        <v>287</v>
       </c>
       <c r="D52" s="2">
         <f>SUM(January:December!D52)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B53" s="3">
         <f>SUM(January:December!B53)</f>
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="C53" s="3">
         <f>SUM(January:December!C53)</f>
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="D53" s="3">
         <f>SUM(January:December!D53)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
       <c r="B54" s="2">
         <f>SUM(January:December!B54)</f>
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="C54" s="2">
         <f>SUM(January:December!C54)</f>
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="D54" s="2">
         <f>SUM(January:December!D54)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
       <c r="B55" s="3">
         <f>SUM(January:December!B55)</f>
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="C55" s="3">
         <f>SUM(January:December!C55)</f>
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="D55" s="3">
         <f>SUM(January:December!D55)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
       <c r="B56" s="4">
         <f>SUM(January:December!B56)</f>
-        <v>0</v>
+        <v>1293</v>
       </c>
       <c r="C56" s="4">
         <f>SUM(January:December!C56)</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="D56" s="4">
         <f>SUM(January:December!D56)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
       <c r="B57" s="7">
         <f>SUM(January:December!B57)</f>
-        <v>0</v>
+        <v>3129</v>
       </c>
       <c r="C57" s="7">
         <f>SUM(January:December!C57)</f>
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="D57" s="7">
         <f>SUM(January:December!D57)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
       <c r="B58" s="8">
         <f>SUM(January:December!B58)</f>
-        <v>0</v>
+        <v>86140</v>
       </c>
       <c r="C58" s="8">
         <f>SUM(January:December!C58)</f>
-        <v>0</v>
+        <v>15198</v>
       </c>
       <c r="D58" s="8">
         <f>SUM(January:December!D58)</f>
-        <v>0</v>
+        <v>14416</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D2"/>
+  <autoFilter ref="A2:D2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="B3">
-    <cfRule type="cellIs" dxfId="97" priority="97" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="97" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3552,15 +3551,15 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -3570,7 +3569,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -3584,7 +3583,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -3592,7 +3591,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -3600,7 +3599,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -3608,7 +3607,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -3616,7 +3615,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -3624,7 +3623,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -3632,7 +3631,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -3640,7 +3639,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -3648,7 +3647,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -3656,7 +3655,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -3664,7 +3663,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -3672,7 +3671,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -3680,7 +3679,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -3688,7 +3687,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -3696,7 +3695,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -3704,7 +3703,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -3712,7 +3711,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -3720,7 +3719,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -3728,7 +3727,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -3736,7 +3735,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -3744,7 +3743,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -3752,7 +3751,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -3760,7 +3759,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -3768,7 +3767,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -3776,7 +3775,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -3784,7 +3783,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -3792,7 +3791,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -3800,7 +3799,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -3808,7 +3807,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -3816,7 +3815,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -3824,7 +3823,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -3832,7 +3831,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -3840,7 +3839,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -3848,7 +3847,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -3856,7 +3855,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -3864,7 +3863,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -3872,7 +3871,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -3880,7 +3879,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -3888,7 +3887,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -3896,7 +3895,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -3904,7 +3903,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -3912,7 +3911,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -3920,7 +3919,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -3928,7 +3927,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -3936,7 +3935,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -3944,7 +3943,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -3952,7 +3951,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -3960,7 +3959,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -3968,7 +3967,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -3976,7 +3975,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -3984,7 +3983,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -3992,7 +3991,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -4000,7 +3999,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -4008,7 +4007,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -4016,7 +4015,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -4024,7 +4023,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -4033,21 +4032,21 @@
       <c r="D58" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D2"/>
+  <autoFilter ref="A2:D2" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -4057,7 +4056,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -4071,7 +4070,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -4079,7 +4078,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -4087,7 +4086,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -4095,7 +4094,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -4103,7 +4102,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -4111,7 +4110,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -4119,7 +4118,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -4127,7 +4126,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -4135,7 +4134,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -4143,7 +4142,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -4151,7 +4150,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -4159,7 +4158,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -4167,7 +4166,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -4175,7 +4174,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -4183,7 +4182,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -4191,7 +4190,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -4199,7 +4198,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -4207,7 +4206,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -4215,7 +4214,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -4223,7 +4222,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -4231,7 +4230,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -4239,7 +4238,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -4247,7 +4246,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -4255,7 +4254,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -4263,7 +4262,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -4271,7 +4270,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -4279,7 +4278,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -4287,7 +4286,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -4295,7 +4294,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -4303,7 +4302,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -4311,7 +4310,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -4319,7 +4318,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -4327,7 +4326,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -4335,7 +4334,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -4343,7 +4342,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -4351,7 +4350,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -4359,7 +4358,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -4367,7 +4366,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -4375,7 +4374,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -4383,7 +4382,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -4391,7 +4390,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -4399,7 +4398,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -4407,7 +4406,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -4415,7 +4414,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -4423,7 +4422,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -4431,7 +4430,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -4439,7 +4438,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -4447,7 +4446,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -4455,7 +4454,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -4463,7 +4462,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -4471,7 +4470,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -4479,7 +4478,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -4487,7 +4486,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -4495,7 +4494,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -4503,7 +4502,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -4511,7 +4510,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -4520,21 +4519,21 @@
       <c r="D58" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D2"/>
+  <autoFilter ref="A2:D2" xr:uid="{00000000-0009-0000-0000-00000A000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -4544,7 +4543,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -4558,7 +4557,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -4566,7 +4565,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -4574,7 +4573,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -4582,7 +4581,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -4590,7 +4589,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -4598,7 +4597,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -4606,7 +4605,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -4614,7 +4613,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -4622,7 +4621,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -4630,7 +4629,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -4638,7 +4637,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -4646,7 +4645,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -4654,7 +4653,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -4662,7 +4661,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -4670,7 +4669,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -4678,7 +4677,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -4686,7 +4685,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -4694,7 +4693,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -4702,7 +4701,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -4710,7 +4709,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -4718,7 +4717,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -4726,7 +4725,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -4734,7 +4733,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -4742,7 +4741,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -4750,7 +4749,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -4758,7 +4757,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -4766,7 +4765,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -4774,7 +4773,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -4782,7 +4781,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -4790,7 +4789,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -4798,7 +4797,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -4806,7 +4805,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -4814,7 +4813,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -4822,7 +4821,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -4830,7 +4829,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -4838,7 +4837,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -4846,7 +4845,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -4854,7 +4853,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -4862,7 +4861,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -4870,7 +4869,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -4878,7 +4877,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -4886,7 +4885,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -4894,7 +4893,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -4902,7 +4901,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -4910,7 +4909,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -4918,7 +4917,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -4926,7 +4925,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -4934,7 +4933,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -4942,7 +4941,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -4950,7 +4949,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -4958,7 +4957,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -4966,7 +4965,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -4974,7 +4973,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -4982,7 +4981,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -4990,7 +4989,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -4998,7 +4997,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -5007,21 +5006,21 @@
       <c r="D58" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D2"/>
+  <autoFilter ref="A2:D2" xr:uid="{00000000-0009-0000-0000-00000B000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -5031,7 +5030,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -5045,7 +5044,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -5053,7 +5052,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -5061,7 +5060,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -5069,7 +5068,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -5077,7 +5076,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -5085,7 +5084,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -5093,7 +5092,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -5101,7 +5100,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -5109,7 +5108,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -5117,7 +5116,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -5125,7 +5124,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -5133,7 +5132,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -5141,7 +5140,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -5149,7 +5148,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -5157,7 +5156,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -5165,7 +5164,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -5173,7 +5172,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -5181,7 +5180,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -5189,7 +5188,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -5197,7 +5196,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -5205,7 +5204,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -5213,7 +5212,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -5221,7 +5220,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -5229,7 +5228,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -5237,7 +5236,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -5245,7 +5244,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -5253,7 +5252,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -5261,7 +5260,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -5269,7 +5268,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -5277,7 +5276,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -5285,7 +5284,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -5293,7 +5292,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -5301,7 +5300,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -5309,7 +5308,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -5317,7 +5316,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -5325,7 +5324,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -5333,7 +5332,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -5341,7 +5340,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -5349,7 +5348,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -5357,7 +5356,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -5365,7 +5364,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -5373,7 +5372,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -5381,7 +5380,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -5389,7 +5388,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -5397,7 +5396,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -5405,7 +5404,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -5413,7 +5412,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -5421,7 +5420,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -5429,7 +5428,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -5437,7 +5436,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -5445,7 +5444,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -5453,7 +5452,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -5461,7 +5460,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -5469,7 +5468,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -5477,7 +5476,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -5485,7 +5484,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -5499,25 +5498,29 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="19"/>
+      <c r="B1" s="19">
+        <v>46023</v>
+      </c>
       <c r="C1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="21"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D1" s="21">
+        <v>46053</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -5531,470 +5534,806 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B3" s="3">
+        <v>5663</v>
+      </c>
+      <c r="C3" s="3">
+        <v>973</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="2">
+        <v>3255</v>
+      </c>
+      <c r="C4" s="2">
+        <v>287</v>
+      </c>
+      <c r="D4" s="2">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="3">
+        <v>9155</v>
+      </c>
+      <c r="C5" s="3">
+        <v>922</v>
+      </c>
+      <c r="D5" s="3">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="2">
+        <v>89</v>
+      </c>
+      <c r="C6" s="2">
+        <v>111</v>
+      </c>
+      <c r="D6" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B7" s="3">
+        <v>6272</v>
+      </c>
+      <c r="C7" s="3">
+        <v>894</v>
+      </c>
+      <c r="D7" s="3">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B8" s="2">
+        <v>1062</v>
+      </c>
+      <c r="C8" s="2">
+        <v>151</v>
+      </c>
+      <c r="D8" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="3">
+        <v>485</v>
+      </c>
+      <c r="C9" s="3">
+        <v>160</v>
+      </c>
+      <c r="D9" s="3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="2">
+        <v>251</v>
+      </c>
+      <c r="C10" s="2">
+        <v>44</v>
+      </c>
+      <c r="D10" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="3">
+        <v>53</v>
+      </c>
+      <c r="C11" s="3">
+        <v>16</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B13" s="4">
+        <v>28</v>
+      </c>
+      <c r="C13" s="4">
+        <v>48</v>
+      </c>
+      <c r="D13" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B14" s="5">
+        <v>150</v>
+      </c>
+      <c r="C14" s="5">
+        <v>100</v>
+      </c>
+      <c r="D14" s="5">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B15" s="4">
+        <v>745</v>
+      </c>
+      <c r="C15" s="4">
+        <v>209</v>
+      </c>
+      <c r="D15" s="4">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B16" s="5">
+        <v>370</v>
+      </c>
+      <c r="C16" s="5">
+        <v>309</v>
+      </c>
+      <c r="D16" s="5">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="3">
+        <v>246</v>
+      </c>
+      <c r="C17" s="3">
+        <v>179</v>
+      </c>
+      <c r="D17" s="3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B18" s="2">
+        <v>1898</v>
+      </c>
+      <c r="C18" s="2">
+        <v>394</v>
+      </c>
+      <c r="D18" s="2">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B19" s="3">
+        <v>179</v>
+      </c>
+      <c r="C19" s="3">
+        <v>73</v>
+      </c>
+      <c r="D19" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="2">
+        <v>2032</v>
+      </c>
+      <c r="C20" s="2">
+        <v>200</v>
+      </c>
+      <c r="D20" s="2">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="3">
+        <v>27</v>
+      </c>
+      <c r="C21" s="3">
+        <v>45</v>
+      </c>
+      <c r="D21" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B22" s="2">
+        <v>2018</v>
+      </c>
+      <c r="C22" s="2">
+        <v>355</v>
+      </c>
+      <c r="D22" s="2">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B23" s="3">
+        <v>313</v>
+      </c>
+      <c r="C23" s="3">
+        <v>183</v>
+      </c>
+      <c r="D23" s="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B24" s="2">
+        <v>2530</v>
+      </c>
+      <c r="C24" s="2">
+        <v>445</v>
+      </c>
+      <c r="D24" s="2">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B25" s="3">
+        <v>11305</v>
+      </c>
+      <c r="C25" s="3">
+        <v>1184</v>
+      </c>
+      <c r="D25" s="3">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B26" s="2">
+        <v>578</v>
+      </c>
+      <c r="C26" s="2">
+        <v>253</v>
+      </c>
+      <c r="D26" s="2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B27" s="3">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B28" s="2">
+        <v>641</v>
+      </c>
+      <c r="C28" s="2">
+        <v>116</v>
+      </c>
+      <c r="D28" s="2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B29" s="3">
+        <v>459</v>
+      </c>
+      <c r="C29" s="3">
+        <v>103</v>
+      </c>
+      <c r="D29" s="3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B30" s="2">
+        <v>2580</v>
+      </c>
+      <c r="C30" s="2">
+        <v>466</v>
+      </c>
+      <c r="D30" s="2">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="3">
+        <v>37</v>
+      </c>
+      <c r="C31" s="3">
+        <v>17</v>
+      </c>
+      <c r="D31" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="2">
+        <v>494</v>
+      </c>
+      <c r="C32" s="2">
+        <v>186</v>
+      </c>
+      <c r="D32" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="3">
+        <v>1790</v>
+      </c>
+      <c r="C33" s="3">
+        <v>430</v>
+      </c>
+      <c r="D33" s="3">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="2">
+        <v>1061</v>
+      </c>
+      <c r="C34" s="2">
+        <v>310</v>
+      </c>
+      <c r="D34" s="2">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="3">
+        <v>645</v>
+      </c>
+      <c r="C35" s="3">
+        <v>86</v>
+      </c>
+      <c r="D35" s="3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B36" s="2">
+        <v>6895</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1269</v>
+      </c>
+      <c r="D36" s="2">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B37" s="3">
+        <v>979</v>
+      </c>
+      <c r="C37" s="3">
+        <v>520</v>
+      </c>
+      <c r="D37" s="3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B38" s="2">
+        <v>3290</v>
+      </c>
+      <c r="C38" s="2">
+        <v>322</v>
+      </c>
+      <c r="D38" s="2">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B39" s="3">
+        <v>187</v>
+      </c>
+      <c r="C39" s="3">
+        <v>187</v>
+      </c>
+      <c r="D39" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B40" s="6">
+        <v>439</v>
+      </c>
+      <c r="C40" s="6">
+        <v>61</v>
+      </c>
+      <c r="D40" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B41" s="7">
+        <v>2327</v>
+      </c>
+      <c r="C41" s="7">
+        <v>114</v>
+      </c>
+      <c r="D41" s="7">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B42" s="6">
+        <v>53</v>
+      </c>
+      <c r="C42" s="6">
+        <v>12</v>
+      </c>
+      <c r="D42" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B43" s="7">
+        <v>310</v>
+      </c>
+      <c r="C43" s="7">
+        <v>24</v>
+      </c>
+      <c r="D43" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B44" s="2">
+        <v>345</v>
+      </c>
+      <c r="C44" s="2">
+        <v>89</v>
+      </c>
+      <c r="D44" s="2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B45" s="3">
+        <v>323</v>
+      </c>
+      <c r="C45" s="3">
+        <v>143</v>
+      </c>
+      <c r="D45" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B46" s="2">
+        <v>1894</v>
+      </c>
+      <c r="C46" s="2">
+        <v>392</v>
+      </c>
+      <c r="D46" s="2">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B47" s="3">
+        <v>3565</v>
+      </c>
+      <c r="C47" s="3">
+        <v>646</v>
+      </c>
+      <c r="D47" s="3">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B48" s="2">
+        <v>1357</v>
+      </c>
+      <c r="C48" s="2">
+        <v>493</v>
+      </c>
+      <c r="D48" s="2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B49" s="3">
+        <v>902</v>
+      </c>
+      <c r="C49" s="3">
+        <v>271</v>
+      </c>
+      <c r="D49" s="3">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B50" s="2">
+        <v>3880</v>
+      </c>
+      <c r="C50" s="2">
+        <v>363</v>
+      </c>
+      <c r="D50" s="2">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B51" s="3">
+        <v>429</v>
+      </c>
+      <c r="C51" s="3">
+        <v>142</v>
+      </c>
+      <c r="D51" s="3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B52" s="2">
+        <v>1570</v>
+      </c>
+      <c r="C52" s="2">
+        <v>287</v>
+      </c>
+      <c r="D52" s="2">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B53" s="3">
+        <v>143</v>
+      </c>
+      <c r="C53" s="3">
+        <v>191</v>
+      </c>
+      <c r="D53" s="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B54" s="2">
+        <v>209</v>
+      </c>
+      <c r="C54" s="2">
+        <v>234</v>
+      </c>
+      <c r="D54" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B55" s="3">
+        <v>632</v>
+      </c>
+      <c r="C55" s="3">
+        <v>189</v>
+      </c>
+      <c r="D55" s="3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B56" s="4">
+        <v>1293</v>
+      </c>
+      <c r="C56" s="4">
+        <v>600</v>
+      </c>
+      <c r="D56" s="4">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B57" s="7">
+        <v>3129</v>
+      </c>
+      <c r="C57" s="7">
+        <v>186</v>
+      </c>
+      <c r="D57" s="7">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
+      <c r="B58" s="8">
+        <v>86140</v>
+      </c>
+      <c r="C58" s="8">
+        <v>15198</v>
+      </c>
+      <c r="D58" s="8">
+        <v>14416</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D2"/>
+  <autoFilter ref="A2:D2" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -6004,7 +6343,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -6018,7 +6357,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -6026,7 +6365,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -6034,7 +6373,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -6042,7 +6381,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -6050,7 +6389,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -6058,7 +6397,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -6066,7 +6405,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -6074,7 +6413,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -6082,7 +6421,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -6090,7 +6429,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -6098,7 +6437,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -6106,7 +6445,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -6114,7 +6453,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -6122,7 +6461,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -6130,7 +6469,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -6138,7 +6477,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -6146,7 +6485,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -6154,7 +6493,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -6162,7 +6501,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -6170,7 +6509,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -6178,7 +6517,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -6186,7 +6525,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -6194,7 +6533,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -6202,7 +6541,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -6210,7 +6549,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -6218,7 +6557,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -6226,7 +6565,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -6234,7 +6573,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -6242,7 +6581,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -6250,7 +6589,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -6258,7 +6597,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -6266,7 +6605,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -6274,7 +6613,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -6282,7 +6621,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -6290,7 +6629,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -6298,7 +6637,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -6306,7 +6645,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -6314,7 +6653,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -6322,7 +6661,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -6330,7 +6669,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -6338,7 +6677,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -6346,7 +6685,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -6354,7 +6693,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -6362,7 +6701,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -6370,7 +6709,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -6378,7 +6717,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -6386,7 +6725,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -6394,7 +6733,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -6402,7 +6741,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -6410,7 +6749,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -6418,7 +6757,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -6426,7 +6765,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -6434,7 +6773,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -6442,7 +6781,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -6450,7 +6789,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -6458,7 +6797,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -6467,21 +6806,21 @@
       <c r="D58" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D2"/>
+  <autoFilter ref="A2:D2" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -6491,7 +6830,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -6505,7 +6844,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -6513,7 +6852,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -6521,7 +6860,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -6529,7 +6868,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -6537,7 +6876,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -6545,7 +6884,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -6553,7 +6892,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -6561,7 +6900,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -6569,7 +6908,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -6577,7 +6916,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -6585,7 +6924,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -6593,7 +6932,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -6601,7 +6940,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -6609,7 +6948,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -6617,7 +6956,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -6625,7 +6964,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -6633,7 +6972,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -6641,7 +6980,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -6649,7 +6988,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -6657,7 +6996,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -6665,7 +7004,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -6673,7 +7012,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -6681,7 +7020,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -6689,7 +7028,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -6697,7 +7036,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -6705,7 +7044,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -6713,7 +7052,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -6721,7 +7060,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -6729,7 +7068,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -6737,7 +7076,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -6745,7 +7084,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -6753,7 +7092,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -6761,7 +7100,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -6769,7 +7108,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -6777,7 +7116,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -6785,7 +7124,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -6793,7 +7132,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -6801,7 +7140,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -6809,7 +7148,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -6817,7 +7156,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -6825,7 +7164,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -6833,7 +7172,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -6841,7 +7180,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -6849,7 +7188,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -6857,7 +7196,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -6865,7 +7204,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -6873,7 +7212,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -6881,7 +7220,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -6889,7 +7228,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -6897,7 +7236,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -6905,7 +7244,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -6913,7 +7252,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -6921,7 +7260,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -6929,7 +7268,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -6937,7 +7276,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -6945,7 +7284,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -6954,21 +7293,21 @@
       <c r="D58" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D2"/>
+  <autoFilter ref="A2:D2" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -6978,7 +7317,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -6992,7 +7331,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -7000,7 +7339,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -7008,7 +7347,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -7016,7 +7355,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -7024,7 +7363,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -7032,7 +7371,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -7040,7 +7379,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -7048,7 +7387,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -7056,7 +7395,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -7064,7 +7403,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -7072,7 +7411,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -7080,7 +7419,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -7088,7 +7427,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -7096,7 +7435,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -7104,7 +7443,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -7112,7 +7451,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -7120,7 +7459,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -7128,7 +7467,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -7136,7 +7475,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -7144,7 +7483,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -7152,7 +7491,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -7160,7 +7499,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -7168,7 +7507,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -7176,7 +7515,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -7184,7 +7523,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -7192,7 +7531,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -7200,7 +7539,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -7208,7 +7547,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -7216,7 +7555,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -7224,7 +7563,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -7232,7 +7571,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -7240,7 +7579,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -7248,7 +7587,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -7256,7 +7595,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -7264,7 +7603,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -7272,7 +7611,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -7280,7 +7619,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -7288,7 +7627,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -7296,7 +7635,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -7304,7 +7643,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -7312,7 +7651,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -7320,7 +7659,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -7328,7 +7667,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -7336,7 +7675,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -7344,7 +7683,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -7352,7 +7691,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -7360,7 +7699,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -7368,7 +7707,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -7376,7 +7715,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -7384,7 +7723,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -7392,7 +7731,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -7400,7 +7739,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -7408,7 +7747,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -7416,7 +7755,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -7424,7 +7763,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -7432,7 +7771,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -7441,21 +7780,21 @@
       <c r="D58" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D2"/>
+  <autoFilter ref="A2:D2" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -7465,7 +7804,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -7479,7 +7818,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -7487,7 +7826,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -7495,7 +7834,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -7503,7 +7842,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -7511,7 +7850,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -7519,7 +7858,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -7527,7 +7866,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -7535,7 +7874,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -7543,7 +7882,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -7551,7 +7890,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -7559,7 +7898,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -7567,7 +7906,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -7575,7 +7914,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -7583,7 +7922,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -7591,7 +7930,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -7599,7 +7938,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -7607,7 +7946,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -7615,7 +7954,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -7623,7 +7962,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -7631,7 +7970,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -7639,7 +7978,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -7647,7 +7986,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -7655,7 +7994,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -7663,7 +8002,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -7671,7 +8010,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -7679,7 +8018,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -7687,7 +8026,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -7695,7 +8034,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -7703,7 +8042,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -7711,7 +8050,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -7719,7 +8058,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -7727,7 +8066,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -7735,7 +8074,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -7743,7 +8082,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -7751,7 +8090,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -7759,7 +8098,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -7767,7 +8106,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -7775,7 +8114,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -7783,7 +8122,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -7791,7 +8130,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -7799,7 +8138,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -7807,7 +8146,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -7815,7 +8154,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -7823,7 +8162,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -7831,7 +8170,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -7839,7 +8178,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -7847,7 +8186,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -7855,7 +8194,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -7863,7 +8202,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -7871,7 +8210,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -7879,7 +8218,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -7887,7 +8226,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -7895,7 +8234,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -7903,7 +8242,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -7911,7 +8250,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -7919,7 +8258,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -7928,21 +8267,21 @@
       <c r="D58" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D2"/>
+  <autoFilter ref="A2:D2" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -7952,7 +8291,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -7966,7 +8305,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -7974,7 +8313,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -7982,7 +8321,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -7990,7 +8329,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -7998,7 +8337,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -8006,7 +8345,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -8014,7 +8353,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -8022,7 +8361,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -8030,7 +8369,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -8038,7 +8377,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -8046,7 +8385,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -8054,7 +8393,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -8062,7 +8401,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -8070,7 +8409,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -8078,7 +8417,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -8086,7 +8425,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -8094,7 +8433,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -8102,7 +8441,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -8110,7 +8449,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -8118,7 +8457,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -8126,7 +8465,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -8134,7 +8473,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -8142,7 +8481,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -8150,7 +8489,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -8158,7 +8497,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -8166,7 +8505,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -8174,7 +8513,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -8182,7 +8521,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -8190,7 +8529,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -8198,7 +8537,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -8206,7 +8545,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -8214,7 +8553,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -8222,7 +8561,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -8230,7 +8569,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -8238,7 +8577,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -8246,7 +8585,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -8254,7 +8593,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -8262,7 +8601,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -8270,7 +8609,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -8278,7 +8617,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -8286,7 +8625,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -8294,7 +8633,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -8302,7 +8641,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -8310,7 +8649,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -8318,7 +8657,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -8326,7 +8665,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -8334,7 +8673,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -8342,7 +8681,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -8350,7 +8689,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -8358,7 +8697,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -8366,7 +8705,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -8374,7 +8713,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -8382,7 +8721,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -8390,7 +8729,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -8398,7 +8737,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -8406,7 +8745,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -8415,21 +8754,21 @@
       <c r="D58" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D2"/>
+  <autoFilter ref="A2:D2" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -8439,7 +8778,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -8453,7 +8792,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -8461,7 +8800,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -8469,7 +8808,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -8477,7 +8816,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -8485,7 +8824,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -8493,7 +8832,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -8501,7 +8840,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -8509,7 +8848,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -8517,7 +8856,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -8525,7 +8864,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -8533,7 +8872,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -8541,7 +8880,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -8549,7 +8888,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -8557,7 +8896,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -8565,7 +8904,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -8573,7 +8912,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -8581,7 +8920,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -8589,7 +8928,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -8597,7 +8936,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -8605,7 +8944,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -8613,7 +8952,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -8621,7 +8960,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -8629,7 +8968,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -8637,7 +8976,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -8645,7 +8984,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -8653,7 +8992,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -8661,7 +9000,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -8669,7 +9008,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -8677,7 +9016,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -8685,7 +9024,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -8693,7 +9032,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -8701,7 +9040,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -8709,7 +9048,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -8717,7 +9056,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -8725,7 +9064,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -8733,7 +9072,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -8741,7 +9080,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -8749,7 +9088,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -8757,7 +9096,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -8765,7 +9104,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -8773,7 +9112,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -8781,7 +9120,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -8789,7 +9128,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -8797,7 +9136,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -8805,7 +9144,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -8813,7 +9152,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -8821,7 +9160,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -8829,7 +9168,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -8837,7 +9176,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -8845,7 +9184,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -8853,7 +9192,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -8861,7 +9200,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -8869,7 +9208,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -8877,7 +9216,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -8885,7 +9224,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -8893,7 +9232,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -8902,21 +9241,21 @@
       <c r="D58" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D2"/>
+  <autoFilter ref="A2:D2" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -8926,7 +9265,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -8940,7 +9279,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -8948,7 +9287,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -8956,7 +9295,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -8964,7 +9303,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -8972,7 +9311,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -8980,7 +9319,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -8988,7 +9327,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -8996,7 +9335,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -9004,7 +9343,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -9012,7 +9351,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -9020,7 +9359,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -9028,7 +9367,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -9036,7 +9375,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -9044,7 +9383,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -9052,7 +9391,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -9060,7 +9399,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -9068,7 +9407,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -9076,7 +9415,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -9084,7 +9423,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -9092,7 +9431,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -9100,7 +9439,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -9108,7 +9447,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -9116,7 +9455,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -9124,7 +9463,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -9132,7 +9471,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -9140,7 +9479,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -9148,7 +9487,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -9156,7 +9495,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -9164,7 +9503,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -9172,7 +9511,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -9180,7 +9519,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -9188,7 +9527,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -9196,7 +9535,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -9204,7 +9543,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -9212,7 +9551,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -9220,7 +9559,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -9228,7 +9567,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -9236,7 +9575,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -9244,7 +9583,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -9252,7 +9591,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -9260,7 +9599,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -9268,7 +9607,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -9276,7 +9615,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -9284,7 +9623,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -9292,7 +9631,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -9300,7 +9639,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -9308,7 +9647,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -9316,7 +9655,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -9324,7 +9663,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -9332,7 +9671,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -9340,7 +9679,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -9348,7 +9687,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -9356,7 +9695,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -9364,7 +9703,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -9372,7 +9711,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -9380,7 +9719,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -9389,7 +9728,7 @@
       <c r="D58" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D2"/>
+  <autoFilter ref="A2:D2" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/statistics_files/nekls_executive_board/2026/2026_next_statistics.xlsx
+++ b/statistics_files/nekls_executive_board/2026/2026_next_statistics.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Staff\Documents\GitHub\next_statistics\statistics_files\nekls_executive_board\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\nekls_executive_board\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F23601E-C71A-4FCD-ADE9-583A24B8F1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{493527C4-8022-4CFA-A9E1-A65C5F5685B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Annual totals" sheetId="1" r:id="rId1"/>
@@ -2071,13 +2071,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -2089,10 +2089,10 @@
       </c>
       <c r="D1" s="21">
         <f>MAX(January:December!D1)</f>
-        <v>46053</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>46081</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -2106,160 +2106,160 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="3">
         <f>SUM(January:December!B3)</f>
-        <v>5663</v>
+        <v>10785</v>
       </c>
       <c r="C3" s="3">
         <f>SUM(January:December!C3)</f>
-        <v>973</v>
+        <v>1799</v>
       </c>
       <c r="D3" s="3">
         <f>SUM(January:December!D3)</f>
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2">
         <f>SUM(January:December!B4)</f>
-        <v>3255</v>
+        <v>6321</v>
       </c>
       <c r="C4" s="2">
         <f>SUM(January:December!C4)</f>
-        <v>287</v>
+        <v>572</v>
       </c>
       <c r="D4" s="2">
         <f>SUM(January:December!D4)</f>
-        <v>496</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="3">
         <f>SUM(January:December!B5)</f>
-        <v>9155</v>
+        <v>17219</v>
       </c>
       <c r="C5" s="3">
         <f>SUM(January:December!C5)</f>
-        <v>922</v>
+        <v>1562</v>
       </c>
       <c r="D5" s="3">
         <f>SUM(January:December!D5)</f>
-        <v>914</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="2">
         <f>SUM(January:December!B6)</f>
-        <v>89</v>
+        <v>191</v>
       </c>
       <c r="C6" s="2">
         <f>SUM(January:December!C6)</f>
-        <v>111</v>
+        <v>184</v>
       </c>
       <c r="D6" s="2">
         <f>SUM(January:December!D6)</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="3">
         <f>SUM(January:December!B7)</f>
-        <v>6272</v>
+        <v>11922</v>
       </c>
       <c r="C7" s="3">
         <f>SUM(January:December!C7)</f>
-        <v>894</v>
+        <v>1698</v>
       </c>
       <c r="D7" s="3">
         <f>SUM(January:December!D7)</f>
-        <v>874</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="2">
         <f>SUM(January:December!B8)</f>
-        <v>1062</v>
+        <v>1959</v>
       </c>
       <c r="C8" s="2">
         <f>SUM(January:December!C8)</f>
-        <v>151</v>
+        <v>277</v>
       </c>
       <c r="D8" s="2">
         <f>SUM(January:December!D8)</f>
-        <v>130</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="3">
         <f>SUM(January:December!B9)</f>
-        <v>485</v>
+        <v>1083</v>
       </c>
       <c r="C9" s="3">
         <f>SUM(January:December!C9)</f>
-        <v>160</v>
+        <v>286</v>
       </c>
       <c r="D9" s="3">
         <f>SUM(January:December!D9)</f>
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="2">
         <f>SUM(January:December!B10)</f>
-        <v>251</v>
+        <v>476</v>
       </c>
       <c r="C10" s="2">
         <f>SUM(January:December!C10)</f>
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="D10" s="2">
         <f>SUM(January:December!D10)</f>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="3">
         <f>SUM(January:December!B11)</f>
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="C11" s="3">
         <f>SUM(January:December!C11)</f>
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D11" s="3">
         <f>SUM(January:December!D11)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -2276,245 +2276,245 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
       <c r="B13" s="4">
         <f>SUM(January:December!B13)</f>
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C13" s="4">
         <f>SUM(January:December!C13)</f>
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="D13" s="4">
         <f>SUM(January:December!D13)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="5">
         <f>SUM(January:December!B14)</f>
-        <v>150</v>
+        <v>275</v>
       </c>
       <c r="C14" s="5">
         <f>SUM(January:December!C14)</f>
-        <v>100</v>
+        <v>258</v>
       </c>
       <c r="D14" s="5">
         <f>SUM(January:December!D14)</f>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
       <c r="B15" s="4">
         <f>SUM(January:December!B15)</f>
-        <v>745</v>
+        <v>1467</v>
       </c>
       <c r="C15" s="4">
         <f>SUM(January:December!C15)</f>
-        <v>209</v>
+        <v>433</v>
       </c>
       <c r="D15" s="4">
         <f>SUM(January:December!D15)</f>
-        <v>175</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
       <c r="B16" s="5">
         <f>SUM(January:December!B16)</f>
-        <v>370</v>
+        <v>596</v>
       </c>
       <c r="C16" s="5">
         <f>SUM(January:December!C16)</f>
-        <v>309</v>
+        <v>558</v>
       </c>
       <c r="D16" s="5">
         <f>SUM(January:December!D16)</f>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="3">
         <f>SUM(January:December!B17)</f>
-        <v>246</v>
+        <v>540</v>
       </c>
       <c r="C17" s="3">
         <f>SUM(January:December!C17)</f>
-        <v>179</v>
+        <v>326</v>
       </c>
       <c r="D17" s="3">
         <f>SUM(January:December!D17)</f>
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="2">
         <f>SUM(January:December!B18)</f>
-        <v>1898</v>
+        <v>3696</v>
       </c>
       <c r="C18" s="2">
         <f>SUM(January:December!C18)</f>
-        <v>394</v>
+        <v>716</v>
       </c>
       <c r="D18" s="2">
         <f>SUM(January:December!D18)</f>
-        <v>507</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="3">
         <f>SUM(January:December!B19)</f>
-        <v>179</v>
+        <v>384</v>
       </c>
       <c r="C19" s="3">
         <f>SUM(January:December!C19)</f>
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="D19" s="3">
         <f>SUM(January:December!D19)</f>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="2">
         <f>SUM(January:December!B20)</f>
-        <v>2032</v>
+        <v>4378</v>
       </c>
       <c r="C20" s="2">
         <f>SUM(January:December!C20)</f>
-        <v>200</v>
+        <v>464</v>
       </c>
       <c r="D20" s="2">
         <f>SUM(January:December!D20)</f>
-        <v>391</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="3">
         <f>SUM(January:December!B21)</f>
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="C21" s="3">
         <f>SUM(January:December!C21)</f>
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="D21" s="3">
         <f>SUM(January:December!D21)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
       <c r="B22" s="2">
         <f>SUM(January:December!B22)</f>
-        <v>2018</v>
+        <v>3815</v>
       </c>
       <c r="C22" s="2">
         <f>SUM(January:December!C22)</f>
-        <v>355</v>
+        <v>654</v>
       </c>
       <c r="D22" s="2">
         <f>SUM(January:December!D22)</f>
-        <v>396</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B23" s="3">
         <f>SUM(January:December!B23)</f>
-        <v>313</v>
+        <v>641</v>
       </c>
       <c r="C23" s="3">
         <f>SUM(January:December!C23)</f>
-        <v>183</v>
+        <v>376</v>
       </c>
       <c r="D23" s="3">
         <f>SUM(January:December!D23)</f>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
       <c r="B24" s="2">
         <f>SUM(January:December!B24)</f>
-        <v>2530</v>
+        <v>5043</v>
       </c>
       <c r="C24" s="2">
         <f>SUM(January:December!C24)</f>
-        <v>445</v>
+        <v>836</v>
       </c>
       <c r="D24" s="2">
         <f>SUM(January:December!D24)</f>
-        <v>490</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
       <c r="B25" s="3">
         <f>SUM(January:December!B25)</f>
-        <v>11305</v>
+        <v>22295</v>
       </c>
       <c r="C25" s="3">
         <f>SUM(January:December!C25)</f>
-        <v>1184</v>
+        <v>2282</v>
       </c>
       <c r="D25" s="3">
         <f>SUM(January:December!D25)</f>
-        <v>1386</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2721</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B26" s="2">
         <f>SUM(January:December!B26)</f>
-        <v>578</v>
+        <v>1143</v>
       </c>
       <c r="C26" s="2">
         <f>SUM(January:December!C26)</f>
-        <v>253</v>
+        <v>484</v>
       </c>
       <c r="D26" s="2">
         <f>SUM(January:December!D26)</f>
-        <v>131</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -2531,531 +2531,531 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
       <c r="B28" s="2">
         <f>SUM(January:December!B28)</f>
-        <v>641</v>
+        <v>1164</v>
       </c>
       <c r="C28" s="2">
         <f>SUM(January:December!C28)</f>
-        <v>116</v>
+        <v>230</v>
       </c>
       <c r="D28" s="2">
         <f>SUM(January:December!D28)</f>
-        <v>153</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
       <c r="B29" s="3">
         <f>SUM(January:December!B29)</f>
-        <v>459</v>
+        <v>901</v>
       </c>
       <c r="C29" s="3">
         <f>SUM(January:December!C29)</f>
-        <v>103</v>
+        <v>210</v>
       </c>
       <c r="D29" s="3">
         <f>SUM(January:December!D29)</f>
-        <v>116</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
       <c r="B30" s="2">
         <f>SUM(January:December!B30)</f>
-        <v>2580</v>
+        <v>4956</v>
       </c>
       <c r="C30" s="2">
         <f>SUM(January:December!C30)</f>
-        <v>466</v>
+        <v>817</v>
       </c>
       <c r="D30" s="2">
         <f>SUM(January:December!D30)</f>
-        <v>641</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
       <c r="B31" s="3">
         <f>SUM(January:December!B31)</f>
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="C31" s="3">
         <f>SUM(January:December!C31)</f>
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D31" s="3">
         <f>SUM(January:December!D31)</f>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B32" s="2">
         <f>SUM(January:December!B32)</f>
-        <v>494</v>
+        <v>965</v>
       </c>
       <c r="C32" s="2">
         <f>SUM(January:December!C32)</f>
-        <v>186</v>
+        <v>401</v>
       </c>
       <c r="D32" s="2">
         <f>SUM(January:December!D32)</f>
-        <v>95</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
       <c r="B33" s="3">
         <f>SUM(January:December!B33)</f>
-        <v>1790</v>
+        <v>3307</v>
       </c>
       <c r="C33" s="3">
         <f>SUM(January:December!C33)</f>
-        <v>430</v>
+        <v>825</v>
       </c>
       <c r="D33" s="3">
         <f>SUM(January:December!D33)</f>
-        <v>408</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
       <c r="B34" s="2">
         <f>SUM(January:December!B34)</f>
-        <v>1061</v>
+        <v>2202</v>
       </c>
       <c r="C34" s="2">
         <f>SUM(January:December!C34)</f>
-        <v>310</v>
+        <v>520</v>
       </c>
       <c r="D34" s="2">
         <f>SUM(January:December!D34)</f>
-        <v>281</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
       <c r="B35" s="3">
         <f>SUM(January:December!B35)</f>
-        <v>645</v>
+        <v>1460</v>
       </c>
       <c r="C35" s="3">
         <f>SUM(January:December!C35)</f>
-        <v>86</v>
+        <v>191</v>
       </c>
       <c r="D35" s="3">
         <f>SUM(January:December!D35)</f>
-        <v>152</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
       <c r="B36" s="2">
         <f>SUM(January:December!B36)</f>
-        <v>6895</v>
+        <v>13304</v>
       </c>
       <c r="C36" s="2">
         <f>SUM(January:December!C36)</f>
-        <v>1269</v>
+        <v>2332</v>
       </c>
       <c r="D36" s="2">
         <f>SUM(January:December!D36)</f>
-        <v>818</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
       <c r="B37" s="3">
         <f>SUM(January:December!B37)</f>
-        <v>979</v>
+        <v>1895</v>
       </c>
       <c r="C37" s="3">
         <f>SUM(January:December!C37)</f>
-        <v>520</v>
+        <v>916</v>
       </c>
       <c r="D37" s="3">
         <f>SUM(January:December!D37)</f>
-        <v>157</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B38" s="2">
         <f>SUM(January:December!B38)</f>
-        <v>3290</v>
+        <v>6582</v>
       </c>
       <c r="C38" s="2">
         <f>SUM(January:December!C38)</f>
-        <v>322</v>
+        <v>645</v>
       </c>
       <c r="D38" s="2">
         <f>SUM(January:December!D38)</f>
-        <v>367</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
       <c r="B39" s="3">
         <f>SUM(January:December!B39)</f>
-        <v>187</v>
+        <v>381</v>
       </c>
       <c r="C39" s="3">
         <f>SUM(January:December!C39)</f>
-        <v>187</v>
+        <v>313</v>
       </c>
       <c r="D39" s="3">
         <f>SUM(January:December!D39)</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B40" s="6">
         <f>SUM(January:December!B40)</f>
-        <v>439</v>
+        <v>871</v>
       </c>
       <c r="C40" s="6">
         <f>SUM(January:December!C40)</f>
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="D40" s="6">
         <f>SUM(January:December!D40)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
       <c r="B41" s="7">
         <f>SUM(January:December!B41)</f>
-        <v>2327</v>
+        <v>4808</v>
       </c>
       <c r="C41" s="7">
         <f>SUM(January:December!C41)</f>
-        <v>114</v>
+        <v>246</v>
       </c>
       <c r="D41" s="7">
         <f>SUM(January:December!D41)</f>
-        <v>94</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
       <c r="B42" s="6">
         <f>SUM(January:December!B42)</f>
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="C42" s="6">
         <f>SUM(January:December!C42)</f>
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="D42" s="6">
         <f>SUM(January:December!D42)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
       <c r="B43" s="7">
         <f>SUM(January:December!B43)</f>
-        <v>310</v>
+        <v>647</v>
       </c>
       <c r="C43" s="7">
         <f>SUM(January:December!C43)</f>
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="D43" s="7">
         <f>SUM(January:December!D43)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B44" s="2">
         <f>SUM(January:December!B44)</f>
-        <v>345</v>
+        <v>619</v>
       </c>
       <c r="C44" s="2">
         <f>SUM(January:December!C44)</f>
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="D44" s="2">
         <f>SUM(January:December!D44)</f>
-        <v>228</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
       <c r="B45" s="3">
         <f>SUM(January:December!B45)</f>
-        <v>323</v>
+        <v>710</v>
       </c>
       <c r="C45" s="3">
         <f>SUM(January:December!C45)</f>
-        <v>143</v>
+        <v>292</v>
       </c>
       <c r="D45" s="3">
         <f>SUM(January:December!D45)</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
       <c r="B46" s="2">
         <f>SUM(January:December!B46)</f>
-        <v>1894</v>
+        <v>3515</v>
       </c>
       <c r="C46" s="2">
         <f>SUM(January:December!C46)</f>
-        <v>392</v>
+        <v>978</v>
       </c>
       <c r="D46" s="2">
         <f>SUM(January:December!D46)</f>
-        <v>432</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
       <c r="B47" s="3">
         <f>SUM(January:December!B47)</f>
-        <v>3565</v>
+        <v>6646</v>
       </c>
       <c r="C47" s="3">
         <f>SUM(January:December!C47)</f>
-        <v>646</v>
+        <v>1170</v>
       </c>
       <c r="D47" s="3">
         <f>SUM(January:December!D47)</f>
-        <v>779</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
       <c r="B48" s="2">
         <f>SUM(January:December!B48)</f>
-        <v>1357</v>
+        <v>2582</v>
       </c>
       <c r="C48" s="2">
         <f>SUM(January:December!C48)</f>
-        <v>493</v>
+        <v>884</v>
       </c>
       <c r="D48" s="2">
         <f>SUM(January:December!D48)</f>
-        <v>164</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
       <c r="B49" s="3">
         <f>SUM(January:December!B49)</f>
-        <v>902</v>
+        <v>1828</v>
       </c>
       <c r="C49" s="3">
         <f>SUM(January:December!C49)</f>
-        <v>271</v>
+        <v>495</v>
       </c>
       <c r="D49" s="3">
         <f>SUM(January:December!D49)</f>
-        <v>295</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B50" s="2">
         <f>SUM(January:December!B50)</f>
-        <v>3880</v>
+        <v>7668</v>
       </c>
       <c r="C50" s="2">
         <f>SUM(January:December!C50)</f>
-        <v>363</v>
+        <v>807</v>
       </c>
       <c r="D50" s="2">
         <f>SUM(January:December!D50)</f>
-        <v>745</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B51" s="3">
         <f>SUM(January:December!B51)</f>
-        <v>429</v>
+        <v>814</v>
       </c>
       <c r="C51" s="3">
         <f>SUM(January:December!C51)</f>
-        <v>142</v>
+        <v>285</v>
       </c>
       <c r="D51" s="3">
         <f>SUM(January:December!D51)</f>
-        <v>118</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
       <c r="B52" s="2">
         <f>SUM(January:December!B52)</f>
-        <v>1570</v>
+        <v>2809</v>
       </c>
       <c r="C52" s="2">
         <f>SUM(January:December!C52)</f>
-        <v>287</v>
+        <v>572</v>
       </c>
       <c r="D52" s="2">
         <f>SUM(January:December!D52)</f>
-        <v>547</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B53" s="3">
         <f>SUM(January:December!B53)</f>
-        <v>143</v>
+        <v>413</v>
       </c>
       <c r="C53" s="3">
         <f>SUM(January:December!C53)</f>
-        <v>191</v>
+        <v>340</v>
       </c>
       <c r="D53" s="3">
         <f>SUM(January:December!D53)</f>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
       <c r="B54" s="2">
         <f>SUM(January:December!B54)</f>
-        <v>209</v>
+        <v>467</v>
       </c>
       <c r="C54" s="2">
         <f>SUM(January:December!C54)</f>
-        <v>234</v>
+        <v>424</v>
       </c>
       <c r="D54" s="2">
         <f>SUM(January:December!D54)</f>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
       <c r="B55" s="3">
         <f>SUM(January:December!B55)</f>
-        <v>632</v>
+        <v>1304</v>
       </c>
       <c r="C55" s="3">
         <f>SUM(January:December!C55)</f>
-        <v>189</v>
+        <v>334</v>
       </c>
       <c r="D55" s="3">
         <f>SUM(January:December!D55)</f>
-        <v>261</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
       <c r="B56" s="4">
         <f>SUM(January:December!B56)</f>
-        <v>1293</v>
+        <v>2384</v>
       </c>
       <c r="C56" s="4">
         <f>SUM(January:December!C56)</f>
-        <v>600</v>
+        <v>1229</v>
       </c>
       <c r="D56" s="4">
         <f>SUM(January:December!D56)</f>
-        <v>229</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
       <c r="B57" s="7">
         <f>SUM(January:December!B57)</f>
-        <v>3129</v>
+        <v>6430</v>
       </c>
       <c r="C57" s="7">
         <f>SUM(January:December!C57)</f>
-        <v>186</v>
+        <v>431</v>
       </c>
       <c r="D57" s="7">
         <f>SUM(January:December!D57)</f>
-        <v>108</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
       <c r="B58" s="8">
         <f>SUM(January:December!B58)</f>
-        <v>86140</v>
+        <v>167420</v>
       </c>
       <c r="C58" s="8">
         <f>SUM(January:December!C58)</f>
-        <v>15198</v>
+        <v>28850</v>
       </c>
       <c r="D58" s="8">
         <f>SUM(January:December!D58)</f>
-        <v>14416</v>
+        <v>27951</v>
       </c>
     </row>
   </sheetData>
@@ -3553,13 +3553,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -3591,7 +3591,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -3599,7 +3599,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -3607,7 +3607,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -3615,7 +3615,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -3623,7 +3623,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -3631,7 +3631,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -3639,7 +3639,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -3647,7 +3647,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -3655,7 +3655,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -3663,7 +3663,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -3671,7 +3671,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -3679,7 +3679,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -3687,7 +3687,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -3695,7 +3695,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -3703,7 +3703,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -3711,7 +3711,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -3719,7 +3719,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -3727,7 +3727,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -3735,7 +3735,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -3743,7 +3743,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -3751,7 +3751,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -3759,7 +3759,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -3767,7 +3767,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -3775,7 +3775,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -3783,7 +3783,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -3791,7 +3791,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -3799,7 +3799,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -3807,7 +3807,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -3815,7 +3815,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -3823,7 +3823,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -3831,7 +3831,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -3839,7 +3839,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -3847,7 +3847,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -3855,7 +3855,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -3863,7 +3863,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -3871,7 +3871,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -3879,7 +3879,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -3887,7 +3887,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -3895,7 +3895,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -3903,7 +3903,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -3911,7 +3911,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -3919,7 +3919,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -3927,7 +3927,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -3935,7 +3935,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -3943,7 +3943,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -3951,7 +3951,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -3959,7 +3959,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -3967,7 +3967,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -3975,7 +3975,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -3983,7 +3983,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -3991,7 +3991,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -3999,7 +3999,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -4007,7 +4007,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -4015,7 +4015,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -4023,7 +4023,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -4040,13 +4040,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -4078,7 +4078,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -4086,7 +4086,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -4094,7 +4094,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -4102,7 +4102,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -4110,7 +4110,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -4118,7 +4118,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -4126,7 +4126,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -4134,7 +4134,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -4142,7 +4142,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -4150,7 +4150,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -4158,7 +4158,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -4166,7 +4166,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -4174,7 +4174,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -4182,7 +4182,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -4190,7 +4190,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -4198,7 +4198,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -4206,7 +4206,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -4214,7 +4214,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -4222,7 +4222,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -4230,7 +4230,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -4238,7 +4238,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -4246,7 +4246,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -4254,7 +4254,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -4262,7 +4262,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -4270,7 +4270,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -4278,7 +4278,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -4286,7 +4286,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -4294,7 +4294,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -4302,7 +4302,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -4310,7 +4310,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -4318,7 +4318,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -4326,7 +4326,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -4334,7 +4334,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -4342,7 +4342,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -4350,7 +4350,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -4358,7 +4358,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -4366,7 +4366,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -4374,7 +4374,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -4382,7 +4382,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -4390,7 +4390,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -4398,7 +4398,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -4406,7 +4406,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -4414,7 +4414,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -4422,7 +4422,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -4430,7 +4430,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -4438,7 +4438,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -4446,7 +4446,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -4454,7 +4454,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -4462,7 +4462,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -4470,7 +4470,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -4478,7 +4478,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -4486,7 +4486,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -4494,7 +4494,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -4502,7 +4502,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -4510,7 +4510,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -4527,13 +4527,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -4557,7 +4557,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -4565,7 +4565,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -4573,7 +4573,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -4581,7 +4581,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -4589,7 +4589,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -4597,7 +4597,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -4605,7 +4605,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -4613,7 +4613,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -4621,7 +4621,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -4629,7 +4629,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -4637,7 +4637,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -4645,7 +4645,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -4653,7 +4653,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -4661,7 +4661,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -4669,7 +4669,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -4677,7 +4677,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -4685,7 +4685,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -4693,7 +4693,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -4701,7 +4701,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -4709,7 +4709,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -4717,7 +4717,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -4725,7 +4725,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -4733,7 +4733,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -4741,7 +4741,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -4749,7 +4749,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -4757,7 +4757,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -4765,7 +4765,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -4773,7 +4773,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -4781,7 +4781,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -4789,7 +4789,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -4797,7 +4797,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -4805,7 +4805,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -4813,7 +4813,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -4821,7 +4821,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -4829,7 +4829,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -4837,7 +4837,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -4845,7 +4845,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -4853,7 +4853,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -4861,7 +4861,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -4869,7 +4869,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -4877,7 +4877,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -4885,7 +4885,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -4893,7 +4893,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -4901,7 +4901,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -4909,7 +4909,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -4917,7 +4917,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -4925,7 +4925,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -4933,7 +4933,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -4941,7 +4941,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -4949,7 +4949,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -4957,7 +4957,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -4965,7 +4965,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -4973,7 +4973,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -4981,7 +4981,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -4989,7 +4989,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -4997,7 +4997,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -5014,13 +5014,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -5044,7 +5044,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -5052,7 +5052,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -5060,7 +5060,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -5068,7 +5068,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -5076,7 +5076,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -5084,7 +5084,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -5092,7 +5092,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -5100,7 +5100,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -5108,7 +5108,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -5116,7 +5116,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -5124,7 +5124,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -5132,7 +5132,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -5140,7 +5140,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -5148,7 +5148,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -5156,7 +5156,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -5164,7 +5164,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -5172,7 +5172,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -5180,7 +5180,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -5188,7 +5188,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -5196,7 +5196,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -5204,7 +5204,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -5212,7 +5212,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -5220,7 +5220,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -5228,7 +5228,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -5236,7 +5236,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -5244,7 +5244,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -5252,7 +5252,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -5260,7 +5260,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -5268,7 +5268,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -5276,7 +5276,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -5284,7 +5284,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -5292,7 +5292,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -5300,7 +5300,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -5308,7 +5308,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -5316,7 +5316,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -5324,7 +5324,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -5332,7 +5332,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -5340,7 +5340,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -5348,7 +5348,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -5356,7 +5356,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -5364,7 +5364,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -5372,7 +5372,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -5380,7 +5380,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -5388,7 +5388,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -5396,7 +5396,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -5404,7 +5404,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -5412,7 +5412,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -5420,7 +5420,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -5428,7 +5428,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -5436,7 +5436,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -5444,7 +5444,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -5452,7 +5452,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -5460,7 +5460,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -5468,7 +5468,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -5476,7 +5476,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -5484,7 +5484,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -5500,13 +5500,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -5520,7 +5520,7 @@
         <v>46053</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -5534,7 +5534,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -5548,7 +5548,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -5562,7 +5562,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -5576,7 +5576,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -5590,7 +5590,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -5604,7 +5604,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -5618,7 +5618,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -5632,7 +5632,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -5646,7 +5646,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -5660,7 +5660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -5674,7 +5674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -5688,7 +5688,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -5702,7 +5702,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -5716,7 +5716,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -5730,7 +5730,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -5744,7 +5744,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -5758,7 +5758,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -5772,7 +5772,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -5786,7 +5786,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -5800,7 +5800,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -5814,7 +5814,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -5828,7 +5828,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -5842,7 +5842,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -5856,7 +5856,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -5870,7 +5870,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -5884,7 +5884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -5898,7 +5898,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -5912,7 +5912,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -5926,7 +5926,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -5940,7 +5940,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -5954,7 +5954,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -5968,7 +5968,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -5982,7 +5982,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -5996,7 +5996,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -6010,7 +6010,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -6024,7 +6024,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -6038,7 +6038,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -6052,7 +6052,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -6066,7 +6066,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -6080,7 +6080,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -6094,7 +6094,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -6108,7 +6108,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -6122,7 +6122,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -6136,7 +6136,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -6150,7 +6150,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -6178,7 +6178,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -6206,7 +6206,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -6220,7 +6220,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -6234,7 +6234,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -6248,7 +6248,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -6262,7 +6262,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -6276,7 +6276,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -6290,7 +6290,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -6304,7 +6304,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -6327,23 +6327,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="19"/>
+      <c r="B1" s="19">
+        <v>46054</v>
+      </c>
       <c r="C1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="21"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D1" s="21">
+        <v>46081</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -6357,453 +6361,789 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B3" s="3">
+        <v>5122</v>
+      </c>
+      <c r="C3" s="3">
+        <v>826</v>
+      </c>
+      <c r="D3" s="3">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>3066</v>
+      </c>
+      <c r="C4" s="2">
+        <v>285</v>
+      </c>
+      <c r="D4" s="2">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B5" s="3">
+        <v>8064</v>
+      </c>
+      <c r="C5" s="3">
+        <v>640</v>
+      </c>
+      <c r="D5" s="3">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>102</v>
+      </c>
+      <c r="C6" s="2">
+        <v>73</v>
+      </c>
+      <c r="D6" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="3">
+        <v>5650</v>
+      </c>
+      <c r="C7" s="3">
+        <v>804</v>
+      </c>
+      <c r="D7" s="3">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <v>897</v>
+      </c>
+      <c r="C8" s="2">
+        <v>126</v>
+      </c>
+      <c r="D8" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="3">
+        <v>598</v>
+      </c>
+      <c r="C9" s="3">
+        <v>126</v>
+      </c>
+      <c r="D9" s="3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
+        <v>225</v>
+      </c>
+      <c r="C10" s="2">
+        <v>47</v>
+      </c>
+      <c r="D10" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="3">
+        <v>44</v>
+      </c>
+      <c r="C11" s="3">
+        <v>20</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B13" s="4">
+        <v>18</v>
+      </c>
+      <c r="C13" s="4">
+        <v>42</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B14" s="5">
+        <v>125</v>
+      </c>
+      <c r="C14" s="5">
+        <v>158</v>
+      </c>
+      <c r="D14" s="5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B15" s="4">
+        <v>722</v>
+      </c>
+      <c r="C15" s="4">
+        <v>224</v>
+      </c>
+      <c r="D15" s="4">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B16" s="5">
+        <v>226</v>
+      </c>
+      <c r="C16" s="5">
+        <v>249</v>
+      </c>
+      <c r="D16" s="5">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B17" s="3">
+        <v>294</v>
+      </c>
+      <c r="C17" s="3">
+        <v>147</v>
+      </c>
+      <c r="D17" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B18" s="2">
+        <v>1798</v>
+      </c>
+      <c r="C18" s="2">
+        <v>322</v>
+      </c>
+      <c r="D18" s="2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="3">
+        <v>205</v>
+      </c>
+      <c r="C19" s="3">
+        <v>55</v>
+      </c>
+      <c r="D19" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="2">
+        <v>2346</v>
+      </c>
+      <c r="C20" s="2">
+        <v>264</v>
+      </c>
+      <c r="D20" s="2">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B21" s="3">
+        <v>32</v>
+      </c>
+      <c r="C21" s="3">
+        <v>39</v>
+      </c>
+      <c r="D21" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B22" s="2">
+        <v>1797</v>
+      </c>
+      <c r="C22" s="2">
+        <v>299</v>
+      </c>
+      <c r="D22" s="2">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B23" s="3">
+        <v>328</v>
+      </c>
+      <c r="C23" s="3">
+        <v>193</v>
+      </c>
+      <c r="D23" s="3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B24" s="2">
+        <v>2513</v>
+      </c>
+      <c r="C24" s="2">
+        <v>391</v>
+      </c>
+      <c r="D24" s="2">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B25" s="3">
+        <v>10990</v>
+      </c>
+      <c r="C25" s="3">
+        <v>1098</v>
+      </c>
+      <c r="D25" s="3">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B26" s="2">
+        <v>565</v>
+      </c>
+      <c r="C26" s="2">
+        <v>231</v>
+      </c>
+      <c r="D26" s="2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B27" s="3">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B28" s="2">
+        <v>523</v>
+      </c>
+      <c r="C28" s="2">
+        <v>114</v>
+      </c>
+      <c r="D28" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B29" s="3">
+        <v>442</v>
+      </c>
+      <c r="C29" s="3">
+        <v>107</v>
+      </c>
+      <c r="D29" s="3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B30" s="2">
+        <v>2376</v>
+      </c>
+      <c r="C30" s="2">
+        <v>351</v>
+      </c>
+      <c r="D30" s="2">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B31" s="3">
+        <v>30</v>
+      </c>
+      <c r="C31" s="3">
+        <v>15</v>
+      </c>
+      <c r="D31" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B32" s="2">
+        <v>471</v>
+      </c>
+      <c r="C32" s="2">
+        <v>215</v>
+      </c>
+      <c r="D32" s="2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B33" s="3">
+        <v>1517</v>
+      </c>
+      <c r="C33" s="3">
+        <v>395</v>
+      </c>
+      <c r="D33" s="3">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B34" s="2">
+        <v>1141</v>
+      </c>
+      <c r="C34" s="2">
+        <v>210</v>
+      </c>
+      <c r="D34" s="2">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B35" s="3">
+        <v>815</v>
+      </c>
+      <c r="C35" s="3">
+        <v>105</v>
+      </c>
+      <c r="D35" s="3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B36" s="2">
+        <v>6409</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1063</v>
+      </c>
+      <c r="D36" s="2">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B37" s="3">
+        <v>916</v>
+      </c>
+      <c r="C37" s="3">
+        <v>396</v>
+      </c>
+      <c r="D37" s="3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B38" s="2">
+        <v>3292</v>
+      </c>
+      <c r="C38" s="2">
+        <v>323</v>
+      </c>
+      <c r="D38" s="2">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B39" s="3">
+        <v>194</v>
+      </c>
+      <c r="C39" s="3">
+        <v>126</v>
+      </c>
+      <c r="D39" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B40" s="6">
+        <v>432</v>
+      </c>
+      <c r="C40" s="6">
+        <v>61</v>
+      </c>
+      <c r="D40" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B41" s="7">
+        <v>2481</v>
+      </c>
+      <c r="C41" s="7">
+        <v>132</v>
+      </c>
+      <c r="D41" s="7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B42" s="6">
+        <v>51</v>
+      </c>
+      <c r="C42" s="6">
+        <v>47</v>
+      </c>
+      <c r="D42" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B43" s="7">
+        <v>337</v>
+      </c>
+      <c r="C43" s="7">
+        <v>44</v>
+      </c>
+      <c r="D43" s="7">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B44" s="2">
+        <v>274</v>
+      </c>
+      <c r="C44" s="2">
+        <v>59</v>
+      </c>
+      <c r="D44" s="2">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B45" s="3">
+        <v>387</v>
+      </c>
+      <c r="C45" s="3">
+        <v>149</v>
+      </c>
+      <c r="D45" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B46" s="2">
+        <v>1621</v>
+      </c>
+      <c r="C46" s="2">
+        <v>586</v>
+      </c>
+      <c r="D46" s="2">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B47" s="3">
+        <v>3081</v>
+      </c>
+      <c r="C47" s="3">
+        <v>524</v>
+      </c>
+      <c r="D47" s="3">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B48" s="2">
+        <v>1225</v>
+      </c>
+      <c r="C48" s="2">
+        <v>391</v>
+      </c>
+      <c r="D48" s="2">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B49" s="3">
+        <v>926</v>
+      </c>
+      <c r="C49" s="3">
+        <v>224</v>
+      </c>
+      <c r="D49" s="3">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B50" s="2">
+        <v>3788</v>
+      </c>
+      <c r="C50" s="2">
+        <v>444</v>
+      </c>
+      <c r="D50" s="2">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B51" s="3">
+        <v>385</v>
+      </c>
+      <c r="C51" s="3">
+        <v>143</v>
+      </c>
+      <c r="D51" s="3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B52" s="2">
+        <v>1239</v>
+      </c>
+      <c r="C52" s="2">
+        <v>285</v>
+      </c>
+      <c r="D52" s="2">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B53" s="3">
+        <v>270</v>
+      </c>
+      <c r="C53" s="3">
+        <v>149</v>
+      </c>
+      <c r="D53" s="3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B54" s="2">
+        <v>258</v>
+      </c>
+      <c r="C54" s="2">
+        <v>190</v>
+      </c>
+      <c r="D54" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B55" s="3">
+        <v>672</v>
+      </c>
+      <c r="C55" s="3">
+        <v>145</v>
+      </c>
+      <c r="D55" s="3">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B56" s="4">
+        <v>1091</v>
+      </c>
+      <c r="C56" s="4">
+        <v>629</v>
+      </c>
+      <c r="D56" s="4">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B57" s="7">
+        <v>3301</v>
+      </c>
+      <c r="C57" s="7">
+        <v>245</v>
+      </c>
+      <c r="D57" s="7">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
+      <c r="B58" s="8">
+        <v>81280</v>
+      </c>
+      <c r="C58" s="8">
+        <v>13652</v>
+      </c>
+      <c r="D58" s="8">
+        <v>13535</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:D2" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
@@ -6814,13 +7154,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -6830,7 +7170,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -6844,7 +7184,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -6852,7 +7192,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -6860,7 +7200,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -6868,7 +7208,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -6876,7 +7216,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -6884,7 +7224,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -6892,7 +7232,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -6900,7 +7240,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -6908,7 +7248,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -6916,7 +7256,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -6924,7 +7264,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -6932,7 +7272,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -6940,7 +7280,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -6948,7 +7288,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -6956,7 +7296,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -6964,7 +7304,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -6972,7 +7312,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -6980,7 +7320,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -6988,7 +7328,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -6996,7 +7336,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -7004,7 +7344,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -7012,7 +7352,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -7020,7 +7360,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -7028,7 +7368,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -7036,7 +7376,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -7044,7 +7384,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -7052,7 +7392,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -7060,7 +7400,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -7068,7 +7408,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -7076,7 +7416,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -7084,7 +7424,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -7092,7 +7432,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -7100,7 +7440,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -7108,7 +7448,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -7116,7 +7456,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -7124,7 +7464,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -7132,7 +7472,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -7140,7 +7480,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -7148,7 +7488,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -7156,7 +7496,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -7164,7 +7504,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -7172,7 +7512,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -7180,7 +7520,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -7188,7 +7528,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -7196,7 +7536,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -7204,7 +7544,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -7212,7 +7552,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -7220,7 +7560,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -7228,7 +7568,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -7236,7 +7576,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -7244,7 +7584,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -7252,7 +7592,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -7260,7 +7600,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -7268,7 +7608,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -7276,7 +7616,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -7284,7 +7624,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -7301,13 +7641,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -7317,7 +7657,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -7331,7 +7671,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -7339,7 +7679,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -7347,7 +7687,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -7355,7 +7695,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -7363,7 +7703,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -7371,7 +7711,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -7379,7 +7719,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -7387,7 +7727,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -7395,7 +7735,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -7403,7 +7743,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -7411,7 +7751,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -7419,7 +7759,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -7427,7 +7767,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -7435,7 +7775,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -7443,7 +7783,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -7451,7 +7791,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -7459,7 +7799,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -7467,7 +7807,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -7475,7 +7815,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -7483,7 +7823,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -7491,7 +7831,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -7499,7 +7839,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -7507,7 +7847,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -7515,7 +7855,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -7523,7 +7863,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -7531,7 +7871,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -7539,7 +7879,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -7547,7 +7887,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -7555,7 +7895,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -7563,7 +7903,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -7571,7 +7911,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -7579,7 +7919,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -7587,7 +7927,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -7595,7 +7935,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -7603,7 +7943,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -7611,7 +7951,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -7619,7 +7959,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -7627,7 +7967,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -7635,7 +7975,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -7643,7 +7983,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -7651,7 +7991,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -7659,7 +7999,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -7667,7 +8007,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -7675,7 +8015,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -7683,7 +8023,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -7691,7 +8031,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -7699,7 +8039,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -7707,7 +8047,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -7715,7 +8055,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -7723,7 +8063,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -7731,7 +8071,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -7739,7 +8079,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -7747,7 +8087,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -7755,7 +8095,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -7763,7 +8103,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -7771,7 +8111,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -7788,13 +8128,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -7804,7 +8144,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -7818,7 +8158,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -7826,7 +8166,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -7834,7 +8174,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -7842,7 +8182,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -7850,7 +8190,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -7858,7 +8198,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -7866,7 +8206,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -7874,7 +8214,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -7882,7 +8222,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -7890,7 +8230,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -7898,7 +8238,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -7906,7 +8246,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -7914,7 +8254,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -7922,7 +8262,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -7930,7 +8270,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -7938,7 +8278,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -7946,7 +8286,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -7954,7 +8294,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -7962,7 +8302,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -7970,7 +8310,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -7978,7 +8318,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -7986,7 +8326,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -7994,7 +8334,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -8002,7 +8342,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -8010,7 +8350,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -8018,7 +8358,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -8026,7 +8366,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -8034,7 +8374,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -8042,7 +8382,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -8050,7 +8390,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -8058,7 +8398,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -8066,7 +8406,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -8074,7 +8414,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -8082,7 +8422,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -8090,7 +8430,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -8098,7 +8438,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -8106,7 +8446,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -8114,7 +8454,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -8122,7 +8462,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -8130,7 +8470,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -8138,7 +8478,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -8146,7 +8486,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -8154,7 +8494,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -8162,7 +8502,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -8170,7 +8510,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -8178,7 +8518,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -8186,7 +8526,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -8194,7 +8534,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -8202,7 +8542,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -8210,7 +8550,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -8218,7 +8558,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -8226,7 +8566,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -8234,7 +8574,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -8242,7 +8582,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -8250,7 +8590,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -8258,7 +8598,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -8275,13 +8615,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -8291,7 +8631,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -8305,7 +8645,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -8313,7 +8653,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -8321,7 +8661,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -8329,7 +8669,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -8337,7 +8677,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -8345,7 +8685,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -8353,7 +8693,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -8361,7 +8701,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -8369,7 +8709,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -8377,7 +8717,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -8385,7 +8725,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -8393,7 +8733,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -8401,7 +8741,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -8409,7 +8749,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -8417,7 +8757,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -8425,7 +8765,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -8433,7 +8773,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -8441,7 +8781,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -8449,7 +8789,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -8457,7 +8797,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -8465,7 +8805,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -8473,7 +8813,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -8481,7 +8821,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -8489,7 +8829,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -8497,7 +8837,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -8505,7 +8845,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -8513,7 +8853,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -8521,7 +8861,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -8529,7 +8869,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -8537,7 +8877,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -8545,7 +8885,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -8553,7 +8893,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -8561,7 +8901,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -8569,7 +8909,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -8577,7 +8917,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -8585,7 +8925,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -8593,7 +8933,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -8601,7 +8941,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -8609,7 +8949,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -8617,7 +8957,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -8625,7 +8965,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -8633,7 +8973,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -8641,7 +8981,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -8649,7 +8989,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -8657,7 +8997,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -8665,7 +9005,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -8673,7 +9013,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -8681,7 +9021,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -8689,7 +9029,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -8697,7 +9037,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -8705,7 +9045,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -8713,7 +9053,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -8721,7 +9061,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -8729,7 +9069,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -8737,7 +9077,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -8745,7 +9085,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -8762,13 +9102,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -8778,7 +9118,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -8792,7 +9132,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -8800,7 +9140,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -8808,7 +9148,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -8816,7 +9156,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -8824,7 +9164,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -8832,7 +9172,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -8840,7 +9180,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -8848,7 +9188,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -8856,7 +9196,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -8864,7 +9204,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -8872,7 +9212,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -8880,7 +9220,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -8888,7 +9228,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -8896,7 +9236,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -8904,7 +9244,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -8912,7 +9252,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -8920,7 +9260,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -8928,7 +9268,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -8936,7 +9276,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -8944,7 +9284,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -8952,7 +9292,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -8960,7 +9300,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -8968,7 +9308,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -8976,7 +9316,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -8984,7 +9324,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -8992,7 +9332,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -9000,7 +9340,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -9008,7 +9348,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -9016,7 +9356,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -9024,7 +9364,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -9032,7 +9372,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -9040,7 +9380,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -9048,7 +9388,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -9056,7 +9396,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -9064,7 +9404,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -9072,7 +9412,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -9080,7 +9420,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -9088,7 +9428,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -9096,7 +9436,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -9104,7 +9444,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -9112,7 +9452,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -9120,7 +9460,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -9128,7 +9468,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -9136,7 +9476,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -9144,7 +9484,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -9152,7 +9492,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -9160,7 +9500,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -9168,7 +9508,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -9176,7 +9516,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -9184,7 +9524,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -9192,7 +9532,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -9200,7 +9540,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -9208,7 +9548,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -9216,7 +9556,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -9224,7 +9564,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -9232,7 +9572,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -9249,13 +9589,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -9265,7 +9605,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -9279,7 +9619,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -9287,7 +9627,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -9295,7 +9635,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -9303,7 +9643,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -9311,7 +9651,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -9319,7 +9659,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -9327,7 +9667,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -9335,7 +9675,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -9343,7 +9683,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -9351,7 +9691,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -9359,7 +9699,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -9367,7 +9707,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -9375,7 +9715,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -9383,7 +9723,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -9391,7 +9731,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -9399,7 +9739,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -9407,7 +9747,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -9415,7 +9755,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -9423,7 +9763,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -9431,7 +9771,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -9439,7 +9779,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -9447,7 +9787,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -9455,7 +9795,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -9463,7 +9803,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -9471,7 +9811,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -9479,7 +9819,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -9487,7 +9827,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -9495,7 +9835,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -9503,7 +9843,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -9511,7 +9851,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -9519,7 +9859,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -9527,7 +9867,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -9535,7 +9875,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -9543,7 +9883,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -9551,7 +9891,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -9559,7 +9899,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -9567,7 +9907,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -9575,7 +9915,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -9583,7 +9923,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -9591,7 +9931,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -9599,7 +9939,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -9607,7 +9947,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -9615,7 +9955,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -9623,7 +9963,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -9631,7 +9971,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -9639,7 +9979,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -9647,7 +9987,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -9655,7 +9995,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -9663,7 +10003,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -9671,7 +10011,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -9679,7 +10019,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -9687,7 +10027,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -9695,7 +10035,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -9703,7 +10043,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -9711,7 +10051,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -9719,7 +10059,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>

--- a/statistics_files/nekls_executive_board/2026/2026_next_statistics.xlsx
+++ b/statistics_files/nekls_executive_board/2026/2026_next_statistics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\nekls_executive_board\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{493527C4-8022-4CFA-A9E1-A65C5F5685B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C250E64-926A-495B-B3A5-4278E71BF5D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="62">
   <si>
     <t>Library</t>
   </si>
@@ -253,8 +253,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="mmmm\ d\,\ yyyy"/>
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -833,7 +834,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -882,6 +883,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="37" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="38" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2089,7 +2093,7 @@
       </c>
       <c r="D1" s="21">
         <f>MAX(January:December!D1)</f>
-        <v>46081</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2112,15 +2116,15 @@
       </c>
       <c r="B3" s="3">
         <f>SUM(January:December!B3)</f>
-        <v>10785</v>
+        <v>16625</v>
       </c>
       <c r="C3" s="3">
         <f>SUM(January:December!C3)</f>
-        <v>1799</v>
+        <v>2743</v>
       </c>
       <c r="D3" s="3">
         <f>SUM(January:December!D3)</f>
-        <v>2085</v>
+        <v>3173</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2129,15 +2133,15 @@
       </c>
       <c r="B4" s="2">
         <f>SUM(January:December!B4)</f>
-        <v>6321</v>
+        <v>9724</v>
       </c>
       <c r="C4" s="2">
         <f>SUM(January:December!C4)</f>
-        <v>572</v>
+        <v>910</v>
       </c>
       <c r="D4" s="2">
         <f>SUM(January:December!D4)</f>
-        <v>1047</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2146,15 +2150,15 @@
       </c>
       <c r="B5" s="3">
         <f>SUM(January:December!B5)</f>
-        <v>17219</v>
+        <v>26706</v>
       </c>
       <c r="C5" s="3">
         <f>SUM(January:December!C5)</f>
-        <v>1562</v>
+        <v>2389</v>
       </c>
       <c r="D5" s="3">
         <f>SUM(January:December!D5)</f>
-        <v>1721</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2163,15 +2167,15 @@
       </c>
       <c r="B6" s="2">
         <f>SUM(January:December!B6)</f>
-        <v>191</v>
+        <v>278</v>
       </c>
       <c r="C6" s="2">
         <f>SUM(January:December!C6)</f>
-        <v>184</v>
+        <v>253</v>
       </c>
       <c r="D6" s="2">
         <f>SUM(January:December!D6)</f>
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2180,15 +2184,15 @@
       </c>
       <c r="B7" s="3">
         <f>SUM(January:December!B7)</f>
-        <v>11922</v>
+        <v>18212</v>
       </c>
       <c r="C7" s="3">
         <f>SUM(January:December!C7)</f>
-        <v>1698</v>
+        <v>2545</v>
       </c>
       <c r="D7" s="3">
         <f>SUM(January:December!D7)</f>
-        <v>1619</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2197,15 +2201,15 @@
       </c>
       <c r="B8" s="2">
         <f>SUM(January:December!B8)</f>
-        <v>1959</v>
+        <v>2668</v>
       </c>
       <c r="C8" s="2">
         <f>SUM(January:December!C8)</f>
-        <v>277</v>
+        <v>428</v>
       </c>
       <c r="D8" s="2">
         <f>SUM(January:December!D8)</f>
-        <v>222</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2214,15 +2218,15 @@
       </c>
       <c r="B9" s="3">
         <f>SUM(January:December!B9)</f>
-        <v>1083</v>
+        <v>1638</v>
       </c>
       <c r="C9" s="3">
         <f>SUM(January:December!C9)</f>
-        <v>286</v>
+        <v>401</v>
       </c>
       <c r="D9" s="3">
         <f>SUM(January:December!D9)</f>
-        <v>210</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2231,15 +2235,15 @@
       </c>
       <c r="B10" s="2">
         <f>SUM(January:December!B10)</f>
-        <v>476</v>
+        <v>702</v>
       </c>
       <c r="C10" s="2">
         <f>SUM(January:December!C10)</f>
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="D10" s="2">
         <f>SUM(January:December!D10)</f>
-        <v>35</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2248,11 +2252,11 @@
       </c>
       <c r="B11" s="3">
         <f>SUM(January:December!B11)</f>
-        <v>97</v>
+        <v>143</v>
       </c>
       <c r="C11" s="3">
         <f>SUM(January:December!C11)</f>
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="D11" s="3">
         <f>SUM(January:December!D11)</f>
@@ -2282,15 +2286,15 @@
       </c>
       <c r="B13" s="4">
         <f>SUM(January:December!B13)</f>
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="C13" s="4">
         <f>SUM(January:December!C13)</f>
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="D13" s="4">
         <f>SUM(January:December!D13)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2299,15 +2303,15 @@
       </c>
       <c r="B14" s="5">
         <f>SUM(January:December!B14)</f>
-        <v>275</v>
+        <v>489</v>
       </c>
       <c r="C14" s="5">
         <f>SUM(January:December!C14)</f>
-        <v>258</v>
+        <v>348</v>
       </c>
       <c r="D14" s="5">
         <f>SUM(January:December!D14)</f>
-        <v>109</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2316,15 +2320,15 @@
       </c>
       <c r="B15" s="4">
         <f>SUM(January:December!B15)</f>
-        <v>1467</v>
+        <v>2276</v>
       </c>
       <c r="C15" s="4">
         <f>SUM(January:December!C15)</f>
-        <v>433</v>
+        <v>697</v>
       </c>
       <c r="D15" s="4">
         <f>SUM(January:December!D15)</f>
-        <v>308</v>
+        <v>446</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2333,15 +2337,15 @@
       </c>
       <c r="B16" s="5">
         <f>SUM(January:December!B16)</f>
-        <v>596</v>
+        <v>924</v>
       </c>
       <c r="C16" s="5">
         <f>SUM(January:December!C16)</f>
-        <v>558</v>
+        <v>747</v>
       </c>
       <c r="D16" s="5">
         <f>SUM(January:December!D16)</f>
-        <v>103</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2350,15 +2354,15 @@
       </c>
       <c r="B17" s="3">
         <f>SUM(January:December!B17)</f>
-        <v>540</v>
+        <v>844</v>
       </c>
       <c r="C17" s="3">
         <f>SUM(January:December!C17)</f>
-        <v>326</v>
+        <v>445</v>
       </c>
       <c r="D17" s="3">
         <f>SUM(January:December!D17)</f>
-        <v>87</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2367,15 +2371,15 @@
       </c>
       <c r="B18" s="2">
         <f>SUM(January:December!B18)</f>
-        <v>3696</v>
+        <v>5730</v>
       </c>
       <c r="C18" s="2">
         <f>SUM(January:December!C18)</f>
-        <v>716</v>
+        <v>1077</v>
       </c>
       <c r="D18" s="2">
         <f>SUM(January:December!D18)</f>
-        <v>987</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2384,15 +2388,15 @@
       </c>
       <c r="B19" s="3">
         <f>SUM(January:December!B19)</f>
-        <v>384</v>
+        <v>561</v>
       </c>
       <c r="C19" s="3">
         <f>SUM(January:December!C19)</f>
-        <v>128</v>
+        <v>201</v>
       </c>
       <c r="D19" s="3">
         <f>SUM(January:December!D19)</f>
-        <v>80</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2401,15 +2405,15 @@
       </c>
       <c r="B20" s="2">
         <f>SUM(January:December!B20)</f>
-        <v>4378</v>
+        <v>6411</v>
       </c>
       <c r="C20" s="2">
         <f>SUM(January:December!C20)</f>
-        <v>464</v>
+        <v>703</v>
       </c>
       <c r="D20" s="2">
         <f>SUM(January:December!D20)</f>
-        <v>914</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2418,11 +2422,11 @@
       </c>
       <c r="B21" s="3">
         <f>SUM(January:December!B21)</f>
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="C21" s="3">
         <f>SUM(January:December!C21)</f>
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="D21" s="3">
         <f>SUM(January:December!D21)</f>
@@ -2435,15 +2439,15 @@
       </c>
       <c r="B22" s="2">
         <f>SUM(January:December!B22)</f>
-        <v>3815</v>
+        <v>5969</v>
       </c>
       <c r="C22" s="2">
         <f>SUM(January:December!C22)</f>
-        <v>654</v>
+        <v>994</v>
       </c>
       <c r="D22" s="2">
         <f>SUM(January:December!D22)</f>
-        <v>811</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2452,15 +2456,15 @@
       </c>
       <c r="B23" s="3">
         <f>SUM(January:December!B23)</f>
-        <v>641</v>
+        <v>977</v>
       </c>
       <c r="C23" s="3">
         <f>SUM(January:December!C23)</f>
-        <v>376</v>
+        <v>572</v>
       </c>
       <c r="D23" s="3">
         <f>SUM(January:December!D23)</f>
-        <v>143</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2469,15 +2473,15 @@
       </c>
       <c r="B24" s="2">
         <f>SUM(January:December!B24)</f>
-        <v>5043</v>
+        <v>8276</v>
       </c>
       <c r="C24" s="2">
         <f>SUM(January:December!C24)</f>
-        <v>836</v>
+        <v>1306</v>
       </c>
       <c r="D24" s="2">
         <f>SUM(January:December!D24)</f>
-        <v>939</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2486,15 +2490,15 @@
       </c>
       <c r="B25" s="3">
         <f>SUM(January:December!B25)</f>
-        <v>22295</v>
+        <v>34372</v>
       </c>
       <c r="C25" s="3">
         <f>SUM(January:December!C25)</f>
-        <v>2282</v>
+        <v>3277</v>
       </c>
       <c r="D25" s="3">
         <f>SUM(January:December!D25)</f>
-        <v>2721</v>
+        <v>3897</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2503,15 +2507,15 @@
       </c>
       <c r="B26" s="2">
         <f>SUM(January:December!B26)</f>
-        <v>1143</v>
+        <v>1680</v>
       </c>
       <c r="C26" s="2">
         <f>SUM(January:December!C26)</f>
-        <v>484</v>
+        <v>761</v>
       </c>
       <c r="D26" s="2">
         <f>SUM(January:December!D26)</f>
-        <v>253</v>
+        <v>360</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2537,15 +2541,15 @@
       </c>
       <c r="B28" s="2">
         <f>SUM(January:December!B28)</f>
-        <v>1164</v>
+        <v>1783</v>
       </c>
       <c r="C28" s="2">
         <f>SUM(January:December!C28)</f>
-        <v>230</v>
+        <v>387</v>
       </c>
       <c r="D28" s="2">
         <f>SUM(January:December!D28)</f>
-        <v>263</v>
+        <v>395</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2554,15 +2558,15 @@
       </c>
       <c r="B29" s="3">
         <f>SUM(January:December!B29)</f>
-        <v>901</v>
+        <v>1370</v>
       </c>
       <c r="C29" s="3">
         <f>SUM(January:December!C29)</f>
-        <v>210</v>
+        <v>287</v>
       </c>
       <c r="D29" s="3">
         <f>SUM(January:December!D29)</f>
-        <v>214</v>
+        <v>361</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2571,15 +2575,15 @@
       </c>
       <c r="B30" s="2">
         <f>SUM(January:December!B30)</f>
-        <v>4956</v>
+        <v>7504</v>
       </c>
       <c r="C30" s="2">
         <f>SUM(January:December!C30)</f>
-        <v>817</v>
+        <v>1205</v>
       </c>
       <c r="D30" s="2">
         <f>SUM(January:December!D30)</f>
-        <v>1115</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2588,15 +2592,15 @@
       </c>
       <c r="B31" s="3">
         <f>SUM(January:December!B31)</f>
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="C31" s="3">
         <f>SUM(January:December!C31)</f>
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D31" s="3">
         <f>SUM(January:December!D31)</f>
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2605,15 +2609,15 @@
       </c>
       <c r="B32" s="2">
         <f>SUM(January:December!B32)</f>
-        <v>965</v>
+        <v>1446</v>
       </c>
       <c r="C32" s="2">
         <f>SUM(January:December!C32)</f>
-        <v>401</v>
+        <v>604</v>
       </c>
       <c r="D32" s="2">
         <f>SUM(January:December!D32)</f>
-        <v>226</v>
+        <v>331</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -2622,15 +2626,15 @@
       </c>
       <c r="B33" s="3">
         <f>SUM(January:December!B33)</f>
-        <v>3307</v>
+        <v>4953</v>
       </c>
       <c r="C33" s="3">
         <f>SUM(January:December!C33)</f>
-        <v>825</v>
+        <v>1280</v>
       </c>
       <c r="D33" s="3">
         <f>SUM(January:December!D33)</f>
-        <v>743</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2639,15 +2643,15 @@
       </c>
       <c r="B34" s="2">
         <f>SUM(January:December!B34)</f>
-        <v>2202</v>
+        <v>3394</v>
       </c>
       <c r="C34" s="2">
         <f>SUM(January:December!C34)</f>
-        <v>520</v>
+        <v>754</v>
       </c>
       <c r="D34" s="2">
         <f>SUM(January:December!D34)</f>
-        <v>554</v>
+        <v>818</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2656,15 +2660,15 @@
       </c>
       <c r="B35" s="3">
         <f>SUM(January:December!B35)</f>
-        <v>1460</v>
+        <v>1948</v>
       </c>
       <c r="C35" s="3">
         <f>SUM(January:December!C35)</f>
-        <v>191</v>
+        <v>289</v>
       </c>
       <c r="D35" s="3">
         <f>SUM(January:December!D35)</f>
-        <v>282</v>
+        <v>389</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2673,15 +2677,15 @@
       </c>
       <c r="B36" s="2">
         <f>SUM(January:December!B36)</f>
-        <v>13304</v>
+        <v>19380</v>
       </c>
       <c r="C36" s="2">
         <f>SUM(January:December!C36)</f>
-        <v>2332</v>
+        <v>3454</v>
       </c>
       <c r="D36" s="2">
         <f>SUM(January:December!D36)</f>
-        <v>1643</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2690,15 +2694,15 @@
       </c>
       <c r="B37" s="3">
         <f>SUM(January:December!B37)</f>
-        <v>1895</v>
+        <v>2770</v>
       </c>
       <c r="C37" s="3">
         <f>SUM(January:December!C37)</f>
-        <v>916</v>
+        <v>1384</v>
       </c>
       <c r="D37" s="3">
         <f>SUM(January:December!D37)</f>
-        <v>301</v>
+        <v>430</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2707,15 +2711,15 @@
       </c>
       <c r="B38" s="2">
         <f>SUM(January:December!B38)</f>
-        <v>6582</v>
+        <v>10436</v>
       </c>
       <c r="C38" s="2">
         <f>SUM(January:December!C38)</f>
-        <v>645</v>
+        <v>969</v>
       </c>
       <c r="D38" s="2">
         <f>SUM(January:December!D38)</f>
-        <v>755</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2724,15 +2728,15 @@
       </c>
       <c r="B39" s="3">
         <f>SUM(January:December!B39)</f>
-        <v>381</v>
+        <v>614</v>
       </c>
       <c r="C39" s="3">
         <f>SUM(January:December!C39)</f>
-        <v>313</v>
+        <v>465</v>
       </c>
       <c r="D39" s="3">
         <f>SUM(January:December!D39)</f>
-        <v>59</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2741,15 +2745,15 @@
       </c>
       <c r="B40" s="6">
         <f>SUM(January:December!B40)</f>
-        <v>871</v>
+        <v>1347</v>
       </c>
       <c r="C40" s="6">
         <f>SUM(January:December!C40)</f>
-        <v>122</v>
+        <v>234</v>
       </c>
       <c r="D40" s="6">
         <f>SUM(January:December!D40)</f>
-        <v>34</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2758,15 +2762,15 @@
       </c>
       <c r="B41" s="7">
         <f>SUM(January:December!B41)</f>
-        <v>4808</v>
+        <v>6943</v>
       </c>
       <c r="C41" s="7">
         <f>SUM(January:December!C41)</f>
-        <v>246</v>
+        <v>327</v>
       </c>
       <c r="D41" s="7">
         <f>SUM(January:December!D41)</f>
-        <v>215</v>
+        <v>331</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2775,15 +2779,15 @@
       </c>
       <c r="B42" s="6">
         <f>SUM(January:December!B42)</f>
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="C42" s="6">
         <f>SUM(January:December!C42)</f>
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="D42" s="6">
         <f>SUM(January:December!D42)</f>
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2792,15 +2796,15 @@
       </c>
       <c r="B43" s="7">
         <f>SUM(January:December!B43)</f>
-        <v>647</v>
+        <v>898</v>
       </c>
       <c r="C43" s="7">
         <f>SUM(January:December!C43)</f>
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="D43" s="7">
         <f>SUM(January:December!D43)</f>
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2809,15 +2813,15 @@
       </c>
       <c r="B44" s="2">
         <f>SUM(January:December!B44)</f>
-        <v>619</v>
+        <v>857</v>
       </c>
       <c r="C44" s="2">
         <f>SUM(January:December!C44)</f>
-        <v>148</v>
+        <v>236</v>
       </c>
       <c r="D44" s="2">
         <f>SUM(January:December!D44)</f>
-        <v>483</v>
+        <v>566</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2826,15 +2830,15 @@
       </c>
       <c r="B45" s="3">
         <f>SUM(January:December!B45)</f>
-        <v>710</v>
+        <v>1121</v>
       </c>
       <c r="C45" s="3">
         <f>SUM(January:December!C45)</f>
-        <v>292</v>
+        <v>462</v>
       </c>
       <c r="D45" s="3">
         <f>SUM(January:December!D45)</f>
-        <v>73</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2843,15 +2847,15 @@
       </c>
       <c r="B46" s="2">
         <f>SUM(January:December!B46)</f>
-        <v>3515</v>
+        <v>5375</v>
       </c>
       <c r="C46" s="2">
         <f>SUM(January:December!C46)</f>
-        <v>978</v>
+        <v>1431</v>
       </c>
       <c r="D46" s="2">
         <f>SUM(January:December!D46)</f>
-        <v>790</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2860,15 +2864,15 @@
       </c>
       <c r="B47" s="3">
         <f>SUM(January:December!B47)</f>
-        <v>6646</v>
+        <v>10185</v>
       </c>
       <c r="C47" s="3">
         <f>SUM(January:December!C47)</f>
-        <v>1170</v>
+        <v>1730</v>
       </c>
       <c r="D47" s="3">
         <f>SUM(January:December!D47)</f>
-        <v>1348</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2877,15 +2881,15 @@
       </c>
       <c r="B48" s="2">
         <f>SUM(January:December!B48)</f>
-        <v>2582</v>
+        <v>4160</v>
       </c>
       <c r="C48" s="2">
         <f>SUM(January:December!C48)</f>
-        <v>884</v>
+        <v>1335</v>
       </c>
       <c r="D48" s="2">
         <f>SUM(January:December!D48)</f>
-        <v>353</v>
+        <v>549</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -2894,15 +2898,15 @@
       </c>
       <c r="B49" s="3">
         <f>SUM(January:December!B49)</f>
-        <v>1828</v>
+        <v>2911</v>
       </c>
       <c r="C49" s="3">
         <f>SUM(January:December!C49)</f>
-        <v>495</v>
+        <v>691</v>
       </c>
       <c r="D49" s="3">
         <f>SUM(January:December!D49)</f>
-        <v>592</v>
+        <v>848</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2911,15 +2915,15 @@
       </c>
       <c r="B50" s="2">
         <f>SUM(January:December!B50)</f>
-        <v>7668</v>
+        <v>11766</v>
       </c>
       <c r="C50" s="2">
         <f>SUM(January:December!C50)</f>
-        <v>807</v>
+        <v>1261</v>
       </c>
       <c r="D50" s="2">
         <f>SUM(January:December!D50)</f>
-        <v>1309</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -2928,15 +2932,15 @@
       </c>
       <c r="B51" s="3">
         <f>SUM(January:December!B51)</f>
-        <v>814</v>
+        <v>1334</v>
       </c>
       <c r="C51" s="3">
         <f>SUM(January:December!C51)</f>
-        <v>285</v>
+        <v>397</v>
       </c>
       <c r="D51" s="3">
         <f>SUM(January:December!D51)</f>
-        <v>212</v>
+        <v>367</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -2945,15 +2949,15 @@
       </c>
       <c r="B52" s="2">
         <f>SUM(January:December!B52)</f>
-        <v>2809</v>
+        <v>4259</v>
       </c>
       <c r="C52" s="2">
         <f>SUM(January:December!C52)</f>
-        <v>572</v>
+        <v>856</v>
       </c>
       <c r="D52" s="2">
         <f>SUM(January:December!D52)</f>
-        <v>1003</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -2962,15 +2966,15 @@
       </c>
       <c r="B53" s="3">
         <f>SUM(January:December!B53)</f>
-        <v>413</v>
+        <v>649</v>
       </c>
       <c r="C53" s="3">
         <f>SUM(January:December!C53)</f>
-        <v>340</v>
+        <v>546</v>
       </c>
       <c r="D53" s="3">
         <f>SUM(January:December!D53)</f>
-        <v>198</v>
+        <v>290</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -2979,15 +2983,15 @@
       </c>
       <c r="B54" s="2">
         <f>SUM(January:December!B54)</f>
-        <v>467</v>
+        <v>673</v>
       </c>
       <c r="C54" s="2">
         <f>SUM(January:December!C54)</f>
-        <v>424</v>
+        <v>605</v>
       </c>
       <c r="D54" s="2">
         <f>SUM(January:December!D54)</f>
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -2996,15 +3000,15 @@
       </c>
       <c r="B55" s="3">
         <f>SUM(January:December!B55)</f>
-        <v>1304</v>
+        <v>2030</v>
       </c>
       <c r="C55" s="3">
         <f>SUM(January:December!C55)</f>
-        <v>334</v>
+        <v>505</v>
       </c>
       <c r="D55" s="3">
         <f>SUM(January:December!D55)</f>
-        <v>633</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -3013,15 +3017,15 @@
       </c>
       <c r="B56" s="4">
         <f>SUM(January:December!B56)</f>
-        <v>2384</v>
+        <v>3751</v>
       </c>
       <c r="C56" s="4">
         <f>SUM(January:December!C56)</f>
-        <v>1229</v>
+        <v>1754</v>
       </c>
       <c r="D56" s="4">
         <f>SUM(January:December!D56)</f>
-        <v>435</v>
+        <v>637</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -3030,15 +3034,15 @@
       </c>
       <c r="B57" s="7">
         <f>SUM(January:December!B57)</f>
-        <v>6430</v>
+        <v>9333</v>
       </c>
       <c r="C57" s="7">
         <f>SUM(January:December!C57)</f>
-        <v>431</v>
+        <v>652</v>
       </c>
       <c r="D57" s="7">
         <f>SUM(January:December!D57)</f>
-        <v>249</v>
+        <v>383</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -3047,15 +3051,15 @@
       </c>
       <c r="B58" s="8">
         <f>SUM(January:December!B58)</f>
-        <v>167420</v>
+        <v>255714</v>
       </c>
       <c r="C58" s="8">
         <f>SUM(January:December!C58)</f>
-        <v>28850</v>
+        <v>43139</v>
       </c>
       <c r="D58" s="8">
         <f>SUM(January:December!D58)</f>
-        <v>27951</v>
+        <v>41783</v>
       </c>
     </row>
   </sheetData>
@@ -7153,7 +7157,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
@@ -7164,23 +7168,27 @@
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="19"/>
+      <c r="B1" s="19">
+        <v>46082</v>
+      </c>
       <c r="C1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="21"/>
+      <c r="D1" s="21">
+        <v>46112</v>
+      </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="22" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="22" t="s">
         <v>3</v>
       </c>
     </row>
@@ -7188,453 +7196,804 @@
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="B3" s="3">
+        <v>5840</v>
+      </c>
+      <c r="C3" s="3">
+        <v>944</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1088</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="B4" s="2">
+        <v>3403</v>
+      </c>
+      <c r="C4" s="2">
+        <v>338</v>
+      </c>
+      <c r="D4" s="2">
+        <v>441</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="B5" s="3">
+        <v>9487</v>
+      </c>
+      <c r="C5" s="3">
+        <v>827</v>
+      </c>
+      <c r="D5" s="3">
+        <v>780</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="B6" s="2">
+        <v>87</v>
+      </c>
+      <c r="C6" s="2">
+        <v>69</v>
+      </c>
+      <c r="D6" s="2">
+        <v>8</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="B7" s="3">
+        <v>6290</v>
+      </c>
+      <c r="C7" s="3">
+        <v>847</v>
+      </c>
+      <c r="D7" s="3">
+        <v>764</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="B8" s="2">
+        <v>709</v>
+      </c>
+      <c r="C8" s="2">
+        <v>151</v>
+      </c>
+      <c r="D8" s="2">
+        <v>142</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="B9" s="3">
+        <v>555</v>
+      </c>
+      <c r="C9" s="3">
+        <v>115</v>
+      </c>
+      <c r="D9" s="3">
+        <v>110</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="B10" s="2">
+        <v>226</v>
+      </c>
+      <c r="C10" s="2">
+        <v>30</v>
+      </c>
+      <c r="D10" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
+      <c r="B11" s="3">
+        <v>46</v>
+      </c>
+      <c r="C11" s="3">
+        <v>22</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
+      <c r="B13" s="4">
+        <v>16</v>
+      </c>
+      <c r="C13" s="4">
+        <v>38</v>
+      </c>
+      <c r="D13" s="4">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="B14" s="5">
+        <v>214</v>
+      </c>
+      <c r="C14" s="5">
+        <v>90</v>
+      </c>
+      <c r="D14" s="5">
+        <v>59</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
+      <c r="B15" s="4">
+        <v>809</v>
+      </c>
+      <c r="C15" s="4">
+        <v>264</v>
+      </c>
+      <c r="D15" s="4">
+        <v>138</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
+      <c r="B16" s="5">
+        <v>328</v>
+      </c>
+      <c r="C16" s="5">
+        <v>189</v>
+      </c>
+      <c r="D16" s="5">
+        <v>50</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
+      <c r="B17" s="3">
+        <v>304</v>
+      </c>
+      <c r="C17" s="3">
+        <v>119</v>
+      </c>
+      <c r="D17" s="3">
+        <v>42</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="B18" s="2">
+        <v>2034</v>
+      </c>
+      <c r="C18" s="2">
+        <v>361</v>
+      </c>
+      <c r="D18" s="2">
+        <v>462</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
+      <c r="B19" s="3">
+        <v>177</v>
+      </c>
+      <c r="C19" s="3">
+        <v>73</v>
+      </c>
+      <c r="D19" s="3">
+        <v>63</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
+      <c r="B20" s="2">
+        <v>2033</v>
+      </c>
+      <c r="C20" s="2">
+        <v>239</v>
+      </c>
+      <c r="D20" s="2">
+        <v>493</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
+      <c r="B21" s="3">
+        <v>39</v>
+      </c>
+      <c r="C21" s="3">
+        <v>40</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
+      <c r="B22" s="2">
+        <v>2154</v>
+      </c>
+      <c r="C22" s="2">
+        <v>340</v>
+      </c>
+      <c r="D22" s="2">
+        <v>437</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
+      <c r="B23" s="3">
+        <v>336</v>
+      </c>
+      <c r="C23" s="3">
+        <v>196</v>
+      </c>
+      <c r="D23" s="3">
+        <v>56</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
+      <c r="B24" s="2">
+        <v>3233</v>
+      </c>
+      <c r="C24" s="2">
+        <v>470</v>
+      </c>
+      <c r="D24" s="2">
+        <v>738</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
+      <c r="B25" s="3">
+        <v>12077</v>
+      </c>
+      <c r="C25" s="3">
+        <v>995</v>
+      </c>
+      <c r="D25" s="3">
+        <v>1176</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
+      <c r="B26" s="2">
+        <v>537</v>
+      </c>
+      <c r="C26" s="2">
+        <v>277</v>
+      </c>
+      <c r="D26" s="2">
+        <v>107</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
+      <c r="B27" s="3">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
+      <c r="B28" s="2">
+        <v>619</v>
+      </c>
+      <c r="C28" s="2">
+        <v>157</v>
+      </c>
+      <c r="D28" s="2">
+        <v>132</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
+      <c r="B29" s="3">
+        <v>469</v>
+      </c>
+      <c r="C29" s="3">
+        <v>77</v>
+      </c>
+      <c r="D29" s="3">
+        <v>147</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
+      <c r="B30" s="2">
+        <v>2548</v>
+      </c>
+      <c r="C30" s="2">
+        <v>388</v>
+      </c>
+      <c r="D30" s="2">
+        <v>469</v>
+      </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
+      <c r="B31" s="3">
+        <v>31</v>
+      </c>
+      <c r="C31" s="3">
+        <v>7</v>
+      </c>
+      <c r="D31" s="3">
+        <v>23</v>
+      </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
+      <c r="B32" s="2">
+        <v>481</v>
+      </c>
+      <c r="C32" s="2">
+        <v>203</v>
+      </c>
+      <c r="D32" s="2">
+        <v>105</v>
+      </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
+      <c r="B33" s="3">
+        <v>1646</v>
+      </c>
+      <c r="C33" s="3">
+        <v>455</v>
+      </c>
+      <c r="D33" s="3">
+        <v>345</v>
+      </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
+      <c r="B34" s="2">
+        <v>1192</v>
+      </c>
+      <c r="C34" s="2">
+        <v>234</v>
+      </c>
+      <c r="D34" s="2">
+        <v>264</v>
+      </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
+      <c r="B35" s="3">
+        <v>488</v>
+      </c>
+      <c r="C35" s="3">
+        <v>98</v>
+      </c>
+      <c r="D35" s="3">
+        <v>107</v>
+      </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
+      <c r="B36" s="2">
+        <v>6076</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1122</v>
+      </c>
+      <c r="D36" s="2">
+        <v>843</v>
+      </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
+      <c r="B37" s="3">
+        <v>875</v>
+      </c>
+      <c r="C37" s="3">
+        <v>468</v>
+      </c>
+      <c r="D37" s="3">
+        <v>129</v>
+      </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
+      <c r="B38" s="2">
+        <v>3854</v>
+      </c>
+      <c r="C38" s="2">
+        <v>324</v>
+      </c>
+      <c r="D38" s="2">
+        <v>515</v>
+      </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
+      <c r="B39" s="3">
+        <v>233</v>
+      </c>
+      <c r="C39" s="3">
+        <v>152</v>
+      </c>
+      <c r="D39" s="3">
+        <v>36</v>
+      </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
+      <c r="B40" s="6">
+        <v>476</v>
+      </c>
+      <c r="C40" s="6">
+        <v>112</v>
+      </c>
+      <c r="D40" s="6">
+        <v>18</v>
+      </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
+      <c r="B41" s="7">
+        <v>2135</v>
+      </c>
+      <c r="C41" s="7">
+        <v>81</v>
+      </c>
+      <c r="D41" s="7">
+        <v>116</v>
+      </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
+      <c r="B42" s="6">
+        <v>41</v>
+      </c>
+      <c r="C42" s="6">
+        <v>16</v>
+      </c>
+      <c r="D42" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
+      <c r="B43" s="7">
+        <v>251</v>
+      </c>
+      <c r="C43" s="7">
+        <v>35</v>
+      </c>
+      <c r="D43" s="7">
+        <v>18</v>
+      </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
+      <c r="B44" s="2">
+        <v>238</v>
+      </c>
+      <c r="C44" s="2">
+        <v>88</v>
+      </c>
+      <c r="D44" s="2">
+        <v>83</v>
+      </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
+      <c r="B45" s="3">
+        <v>411</v>
+      </c>
+      <c r="C45" s="3">
+        <v>170</v>
+      </c>
+      <c r="D45" s="3">
+        <v>35</v>
+      </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
+      <c r="B46" s="2">
+        <v>1860</v>
+      </c>
+      <c r="C46" s="2">
+        <v>453</v>
+      </c>
+      <c r="D46" s="2">
+        <v>406</v>
+      </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
+      <c r="B47" s="3">
+        <v>3539</v>
+      </c>
+      <c r="C47" s="3">
+        <v>560</v>
+      </c>
+      <c r="D47" s="3">
+        <v>642</v>
+      </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
+      <c r="B48" s="2">
+        <v>1578</v>
+      </c>
+      <c r="C48" s="2">
+        <v>451</v>
+      </c>
+      <c r="D48" s="2">
+        <v>196</v>
+      </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
+      <c r="B49" s="3">
+        <v>1083</v>
+      </c>
+      <c r="C49" s="3">
+        <v>196</v>
+      </c>
+      <c r="D49" s="3">
+        <v>256</v>
+      </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
+      <c r="B50" s="2">
+        <v>4098</v>
+      </c>
+      <c r="C50" s="2">
+        <v>454</v>
+      </c>
+      <c r="D50" s="2">
+        <v>706</v>
+      </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
+      <c r="B51" s="3">
+        <v>520</v>
+      </c>
+      <c r="C51" s="3">
+        <v>112</v>
+      </c>
+      <c r="D51" s="3">
+        <v>155</v>
+      </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
+      <c r="B52" s="2">
+        <v>1450</v>
+      </c>
+      <c r="C52" s="2">
+        <v>284</v>
+      </c>
+      <c r="D52" s="2">
+        <v>394</v>
+      </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
+      <c r="B53" s="3">
+        <v>236</v>
+      </c>
+      <c r="C53" s="3">
+        <v>206</v>
+      </c>
+      <c r="D53" s="3">
+        <v>92</v>
+      </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
+      <c r="B54" s="2">
+        <v>206</v>
+      </c>
+      <c r="C54" s="2">
+        <v>181</v>
+      </c>
+      <c r="D54" s="2">
+        <v>15</v>
+      </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
+      <c r="B55" s="3">
+        <v>726</v>
+      </c>
+      <c r="C55" s="3">
+        <v>171</v>
+      </c>
+      <c r="D55" s="3">
+        <v>403</v>
+      </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
+      <c r="B56" s="4">
+        <v>1367</v>
+      </c>
+      <c r="C56" s="4">
+        <v>525</v>
+      </c>
+      <c r="D56" s="4">
+        <v>202</v>
+      </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
+      <c r="B57" s="7">
+        <v>2903</v>
+      </c>
+      <c r="C57" s="7">
+        <v>221</v>
+      </c>
+      <c r="D57" s="7">
+        <v>134</v>
+      </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
+      <c r="B58" s="8">
+        <v>88294</v>
+      </c>
+      <c r="C58" s="8">
+        <v>14289</v>
+      </c>
+      <c r="D58" s="8">
+        <v>13832</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B59">
+        <v>88294</v>
+      </c>
+      <c r="C59">
+        <v>14289</v>
+      </c>
+      <c r="D59">
+        <v>13832</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:D2" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="20480" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/statistics_files/nekls_executive_board/2026/2026_next_statistics.xlsx
+++ b/statistics_files/nekls_executive_board/2026/2026_next_statistics.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\nekls_executive_board\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Staff\Documents\GitHub\next_statistics\statistics_files\nekls_executive_board\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C250E64-926A-495B-B3A5-4278E71BF5D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABC21763-A088-4702-9B51-9FE3DF915054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="740" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Annual totals" sheetId="1" r:id="rId1"/>
@@ -2075,13 +2075,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -2093,10 +2093,10 @@
       </c>
       <c r="D1" s="21">
         <f>MAX(January:December!D1)</f>
-        <v>46112</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -2110,160 +2110,160 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="3">
         <f>SUM(January:December!B3)</f>
-        <v>16625</v>
+        <v>22570</v>
       </c>
       <c r="C3" s="3">
         <f>SUM(January:December!C3)</f>
-        <v>2743</v>
+        <v>3390</v>
       </c>
       <c r="D3" s="3">
         <f>SUM(January:December!D3)</f>
-        <v>3173</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4064</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2">
         <f>SUM(January:December!B4)</f>
-        <v>9724</v>
+        <v>13339</v>
       </c>
       <c r="C4" s="2">
         <f>SUM(January:December!C4)</f>
-        <v>910</v>
+        <v>1195</v>
       </c>
       <c r="D4" s="2">
         <f>SUM(January:December!D4)</f>
-        <v>1488</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="3">
         <f>SUM(January:December!B5)</f>
-        <v>26706</v>
+        <v>34923</v>
       </c>
       <c r="C5" s="3">
         <f>SUM(January:December!C5)</f>
-        <v>2389</v>
+        <v>3228</v>
       </c>
       <c r="D5" s="3">
         <f>SUM(January:December!D5)</f>
-        <v>2501</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="2">
         <f>SUM(January:December!B6)</f>
-        <v>278</v>
+        <v>448</v>
       </c>
       <c r="C6" s="2">
         <f>SUM(January:December!C6)</f>
-        <v>253</v>
+        <v>308</v>
       </c>
       <c r="D6" s="2">
         <f>SUM(January:December!D6)</f>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="3">
         <f>SUM(January:December!B7)</f>
-        <v>18212</v>
+        <v>24471</v>
       </c>
       <c r="C7" s="3">
         <f>SUM(January:December!C7)</f>
-        <v>2545</v>
+        <v>3378</v>
       </c>
       <c r="D7" s="3">
         <f>SUM(January:December!D7)</f>
-        <v>2383</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2985</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="2">
         <f>SUM(January:December!B8)</f>
-        <v>2668</v>
+        <v>3611</v>
       </c>
       <c r="C8" s="2">
         <f>SUM(January:December!C8)</f>
-        <v>428</v>
+        <v>558</v>
       </c>
       <c r="D8" s="2">
         <f>SUM(January:December!D8)</f>
-        <v>364</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="3">
         <f>SUM(January:December!B9)</f>
-        <v>1638</v>
+        <v>2172</v>
       </c>
       <c r="C9" s="3">
         <f>SUM(January:December!C9)</f>
-        <v>401</v>
+        <v>488</v>
       </c>
       <c r="D9" s="3">
         <f>SUM(January:December!D9)</f>
-        <v>320</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="2">
         <f>SUM(January:December!B10)</f>
-        <v>702</v>
+        <v>993</v>
       </c>
       <c r="C10" s="2">
         <f>SUM(January:December!C10)</f>
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="D10" s="2">
         <f>SUM(January:December!D10)</f>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="3">
         <f>SUM(January:December!B11)</f>
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="C11" s="3">
         <f>SUM(January:December!C11)</f>
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D11" s="3">
         <f>SUM(January:December!D11)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -2280,245 +2280,245 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
       <c r="B13" s="4">
         <f>SUM(January:December!B13)</f>
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="C13" s="4">
         <f>SUM(January:December!C13)</f>
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D13" s="4">
         <f>SUM(January:December!D13)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="5">
         <f>SUM(January:December!B14)</f>
-        <v>489</v>
+        <v>673</v>
       </c>
       <c r="C14" s="5">
         <f>SUM(January:December!C14)</f>
-        <v>348</v>
+        <v>415</v>
       </c>
       <c r="D14" s="5">
         <f>SUM(January:December!D14)</f>
-        <v>168</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
       <c r="B15" s="4">
         <f>SUM(January:December!B15)</f>
-        <v>2276</v>
+        <v>2970</v>
       </c>
       <c r="C15" s="4">
         <f>SUM(January:December!C15)</f>
-        <v>697</v>
+        <v>886</v>
       </c>
       <c r="D15" s="4">
         <f>SUM(January:December!D15)</f>
-        <v>446</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
       <c r="B16" s="5">
         <f>SUM(January:December!B16)</f>
-        <v>924</v>
+        <v>1209</v>
       </c>
       <c r="C16" s="5">
         <f>SUM(January:December!C16)</f>
-        <v>747</v>
+        <v>952</v>
       </c>
       <c r="D16" s="5">
         <f>SUM(January:December!D16)</f>
-        <v>153</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="3">
         <f>SUM(January:December!B17)</f>
-        <v>844</v>
+        <v>1105</v>
       </c>
       <c r="C17" s="3">
         <f>SUM(January:December!C17)</f>
-        <v>445</v>
+        <v>553</v>
       </c>
       <c r="D17" s="3">
         <f>SUM(January:December!D17)</f>
-        <v>129</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="2">
         <f>SUM(January:December!B18)</f>
-        <v>5730</v>
+        <v>7684</v>
       </c>
       <c r="C18" s="2">
         <f>SUM(January:December!C18)</f>
-        <v>1077</v>
+        <v>1331</v>
       </c>
       <c r="D18" s="2">
         <f>SUM(January:December!D18)</f>
-        <v>1449</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="3">
         <f>SUM(January:December!B19)</f>
-        <v>561</v>
+        <v>726</v>
       </c>
       <c r="C19" s="3">
         <f>SUM(January:December!C19)</f>
-        <v>201</v>
+        <v>278</v>
       </c>
       <c r="D19" s="3">
         <f>SUM(January:December!D19)</f>
-        <v>143</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="2">
         <f>SUM(January:December!B20)</f>
-        <v>6411</v>
+        <v>8445</v>
       </c>
       <c r="C20" s="2">
         <f>SUM(January:December!C20)</f>
-        <v>703</v>
+        <v>958</v>
       </c>
       <c r="D20" s="2">
         <f>SUM(January:December!D20)</f>
-        <v>1407</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="3">
         <f>SUM(January:December!B21)</f>
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C21" s="3">
         <f>SUM(January:December!C21)</f>
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="D21" s="3">
         <f>SUM(January:December!D21)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
       <c r="B22" s="2">
         <f>SUM(January:December!B22)</f>
-        <v>5969</v>
+        <v>8097</v>
       </c>
       <c r="C22" s="2">
         <f>SUM(January:December!C22)</f>
-        <v>994</v>
+        <v>1246</v>
       </c>
       <c r="D22" s="2">
         <f>SUM(January:December!D22)</f>
-        <v>1248</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B23" s="3">
         <f>SUM(January:December!B23)</f>
-        <v>977</v>
+        <v>1329</v>
       </c>
       <c r="C23" s="3">
         <f>SUM(January:December!C23)</f>
-        <v>572</v>
+        <v>734</v>
       </c>
       <c r="D23" s="3">
         <f>SUM(January:December!D23)</f>
-        <v>199</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
       <c r="B24" s="2">
         <f>SUM(January:December!B24)</f>
-        <v>8276</v>
+        <v>10122</v>
       </c>
       <c r="C24" s="2">
         <f>SUM(January:December!C24)</f>
-        <v>1306</v>
+        <v>1625</v>
       </c>
       <c r="D24" s="2">
         <f>SUM(January:December!D24)</f>
-        <v>1677</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
       <c r="B25" s="3">
         <f>SUM(January:December!B25)</f>
-        <v>34372</v>
+        <v>47493</v>
       </c>
       <c r="C25" s="3">
         <f>SUM(January:December!C25)</f>
-        <v>3277</v>
+        <v>4284</v>
       </c>
       <c r="D25" s="3">
         <f>SUM(January:December!D25)</f>
-        <v>3897</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4985</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B26" s="2">
         <f>SUM(January:December!B26)</f>
-        <v>1680</v>
+        <v>2302</v>
       </c>
       <c r="C26" s="2">
         <f>SUM(January:December!C26)</f>
-        <v>761</v>
+        <v>944</v>
       </c>
       <c r="D26" s="2">
         <f>SUM(January:December!D26)</f>
-        <v>360</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -2535,251 +2535,251 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
       <c r="B28" s="2">
         <f>SUM(January:December!B28)</f>
-        <v>1783</v>
+        <v>2459</v>
       </c>
       <c r="C28" s="2">
         <f>SUM(January:December!C28)</f>
-        <v>387</v>
+        <v>513</v>
       </c>
       <c r="D28" s="2">
         <f>SUM(January:December!D28)</f>
-        <v>395</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
       <c r="B29" s="3">
         <f>SUM(January:December!B29)</f>
-        <v>1370</v>
+        <v>1841</v>
       </c>
       <c r="C29" s="3">
         <f>SUM(January:December!C29)</f>
-        <v>287</v>
+        <v>350</v>
       </c>
       <c r="D29" s="3">
         <f>SUM(January:December!D29)</f>
-        <v>361</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
       <c r="B30" s="2">
         <f>SUM(January:December!B30)</f>
-        <v>7504</v>
+        <v>10677</v>
       </c>
       <c r="C30" s="2">
         <f>SUM(January:December!C30)</f>
-        <v>1205</v>
+        <v>1453</v>
       </c>
       <c r="D30" s="2">
         <f>SUM(January:December!D30)</f>
-        <v>1584</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
       <c r="B31" s="3">
         <f>SUM(January:December!B31)</f>
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="C31" s="3">
         <f>SUM(January:December!C31)</f>
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="D31" s="3">
         <f>SUM(January:December!D31)</f>
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B32" s="2">
         <f>SUM(January:December!B32)</f>
-        <v>1446</v>
+        <v>1864</v>
       </c>
       <c r="C32" s="2">
         <f>SUM(January:December!C32)</f>
-        <v>604</v>
+        <v>795</v>
       </c>
       <c r="D32" s="2">
         <f>SUM(January:December!D32)</f>
-        <v>331</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
       <c r="B33" s="3">
         <f>SUM(January:December!B33)</f>
-        <v>4953</v>
+        <v>6648</v>
       </c>
       <c r="C33" s="3">
         <f>SUM(January:December!C33)</f>
-        <v>1280</v>
+        <v>1597</v>
       </c>
       <c r="D33" s="3">
         <f>SUM(January:December!D33)</f>
-        <v>1088</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
       <c r="B34" s="2">
         <f>SUM(January:December!B34)</f>
-        <v>3394</v>
+        <v>4595</v>
       </c>
       <c r="C34" s="2">
         <f>SUM(January:December!C34)</f>
-        <v>754</v>
+        <v>985</v>
       </c>
       <c r="D34" s="2">
         <f>SUM(January:December!D34)</f>
-        <v>818</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
       <c r="B35" s="3">
         <f>SUM(January:December!B35)</f>
-        <v>1948</v>
+        <v>2601</v>
       </c>
       <c r="C35" s="3">
         <f>SUM(January:December!C35)</f>
-        <v>289</v>
+        <v>350</v>
       </c>
       <c r="D35" s="3">
         <f>SUM(January:December!D35)</f>
-        <v>389</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
       <c r="B36" s="2">
         <f>SUM(January:December!B36)</f>
-        <v>19380</v>
+        <v>24863</v>
       </c>
       <c r="C36" s="2">
         <f>SUM(January:December!C36)</f>
-        <v>3454</v>
+        <v>4544</v>
       </c>
       <c r="D36" s="2">
         <f>SUM(January:December!D36)</f>
-        <v>2486</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3287</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
       <c r="B37" s="3">
         <f>SUM(January:December!B37)</f>
-        <v>2770</v>
+        <v>3731</v>
       </c>
       <c r="C37" s="3">
         <f>SUM(January:December!C37)</f>
-        <v>1384</v>
+        <v>1787</v>
       </c>
       <c r="D37" s="3">
         <f>SUM(January:December!D37)</f>
-        <v>430</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B38" s="2">
         <f>SUM(January:December!B38)</f>
-        <v>10436</v>
+        <v>14516</v>
       </c>
       <c r="C38" s="2">
         <f>SUM(January:December!C38)</f>
-        <v>969</v>
+        <v>1197</v>
       </c>
       <c r="D38" s="2">
         <f>SUM(January:December!D38)</f>
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
       <c r="B39" s="3">
         <f>SUM(January:December!B39)</f>
-        <v>614</v>
+        <v>974</v>
       </c>
       <c r="C39" s="3">
         <f>SUM(January:December!C39)</f>
-        <v>465</v>
+        <v>618</v>
       </c>
       <c r="D39" s="3">
         <f>SUM(January:December!D39)</f>
-        <v>95</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B40" s="6">
         <f>SUM(January:December!B40)</f>
-        <v>1347</v>
+        <v>1449</v>
       </c>
       <c r="C40" s="6">
         <f>SUM(January:December!C40)</f>
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D40" s="6">
         <f>SUM(January:December!D40)</f>
         <v>52</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
       <c r="B41" s="7">
         <f>SUM(January:December!B41)</f>
-        <v>6943</v>
+        <v>6969</v>
       </c>
       <c r="C41" s="7">
         <f>SUM(January:December!C41)</f>
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D41" s="7">
         <f>SUM(January:December!D41)</f>
-        <v>331</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
       <c r="B42" s="6">
         <f>SUM(January:December!B42)</f>
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C42" s="6">
         <f>SUM(January:December!C42)</f>
@@ -2790,7 +2790,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -2807,259 +2807,259 @@
         <v>71</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B44" s="2">
         <f>SUM(January:December!B44)</f>
-        <v>857</v>
+        <v>1073</v>
       </c>
       <c r="C44" s="2">
         <f>SUM(January:December!C44)</f>
-        <v>236</v>
+        <v>304</v>
       </c>
       <c r="D44" s="2">
         <f>SUM(January:December!D44)</f>
-        <v>566</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
       <c r="B45" s="3">
         <f>SUM(January:December!B45)</f>
-        <v>1121</v>
+        <v>1552</v>
       </c>
       <c r="C45" s="3">
         <f>SUM(January:December!C45)</f>
-        <v>462</v>
+        <v>633</v>
       </c>
       <c r="D45" s="3">
         <f>SUM(January:December!D45)</f>
-        <v>108</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
       <c r="B46" s="2">
         <f>SUM(January:December!B46)</f>
-        <v>5375</v>
+        <v>7208</v>
       </c>
       <c r="C46" s="2">
         <f>SUM(January:December!C46)</f>
-        <v>1431</v>
+        <v>1818</v>
       </c>
       <c r="D46" s="2">
         <f>SUM(January:December!D46)</f>
-        <v>1196</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
       <c r="B47" s="3">
         <f>SUM(January:December!B47)</f>
-        <v>10185</v>
+        <v>15164</v>
       </c>
       <c r="C47" s="3">
         <f>SUM(January:December!C47)</f>
-        <v>1730</v>
+        <v>2112</v>
       </c>
       <c r="D47" s="3">
         <f>SUM(January:December!D47)</f>
-        <v>1990</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2454</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
       <c r="B48" s="2">
         <f>SUM(January:December!B48)</f>
-        <v>4160</v>
+        <v>5991</v>
       </c>
       <c r="C48" s="2">
         <f>SUM(January:December!C48)</f>
-        <v>1335</v>
+        <v>1710</v>
       </c>
       <c r="D48" s="2">
         <f>SUM(January:December!D48)</f>
-        <v>549</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
       <c r="B49" s="3">
         <f>SUM(January:December!B49)</f>
-        <v>2911</v>
+        <v>3649</v>
       </c>
       <c r="C49" s="3">
         <f>SUM(January:December!C49)</f>
-        <v>691</v>
+        <v>818</v>
       </c>
       <c r="D49" s="3">
         <f>SUM(January:December!D49)</f>
-        <v>848</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B50" s="2">
         <f>SUM(January:December!B50)</f>
-        <v>11766</v>
+        <v>16433</v>
       </c>
       <c r="C50" s="2">
         <f>SUM(January:December!C50)</f>
-        <v>1261</v>
+        <v>1580</v>
       </c>
       <c r="D50" s="2">
         <f>SUM(January:December!D50)</f>
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B51" s="3">
         <f>SUM(January:December!B51)</f>
-        <v>1334</v>
+        <v>1812</v>
       </c>
       <c r="C51" s="3">
         <f>SUM(January:December!C51)</f>
-        <v>397</v>
+        <v>504</v>
       </c>
       <c r="D51" s="3">
         <f>SUM(January:December!D51)</f>
-        <v>367</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
       <c r="B52" s="2">
         <f>SUM(January:December!B52)</f>
-        <v>4259</v>
+        <v>5435</v>
       </c>
       <c r="C52" s="2">
         <f>SUM(January:December!C52)</f>
-        <v>856</v>
+        <v>1083</v>
       </c>
       <c r="D52" s="2">
         <f>SUM(January:December!D52)</f>
-        <v>1397</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B53" s="3">
         <f>SUM(January:December!B53)</f>
-        <v>649</v>
+        <v>789</v>
       </c>
       <c r="C53" s="3">
         <f>SUM(January:December!C53)</f>
-        <v>546</v>
+        <v>703</v>
       </c>
       <c r="D53" s="3">
         <f>SUM(January:December!D53)</f>
-        <v>290</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
       <c r="B54" s="2">
         <f>SUM(January:December!B54)</f>
-        <v>673</v>
+        <v>941</v>
       </c>
       <c r="C54" s="2">
         <f>SUM(January:December!C54)</f>
-        <v>605</v>
+        <v>779</v>
       </c>
       <c r="D54" s="2">
         <f>SUM(January:December!D54)</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
       <c r="B55" s="3">
         <f>SUM(January:December!B55)</f>
-        <v>2030</v>
+        <v>2965</v>
       </c>
       <c r="C55" s="3">
         <f>SUM(January:December!C55)</f>
-        <v>505</v>
+        <v>646</v>
       </c>
       <c r="D55" s="3">
         <f>SUM(January:December!D55)</f>
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
       <c r="B56" s="4">
         <f>SUM(January:December!B56)</f>
-        <v>3751</v>
+        <v>4977</v>
       </c>
       <c r="C56" s="4">
         <f>SUM(January:December!C56)</f>
-        <v>1754</v>
+        <v>2184</v>
       </c>
       <c r="D56" s="4">
         <f>SUM(January:December!D56)</f>
-        <v>637</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
       <c r="B57" s="7">
         <f>SUM(January:December!B57)</f>
-        <v>9333</v>
+        <v>9463</v>
       </c>
       <c r="C57" s="7">
         <f>SUM(January:December!C57)</f>
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="D57" s="7">
         <f>SUM(January:December!D57)</f>
-        <v>383</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
       <c r="B58" s="8">
         <f>SUM(January:December!B58)</f>
-        <v>255714</v>
+        <v>342462</v>
       </c>
       <c r="C58" s="8">
         <f>SUM(January:December!C58)</f>
-        <v>43139</v>
+        <v>54929</v>
       </c>
       <c r="D58" s="8">
         <f>SUM(January:December!D58)</f>
-        <v>41783</v>
+        <v>52577</v>
       </c>
     </row>
   </sheetData>
@@ -3557,13 +3557,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -3587,7 +3587,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -3595,7 +3595,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -3603,7 +3603,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -3611,7 +3611,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -3619,7 +3619,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -3627,7 +3627,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -3635,7 +3635,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -3643,7 +3643,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -3651,7 +3651,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -3659,7 +3659,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -3667,7 +3667,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -3675,7 +3675,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -3683,7 +3683,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -3691,7 +3691,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -3699,7 +3699,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -3707,7 +3707,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -3715,7 +3715,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -3723,7 +3723,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -3731,7 +3731,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -3739,7 +3739,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -3747,7 +3747,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -3755,7 +3755,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -3763,7 +3763,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -3771,7 +3771,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -3779,7 +3779,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -3787,7 +3787,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -3795,7 +3795,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -3803,7 +3803,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -3811,7 +3811,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -3819,7 +3819,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -3827,7 +3827,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -3835,7 +3835,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -3843,7 +3843,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -3851,7 +3851,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -3859,7 +3859,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -3867,7 +3867,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -3875,7 +3875,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -3883,7 +3883,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -3891,7 +3891,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -3899,7 +3899,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -3907,7 +3907,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -3915,7 +3915,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -3923,7 +3923,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -3931,7 +3931,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -3939,7 +3939,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -3947,7 +3947,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -3955,7 +3955,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -3963,7 +3963,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -3971,7 +3971,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -3979,7 +3979,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -3987,7 +3987,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -3995,7 +3995,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -4003,7 +4003,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -4011,7 +4011,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -4019,7 +4019,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -4027,7 +4027,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -4044,13 +4044,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -4074,7 +4074,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -4082,7 +4082,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -4090,7 +4090,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -4098,7 +4098,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -4106,7 +4106,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -4114,7 +4114,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -4122,7 +4122,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -4130,7 +4130,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -4138,7 +4138,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -4146,7 +4146,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -4154,7 +4154,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -4162,7 +4162,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -4170,7 +4170,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -4178,7 +4178,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -4186,7 +4186,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -4194,7 +4194,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -4202,7 +4202,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -4210,7 +4210,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -4218,7 +4218,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -4226,7 +4226,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -4234,7 +4234,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -4242,7 +4242,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -4250,7 +4250,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -4258,7 +4258,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -4266,7 +4266,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -4274,7 +4274,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -4282,7 +4282,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -4290,7 +4290,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -4298,7 +4298,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -4306,7 +4306,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -4314,7 +4314,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -4322,7 +4322,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -4330,7 +4330,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -4338,7 +4338,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -4346,7 +4346,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -4354,7 +4354,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -4362,7 +4362,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -4370,7 +4370,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -4378,7 +4378,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -4386,7 +4386,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -4394,7 +4394,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -4402,7 +4402,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -4410,7 +4410,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -4418,7 +4418,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -4426,7 +4426,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -4434,7 +4434,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -4442,7 +4442,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -4450,7 +4450,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -4458,7 +4458,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -4466,7 +4466,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -4474,7 +4474,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -4482,7 +4482,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -4490,7 +4490,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -4498,7 +4498,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -4506,7 +4506,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -4514,7 +4514,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -4531,13 +4531,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -4561,7 +4561,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -4569,7 +4569,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -4577,7 +4577,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -4585,7 +4585,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -4593,7 +4593,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -4601,7 +4601,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -4609,7 +4609,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -4617,7 +4617,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -4625,7 +4625,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -4633,7 +4633,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -4641,7 +4641,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -4649,7 +4649,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -4657,7 +4657,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -4665,7 +4665,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -4673,7 +4673,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -4681,7 +4681,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -4689,7 +4689,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -4697,7 +4697,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -4705,7 +4705,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -4713,7 +4713,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -4721,7 +4721,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -4729,7 +4729,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -4737,7 +4737,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -4745,7 +4745,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -4753,7 +4753,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -4761,7 +4761,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -4769,7 +4769,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -4777,7 +4777,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -4785,7 +4785,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -4793,7 +4793,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -4801,7 +4801,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -4809,7 +4809,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -4817,7 +4817,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -4825,7 +4825,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -4833,7 +4833,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -4841,7 +4841,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -4849,7 +4849,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -4857,7 +4857,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -4865,7 +4865,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -4873,7 +4873,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -4881,7 +4881,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -4889,7 +4889,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -4897,7 +4897,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -4905,7 +4905,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -4913,7 +4913,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -4921,7 +4921,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -4929,7 +4929,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -4937,7 +4937,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -4945,7 +4945,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -4953,7 +4953,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -4961,7 +4961,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -4969,7 +4969,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -4977,7 +4977,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -4985,7 +4985,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -4993,7 +4993,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -5001,7 +5001,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -5018,13 +5018,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -5048,7 +5048,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -5056,7 +5056,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -5064,7 +5064,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -5072,7 +5072,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -5080,7 +5080,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -5088,7 +5088,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -5096,7 +5096,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -5104,7 +5104,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -5112,7 +5112,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -5120,7 +5120,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -5128,7 +5128,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -5136,7 +5136,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -5144,7 +5144,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -5152,7 +5152,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -5160,7 +5160,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -5168,7 +5168,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -5176,7 +5176,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -5184,7 +5184,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -5192,7 +5192,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -5200,7 +5200,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -5208,7 +5208,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -5216,7 +5216,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -5224,7 +5224,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -5232,7 +5232,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -5240,7 +5240,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -5248,7 +5248,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -5256,7 +5256,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -5264,7 +5264,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -5272,7 +5272,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -5280,7 +5280,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -5288,7 +5288,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -5296,7 +5296,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -5304,7 +5304,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -5312,7 +5312,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -5320,7 +5320,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -5328,7 +5328,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -5336,7 +5336,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -5344,7 +5344,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -5352,7 +5352,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -5360,7 +5360,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -5368,7 +5368,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -5376,7 +5376,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -5384,7 +5384,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -5392,7 +5392,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -5400,7 +5400,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -5408,7 +5408,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -5416,7 +5416,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -5424,7 +5424,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -5432,7 +5432,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -5440,7 +5440,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -5448,7 +5448,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -5456,7 +5456,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -5464,7 +5464,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -5472,7 +5472,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -5480,7 +5480,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -5488,7 +5488,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -5504,13 +5504,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -5524,7 +5524,7 @@
         <v>46053</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -5538,7 +5538,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -5566,7 +5566,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -5580,7 +5580,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -5594,7 +5594,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -5608,7 +5608,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -5622,7 +5622,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -5636,7 +5636,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -5650,7 +5650,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -5678,7 +5678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -5692,7 +5692,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -5706,7 +5706,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -5720,7 +5720,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -5734,7 +5734,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -5748,7 +5748,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -5762,7 +5762,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -5776,7 +5776,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -5790,7 +5790,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -5804,7 +5804,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -5818,7 +5818,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -5832,7 +5832,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -5846,7 +5846,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -5860,7 +5860,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -5874,7 +5874,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -5888,7 +5888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -5902,7 +5902,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -5916,7 +5916,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -5930,7 +5930,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -5944,7 +5944,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -5958,7 +5958,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -5986,7 +5986,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -6000,7 +6000,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -6014,7 +6014,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -6028,7 +6028,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -6042,7 +6042,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -6056,7 +6056,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -6070,7 +6070,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -6084,7 +6084,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -6098,7 +6098,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -6112,7 +6112,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -6126,7 +6126,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -6140,7 +6140,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -6154,7 +6154,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -6168,7 +6168,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -6182,7 +6182,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -6196,7 +6196,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -6210,7 +6210,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -6224,7 +6224,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -6238,7 +6238,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -6252,7 +6252,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -6266,7 +6266,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -6280,7 +6280,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -6294,7 +6294,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -6308,7 +6308,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -6331,13 +6331,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -6351,7 +6351,7 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -6365,7 +6365,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -6379,7 +6379,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -6393,7 +6393,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -6407,7 +6407,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -6421,7 +6421,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -6435,7 +6435,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -6449,7 +6449,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -6463,7 +6463,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -6477,7 +6477,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -6491,7 +6491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -6505,7 +6505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -6519,7 +6519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -6533,7 +6533,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -6547,7 +6547,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -6561,7 +6561,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -6575,7 +6575,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -6589,7 +6589,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -6603,7 +6603,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -6617,7 +6617,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -6631,7 +6631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -6645,7 +6645,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -6659,7 +6659,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -6673,7 +6673,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -6687,7 +6687,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -6701,7 +6701,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -6715,7 +6715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -6729,7 +6729,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -6757,7 +6757,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -6771,7 +6771,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -6785,7 +6785,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -6799,7 +6799,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -6813,7 +6813,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -6827,7 +6827,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -6841,7 +6841,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -6855,7 +6855,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -6869,7 +6869,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -6883,7 +6883,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -6897,7 +6897,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -6911,7 +6911,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -6925,7 +6925,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -6939,7 +6939,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -6953,7 +6953,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -6967,7 +6967,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -6981,7 +6981,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -6995,7 +6995,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -7009,7 +7009,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -7023,7 +7023,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -7037,7 +7037,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -7051,7 +7051,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -7065,7 +7065,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -7079,7 +7079,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -7093,7 +7093,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -7107,7 +7107,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -7121,7 +7121,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -7135,7 +7135,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -7158,13 +7158,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D59"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -7178,7 +7178,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -7192,7 +7192,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -7206,7 +7206,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -7220,7 +7220,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -7234,7 +7234,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -7248,7 +7248,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -7262,7 +7262,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -7276,7 +7276,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -7290,7 +7290,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -7304,7 +7304,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -7318,7 +7318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -7332,7 +7332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -7346,7 +7346,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -7360,7 +7360,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -7374,7 +7374,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -7388,7 +7388,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -7402,7 +7402,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -7416,7 +7416,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -7430,7 +7430,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -7444,7 +7444,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -7458,7 +7458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -7472,7 +7472,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -7486,7 +7486,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -7500,7 +7500,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -7514,7 +7514,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -7528,7 +7528,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -7542,7 +7542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -7556,7 +7556,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -7570,7 +7570,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -7584,7 +7584,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -7598,7 +7598,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -7612,7 +7612,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -7626,7 +7626,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -7640,7 +7640,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -7654,7 +7654,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -7668,7 +7668,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -7682,7 +7682,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -7696,7 +7696,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -7710,7 +7710,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -7724,7 +7724,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -7738,7 +7738,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -7752,7 +7752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -7766,7 +7766,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -7780,7 +7780,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -7794,7 +7794,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -7808,7 +7808,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -7822,7 +7822,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -7836,7 +7836,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -7850,7 +7850,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -7864,7 +7864,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -7878,7 +7878,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -7892,7 +7892,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -7906,7 +7906,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -7920,7 +7920,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -7934,7 +7934,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -7948,7 +7948,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -7962,7 +7962,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -7976,7 +7976,7 @@
         <v>13832</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>61</v>
       </c>
@@ -8000,13 +8000,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -8030,7 +8030,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -8038,7 +8038,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -8046,7 +8046,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -8054,7 +8054,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -8062,7 +8062,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -8070,7 +8070,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -8078,7 +8078,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -8086,7 +8086,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -8094,7 +8094,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -8102,7 +8102,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -8110,7 +8110,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -8118,7 +8118,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -8126,7 +8126,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -8134,7 +8134,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -8142,7 +8142,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -8150,7 +8150,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -8158,7 +8158,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -8166,7 +8166,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -8174,7 +8174,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -8182,7 +8182,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -8190,7 +8190,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -8198,7 +8198,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -8206,7 +8206,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -8214,7 +8214,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -8222,7 +8222,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -8230,7 +8230,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -8238,7 +8238,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -8246,7 +8246,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -8254,7 +8254,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -8262,7 +8262,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -8270,7 +8270,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -8278,7 +8278,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -8286,7 +8286,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -8294,7 +8294,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -8302,7 +8302,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -8310,7 +8310,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -8318,7 +8318,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -8326,7 +8326,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -8334,7 +8334,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -8342,7 +8342,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -8350,7 +8350,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -8358,7 +8358,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -8366,7 +8366,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -8374,7 +8374,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -8382,7 +8382,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -8390,7 +8390,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -8398,7 +8398,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -8406,7 +8406,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -8414,7 +8414,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -8422,7 +8422,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -8430,7 +8430,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -8438,7 +8438,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -8446,7 +8446,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -8454,7 +8454,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -8462,7 +8462,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -8470,7 +8470,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -8487,23 +8487,27 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="19"/>
+      <c r="B1" s="19">
+        <v>46143</v>
+      </c>
       <c r="C1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="21"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D1" s="21">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -8517,453 +8521,789 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B3" s="3">
+        <v>5945</v>
+      </c>
+      <c r="C3" s="3">
+        <v>647</v>
+      </c>
+      <c r="D3" s="3">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="2">
+        <v>3615</v>
+      </c>
+      <c r="C4" s="2">
+        <v>285</v>
+      </c>
+      <c r="D4" s="2">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="3">
+        <v>8217</v>
+      </c>
+      <c r="C5" s="3">
+        <v>839</v>
+      </c>
+      <c r="D5" s="3">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="2">
+        <v>170</v>
+      </c>
+      <c r="C6" s="2">
+        <v>55</v>
+      </c>
+      <c r="D6" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B7" s="3">
+        <v>6259</v>
+      </c>
+      <c r="C7" s="3">
+        <v>833</v>
+      </c>
+      <c r="D7" s="3">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B8" s="2">
+        <v>943</v>
+      </c>
+      <c r="C8" s="2">
+        <v>130</v>
+      </c>
+      <c r="D8" s="2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="3">
+        <v>534</v>
+      </c>
+      <c r="C9" s="3">
+        <v>87</v>
+      </c>
+      <c r="D9" s="3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="2">
+        <v>291</v>
+      </c>
+      <c r="C10" s="2">
+        <v>30</v>
+      </c>
+      <c r="D10" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="3">
+        <v>30</v>
+      </c>
+      <c r="C11" s="3">
+        <v>8</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B13" s="4">
+        <v>63</v>
+      </c>
+      <c r="C13" s="4">
+        <v>8</v>
+      </c>
+      <c r="D13" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B14" s="5">
+        <v>184</v>
+      </c>
+      <c r="C14" s="5">
+        <v>67</v>
+      </c>
+      <c r="D14" s="5">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B15" s="4">
+        <v>694</v>
+      </c>
+      <c r="C15" s="4">
+        <v>189</v>
+      </c>
+      <c r="D15" s="4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B16" s="5">
+        <v>285</v>
+      </c>
+      <c r="C16" s="5">
+        <v>205</v>
+      </c>
+      <c r="D16" s="5">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="3">
+        <v>261</v>
+      </c>
+      <c r="C17" s="3">
+        <v>108</v>
+      </c>
+      <c r="D17" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B18" s="2">
+        <v>1954</v>
+      </c>
+      <c r="C18" s="2">
+        <v>254</v>
+      </c>
+      <c r="D18" s="2">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B19" s="3">
+        <v>165</v>
+      </c>
+      <c r="C19" s="3">
+        <v>77</v>
+      </c>
+      <c r="D19" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="2">
+        <v>2034</v>
+      </c>
+      <c r="C20" s="2">
+        <v>255</v>
+      </c>
+      <c r="D20" s="2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="3">
+        <v>8</v>
+      </c>
+      <c r="C21" s="3">
+        <v>14</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B22" s="2">
+        <v>2128</v>
+      </c>
+      <c r="C22" s="2">
+        <v>252</v>
+      </c>
+      <c r="D22" s="2">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B23" s="3">
+        <v>352</v>
+      </c>
+      <c r="C23" s="3">
+        <v>162</v>
+      </c>
+      <c r="D23" s="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B24" s="2">
+        <v>1846</v>
+      </c>
+      <c r="C24" s="2">
+        <v>319</v>
+      </c>
+      <c r="D24" s="2">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B25" s="3">
+        <v>13121</v>
+      </c>
+      <c r="C25" s="3">
+        <v>1007</v>
+      </c>
+      <c r="D25" s="3">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B26" s="2">
+        <v>622</v>
+      </c>
+      <c r="C26" s="2">
+        <v>183</v>
+      </c>
+      <c r="D26" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B27" s="3">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B28" s="2">
+        <v>676</v>
+      </c>
+      <c r="C28" s="2">
+        <v>126</v>
+      </c>
+      <c r="D28" s="2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B29" s="3">
+        <v>471</v>
+      </c>
+      <c r="C29" s="3">
+        <v>63</v>
+      </c>
+      <c r="D29" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B30" s="2">
+        <v>3173</v>
+      </c>
+      <c r="C30" s="2">
+        <v>248</v>
+      </c>
+      <c r="D30" s="2">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="3">
+        <v>34</v>
+      </c>
+      <c r="C31" s="3">
+        <v>26</v>
+      </c>
+      <c r="D31" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="2">
+        <v>418</v>
+      </c>
+      <c r="C32" s="2">
+        <v>191</v>
+      </c>
+      <c r="D32" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="3">
+        <v>1695</v>
+      </c>
+      <c r="C33" s="3">
+        <v>317</v>
+      </c>
+      <c r="D33" s="3">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="2">
+        <v>1201</v>
+      </c>
+      <c r="C34" s="2">
+        <v>231</v>
+      </c>
+      <c r="D34" s="2">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="3">
+        <v>653</v>
+      </c>
+      <c r="C35" s="3">
+        <v>61</v>
+      </c>
+      <c r="D35" s="3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B36" s="2">
+        <v>5483</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1090</v>
+      </c>
+      <c r="D36" s="2">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B37" s="3">
+        <v>961</v>
+      </c>
+      <c r="C37" s="3">
+        <v>403</v>
+      </c>
+      <c r="D37" s="3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B38" s="2">
+        <v>4080</v>
+      </c>
+      <c r="C38" s="2">
+        <v>228</v>
+      </c>
+      <c r="D38" s="2">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B39" s="3">
+        <v>360</v>
+      </c>
+      <c r="C39" s="3">
+        <v>153</v>
+      </c>
+      <c r="D39" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B40" s="6">
+        <v>102</v>
+      </c>
+      <c r="C40" s="6">
+        <v>1</v>
+      </c>
+      <c r="D40" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B41" s="7">
+        <v>26</v>
+      </c>
+      <c r="C41" s="7">
+        <v>3</v>
+      </c>
+      <c r="D41" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B42" s="6">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0</v>
+      </c>
+      <c r="D42" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B43" s="7">
+        <v>0</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0</v>
+      </c>
+      <c r="D43" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B44" s="2">
+        <v>216</v>
+      </c>
+      <c r="C44" s="2">
+        <v>68</v>
+      </c>
+      <c r="D44" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B45" s="3">
+        <v>431</v>
+      </c>
+      <c r="C45" s="3">
+        <v>171</v>
+      </c>
+      <c r="D45" s="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B46" s="2">
+        <v>1833</v>
+      </c>
+      <c r="C46" s="2">
+        <v>387</v>
+      </c>
+      <c r="D46" s="2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B47" s="3">
+        <v>4979</v>
+      </c>
+      <c r="C47" s="3">
+        <v>382</v>
+      </c>
+      <c r="D47" s="3">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B48" s="2">
+        <v>1831</v>
+      </c>
+      <c r="C48" s="2">
+        <v>375</v>
+      </c>
+      <c r="D48" s="2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B49" s="3">
+        <v>738</v>
+      </c>
+      <c r="C49" s="3">
+        <v>127</v>
+      </c>
+      <c r="D49" s="3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B50" s="2">
+        <v>4667</v>
+      </c>
+      <c r="C50" s="2">
+        <v>319</v>
+      </c>
+      <c r="D50" s="2">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B51" s="3">
+        <v>478</v>
+      </c>
+      <c r="C51" s="3">
+        <v>107</v>
+      </c>
+      <c r="D51" s="3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B52" s="2">
+        <v>1176</v>
+      </c>
+      <c r="C52" s="2">
+        <v>227</v>
+      </c>
+      <c r="D52" s="2">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B53" s="3">
+        <v>140</v>
+      </c>
+      <c r="C53" s="3">
+        <v>157</v>
+      </c>
+      <c r="D53" s="3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B54" s="2">
+        <v>268</v>
+      </c>
+      <c r="C54" s="2">
+        <v>174</v>
+      </c>
+      <c r="D54" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B55" s="3">
+        <v>935</v>
+      </c>
+      <c r="C55" s="3">
+        <v>141</v>
+      </c>
+      <c r="D55" s="3">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B56" s="4">
+        <v>1226</v>
+      </c>
+      <c r="C56" s="4">
+        <v>430</v>
+      </c>
+      <c r="D56" s="4">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B57" s="7">
+        <v>130</v>
+      </c>
+      <c r="C57" s="7">
+        <v>4</v>
+      </c>
+      <c r="D57" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
+      <c r="B58" s="8">
+        <v>86748</v>
+      </c>
+      <c r="C58" s="8">
+        <v>11790</v>
+      </c>
+      <c r="D58" s="8">
+        <v>10794</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:D2" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
@@ -8974,13 +9314,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -8990,7 +9330,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -9004,7 +9344,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -9012,7 +9352,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -9020,7 +9360,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -9028,7 +9368,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -9036,7 +9376,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -9044,7 +9384,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -9052,7 +9392,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -9060,7 +9400,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -9068,7 +9408,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -9076,7 +9416,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -9084,7 +9424,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -9092,7 +9432,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -9100,7 +9440,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -9108,7 +9448,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -9116,7 +9456,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -9124,7 +9464,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -9132,7 +9472,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -9140,7 +9480,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -9148,7 +9488,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -9156,7 +9496,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -9164,7 +9504,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -9172,7 +9512,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -9180,7 +9520,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -9188,7 +9528,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -9196,7 +9536,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -9204,7 +9544,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -9212,7 +9552,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -9220,7 +9560,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -9228,7 +9568,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -9236,7 +9576,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -9244,7 +9584,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -9252,7 +9592,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -9260,7 +9600,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -9268,7 +9608,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -9276,7 +9616,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -9284,7 +9624,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -9292,7 +9632,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -9300,7 +9640,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -9308,7 +9648,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -9316,7 +9656,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -9324,7 +9664,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -9332,7 +9672,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -9340,7 +9680,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -9348,7 +9688,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -9356,7 +9696,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -9364,7 +9704,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -9372,7 +9712,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -9380,7 +9720,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -9388,7 +9728,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -9396,7 +9736,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -9404,7 +9744,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -9412,7 +9752,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -9420,7 +9760,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -9428,7 +9768,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -9436,7 +9776,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -9444,7 +9784,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -9461,13 +9801,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -9477,7 +9817,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -9491,7 +9831,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -9499,7 +9839,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -9507,7 +9847,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -9515,7 +9855,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -9523,7 +9863,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -9531,7 +9871,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -9539,7 +9879,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -9547,7 +9887,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -9555,7 +9895,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -9563,7 +9903,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -9571,7 +9911,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -9579,7 +9919,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -9587,7 +9927,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -9595,7 +9935,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -9603,7 +9943,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -9611,7 +9951,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -9619,7 +9959,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -9627,7 +9967,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -9635,7 +9975,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -9643,7 +9983,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -9651,7 +9991,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -9659,7 +9999,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -9667,7 +10007,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -9675,7 +10015,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -9683,7 +10023,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -9691,7 +10031,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -9699,7 +10039,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -9707,7 +10047,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -9715,7 +10055,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -9723,7 +10063,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -9731,7 +10071,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -9739,7 +10079,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -9747,7 +10087,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -9755,7 +10095,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -9763,7 +10103,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -9771,7 +10111,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -9779,7 +10119,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -9787,7 +10127,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -9795,7 +10135,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -9803,7 +10143,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -9811,7 +10151,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -9819,7 +10159,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -9827,7 +10167,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -9835,7 +10175,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -9843,7 +10183,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -9851,7 +10191,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -9859,7 +10199,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -9867,7 +10207,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -9875,7 +10215,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -9883,7 +10223,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -9891,7 +10231,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -9899,7 +10239,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -9907,7 +10247,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -9915,7 +10255,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -9923,7 +10263,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -9931,7 +10271,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -9948,13 +10288,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -9964,7 +10304,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -9978,7 +10318,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -9986,7 +10326,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -9994,7 +10334,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -10002,7 +10342,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -10010,7 +10350,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -10018,7 +10358,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -10026,7 +10366,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -10034,7 +10374,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -10042,7 +10382,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -10050,7 +10390,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -10058,7 +10398,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -10066,7 +10406,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -10074,7 +10414,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -10082,7 +10422,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -10090,7 +10430,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -10098,7 +10438,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -10106,7 +10446,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -10114,7 +10454,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -10122,7 +10462,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -10130,7 +10470,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -10138,7 +10478,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -10146,7 +10486,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -10154,7 +10494,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -10162,7 +10502,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -10170,7 +10510,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -10178,7 +10518,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -10186,7 +10526,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -10194,7 +10534,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -10202,7 +10542,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -10210,7 +10550,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -10218,7 +10558,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -10226,7 +10566,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -10234,7 +10574,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -10242,7 +10582,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -10250,7 +10590,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -10258,7 +10598,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -10266,7 +10606,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -10274,7 +10614,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -10282,7 +10622,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -10290,7 +10630,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -10298,7 +10638,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -10306,7 +10646,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -10314,7 +10654,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -10322,7 +10662,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -10330,7 +10670,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -10338,7 +10678,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -10346,7 +10686,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -10354,7 +10694,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -10362,7 +10702,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -10370,7 +10710,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -10378,7 +10718,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -10386,7 +10726,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -10394,7 +10734,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -10402,7 +10742,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -10410,7 +10750,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -10418,7 +10758,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>

--- a/statistics_files/nekls_executive_board/2026/2026_next_statistics.xlsx
+++ b/statistics_files/nekls_executive_board/2026/2026_next_statistics.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Staff\Documents\GitHub\next_statistics\statistics_files\nekls_executive_board\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\nekls_executive_board\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABC21763-A088-4702-9B51-9FE3DF915054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F01E27A-D295-488E-88DF-3A823DF519A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="740" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Annual totals" sheetId="1" r:id="rId1"/>
@@ -2075,13 +2075,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -2110,160 +2110,160 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="3">
         <f>SUM(January:December!B3)</f>
-        <v>22570</v>
+        <v>27824</v>
       </c>
       <c r="C3" s="3">
         <f>SUM(January:December!C3)</f>
-        <v>3390</v>
+        <v>4253</v>
       </c>
       <c r="D3" s="3">
         <f>SUM(January:December!D3)</f>
-        <v>4064</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5077</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2">
         <f>SUM(January:December!B4)</f>
-        <v>13339</v>
+        <v>16170</v>
       </c>
       <c r="C4" s="2">
         <f>SUM(January:December!C4)</f>
-        <v>1195</v>
+        <v>1544</v>
       </c>
       <c r="D4" s="2">
         <f>SUM(January:December!D4)</f>
-        <v>1903</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="3">
         <f>SUM(January:December!B5)</f>
-        <v>34923</v>
+        <v>43028</v>
       </c>
       <c r="C5" s="3">
         <f>SUM(January:December!C5)</f>
-        <v>3228</v>
+        <v>4008</v>
       </c>
       <c r="D5" s="3">
         <f>SUM(January:December!D5)</f>
-        <v>3114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3864</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="2">
         <f>SUM(January:December!B6)</f>
-        <v>448</v>
+        <v>575</v>
       </c>
       <c r="C6" s="2">
         <f>SUM(January:December!C6)</f>
-        <v>308</v>
+        <v>398</v>
       </c>
       <c r="D6" s="2">
         <f>SUM(January:December!D6)</f>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="3">
         <f>SUM(January:December!B7)</f>
-        <v>24471</v>
+        <v>30436</v>
       </c>
       <c r="C7" s="3">
         <f>SUM(January:December!C7)</f>
-        <v>3378</v>
+        <v>4163</v>
       </c>
       <c r="D7" s="3">
         <f>SUM(January:December!D7)</f>
-        <v>2985</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="2">
         <f>SUM(January:December!B8)</f>
-        <v>3611</v>
+        <v>4622</v>
       </c>
       <c r="C8" s="2">
         <f>SUM(January:December!C8)</f>
-        <v>558</v>
+        <v>682</v>
       </c>
       <c r="D8" s="2">
         <f>SUM(January:December!D8)</f>
-        <v>510</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="3">
         <f>SUM(January:December!B9)</f>
-        <v>2172</v>
+        <v>2574</v>
       </c>
       <c r="C9" s="3">
         <f>SUM(January:December!C9)</f>
-        <v>488</v>
+        <v>621</v>
       </c>
       <c r="D9" s="3">
         <f>SUM(January:December!D9)</f>
-        <v>401</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="2">
         <f>SUM(January:December!B10)</f>
-        <v>993</v>
+        <v>1225</v>
       </c>
       <c r="C10" s="2">
         <f>SUM(January:December!C10)</f>
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="D10" s="2">
         <f>SUM(January:December!D10)</f>
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="3">
         <f>SUM(January:December!B11)</f>
-        <v>173</v>
+        <v>232</v>
       </c>
       <c r="C11" s="3">
         <f>SUM(January:December!C11)</f>
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D11" s="3">
         <f>SUM(January:December!D11)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -2280,245 +2280,245 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
       <c r="B13" s="4">
         <f>SUM(January:December!B13)</f>
-        <v>125</v>
+        <v>182</v>
       </c>
       <c r="C13" s="4">
         <f>SUM(January:December!C13)</f>
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="D13" s="4">
         <f>SUM(January:December!D13)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="5">
         <f>SUM(January:December!B14)</f>
-        <v>673</v>
+        <v>882</v>
       </c>
       <c r="C14" s="5">
         <f>SUM(January:December!C14)</f>
-        <v>415</v>
+        <v>496</v>
       </c>
       <c r="D14" s="5">
         <f>SUM(January:December!D14)</f>
-        <v>214</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
       <c r="B15" s="4">
         <f>SUM(January:December!B15)</f>
-        <v>2970</v>
+        <v>3655</v>
       </c>
       <c r="C15" s="4">
         <f>SUM(January:December!C15)</f>
-        <v>886</v>
+        <v>1096</v>
       </c>
       <c r="D15" s="4">
         <f>SUM(January:December!D15)</f>
-        <v>533</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
       <c r="B16" s="5">
         <f>SUM(January:December!B16)</f>
-        <v>1209</v>
+        <v>1488</v>
       </c>
       <c r="C16" s="5">
         <f>SUM(January:December!C16)</f>
-        <v>952</v>
+        <v>1119</v>
       </c>
       <c r="D16" s="5">
         <f>SUM(January:December!D16)</f>
-        <v>192</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="3">
         <f>SUM(January:December!B17)</f>
-        <v>1105</v>
+        <v>1432</v>
       </c>
       <c r="C17" s="3">
         <f>SUM(January:December!C17)</f>
-        <v>553</v>
+        <v>646</v>
       </c>
       <c r="D17" s="3">
         <f>SUM(January:December!D17)</f>
-        <v>170</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="2">
         <f>SUM(January:December!B18)</f>
-        <v>7684</v>
+        <v>9348</v>
       </c>
       <c r="C18" s="2">
         <f>SUM(January:December!C18)</f>
-        <v>1331</v>
+        <v>1641</v>
       </c>
       <c r="D18" s="2">
         <f>SUM(January:December!D18)</f>
-        <v>1836</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2256</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="3">
         <f>SUM(January:December!B19)</f>
-        <v>726</v>
+        <v>929</v>
       </c>
       <c r="C19" s="3">
         <f>SUM(January:December!C19)</f>
-        <v>278</v>
+        <v>332</v>
       </c>
       <c r="D19" s="3">
         <f>SUM(January:December!D19)</f>
-        <v>184</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="2">
         <f>SUM(January:December!B20)</f>
-        <v>8445</v>
+        <v>10443</v>
       </c>
       <c r="C20" s="2">
         <f>SUM(January:December!C20)</f>
-        <v>958</v>
+        <v>1188</v>
       </c>
       <c r="D20" s="2">
         <f>SUM(January:December!D20)</f>
-        <v>1714</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="3">
         <f>SUM(January:December!B21)</f>
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="C21" s="3">
         <f>SUM(January:December!C21)</f>
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="D21" s="3">
         <f>SUM(January:December!D21)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
       <c r="B22" s="2">
         <f>SUM(January:December!B22)</f>
-        <v>8097</v>
+        <v>9974</v>
       </c>
       <c r="C22" s="2">
         <f>SUM(January:December!C22)</f>
-        <v>1246</v>
+        <v>1554</v>
       </c>
       <c r="D22" s="2">
         <f>SUM(January:December!D22)</f>
-        <v>1607</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B23" s="3">
         <f>SUM(January:December!B23)</f>
-        <v>1329</v>
+        <v>1703</v>
       </c>
       <c r="C23" s="3">
         <f>SUM(January:December!C23)</f>
-        <v>734</v>
+        <v>859</v>
       </c>
       <c r="D23" s="3">
         <f>SUM(January:December!D23)</f>
-        <v>265</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
       <c r="B24" s="2">
         <f>SUM(January:December!B24)</f>
-        <v>10122</v>
+        <v>13093</v>
       </c>
       <c r="C24" s="2">
         <f>SUM(January:December!C24)</f>
-        <v>1625</v>
+        <v>2062</v>
       </c>
       <c r="D24" s="2">
         <f>SUM(January:December!D24)</f>
-        <v>1939</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2369</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
       <c r="B25" s="3">
         <f>SUM(January:December!B25)</f>
-        <v>47493</v>
+        <v>58820</v>
       </c>
       <c r="C25" s="3">
         <f>SUM(January:December!C25)</f>
-        <v>4284</v>
+        <v>5279</v>
       </c>
       <c r="D25" s="3">
         <f>SUM(January:December!D25)</f>
-        <v>4985</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+        <v>6403</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B26" s="2">
         <f>SUM(January:December!B26)</f>
-        <v>2302</v>
+        <v>2906</v>
       </c>
       <c r="C26" s="2">
         <f>SUM(January:December!C26)</f>
-        <v>944</v>
+        <v>1156</v>
       </c>
       <c r="D26" s="2">
         <f>SUM(January:December!D26)</f>
-        <v>437</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -2535,531 +2535,531 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
       <c r="B28" s="2">
         <f>SUM(January:December!B28)</f>
-        <v>2459</v>
+        <v>3058</v>
       </c>
       <c r="C28" s="2">
         <f>SUM(January:December!C28)</f>
-        <v>513</v>
+        <v>606</v>
       </c>
       <c r="D28" s="2">
         <f>SUM(January:December!D28)</f>
-        <v>571</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
       <c r="B29" s="3">
         <f>SUM(January:December!B29)</f>
-        <v>1841</v>
+        <v>2228</v>
       </c>
       <c r="C29" s="3">
         <f>SUM(January:December!C29)</f>
-        <v>350</v>
+        <v>434</v>
       </c>
       <c r="D29" s="3">
         <f>SUM(January:December!D29)</f>
-        <v>461</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
       <c r="B30" s="2">
         <f>SUM(January:December!B30)</f>
-        <v>10677</v>
+        <v>13447</v>
       </c>
       <c r="C30" s="2">
         <f>SUM(January:December!C30)</f>
-        <v>1453</v>
+        <v>1736</v>
       </c>
       <c r="D30" s="2">
         <f>SUM(January:December!D30)</f>
-        <v>2041</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
       <c r="B31" s="3">
         <f>SUM(January:December!B31)</f>
-        <v>132</v>
+        <v>217</v>
       </c>
       <c r="C31" s="3">
         <f>SUM(January:December!C31)</f>
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="D31" s="3">
         <f>SUM(January:December!D31)</f>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B32" s="2">
         <f>SUM(January:December!B32)</f>
-        <v>1864</v>
+        <v>2257</v>
       </c>
       <c r="C32" s="2">
         <f>SUM(January:December!C32)</f>
-        <v>795</v>
+        <v>994</v>
       </c>
       <c r="D32" s="2">
         <f>SUM(January:December!D32)</f>
-        <v>395</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
       <c r="B33" s="3">
         <f>SUM(January:December!B33)</f>
-        <v>6648</v>
+        <v>8166</v>
       </c>
       <c r="C33" s="3">
         <f>SUM(January:December!C33)</f>
-        <v>1597</v>
+        <v>1956</v>
       </c>
       <c r="D33" s="3">
         <f>SUM(January:December!D33)</f>
-        <v>1390</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
       <c r="B34" s="2">
         <f>SUM(January:December!B34)</f>
-        <v>4595</v>
+        <v>5641</v>
       </c>
       <c r="C34" s="2">
         <f>SUM(January:December!C34)</f>
-        <v>985</v>
+        <v>1180</v>
       </c>
       <c r="D34" s="2">
         <f>SUM(January:December!D34)</f>
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
       <c r="B35" s="3">
         <f>SUM(January:December!B35)</f>
-        <v>2601</v>
+        <v>3145</v>
       </c>
       <c r="C35" s="3">
         <f>SUM(January:December!C35)</f>
-        <v>350</v>
+        <v>416</v>
       </c>
       <c r="D35" s="3">
         <f>SUM(January:December!D35)</f>
-        <v>486</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
       <c r="B36" s="2">
         <f>SUM(January:December!B36)</f>
-        <v>24863</v>
+        <v>28428</v>
       </c>
       <c r="C36" s="2">
         <f>SUM(January:December!C36)</f>
-        <v>4544</v>
+        <v>5488</v>
       </c>
       <c r="D36" s="2">
         <f>SUM(January:December!D36)</f>
-        <v>3287</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+        <v>4229</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
       <c r="B37" s="3">
         <f>SUM(January:December!B37)</f>
-        <v>3731</v>
+        <v>4552</v>
       </c>
       <c r="C37" s="3">
         <f>SUM(January:December!C37)</f>
-        <v>1787</v>
+        <v>2123</v>
       </c>
       <c r="D37" s="3">
         <f>SUM(January:December!D37)</f>
-        <v>549</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B38" s="2">
         <f>SUM(January:December!B38)</f>
-        <v>14516</v>
+        <v>17901</v>
       </c>
       <c r="C38" s="2">
         <f>SUM(January:December!C38)</f>
-        <v>1197</v>
+        <v>1390</v>
       </c>
       <c r="D38" s="2">
         <f>SUM(January:December!D38)</f>
-        <v>1632</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
       <c r="B39" s="3">
         <f>SUM(January:December!B39)</f>
-        <v>974</v>
+        <v>1271</v>
       </c>
       <c r="C39" s="3">
         <f>SUM(January:December!C39)</f>
-        <v>618</v>
+        <v>742</v>
       </c>
       <c r="D39" s="3">
         <f>SUM(January:December!D39)</f>
-        <v>119</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B40" s="6">
         <f>SUM(January:December!B40)</f>
-        <v>1449</v>
+        <v>2009</v>
       </c>
       <c r="C40" s="6">
         <f>SUM(January:December!C40)</f>
-        <v>235</v>
+        <v>292</v>
       </c>
       <c r="D40" s="6">
         <f>SUM(January:December!D40)</f>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
       <c r="B41" s="7">
         <f>SUM(January:December!B41)</f>
-        <v>6969</v>
+        <v>8969</v>
       </c>
       <c r="C41" s="7">
         <f>SUM(January:December!C41)</f>
-        <v>330</v>
+        <v>428</v>
       </c>
       <c r="D41" s="7">
         <f>SUM(January:December!D41)</f>
-        <v>333</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
       <c r="B42" s="6">
         <f>SUM(January:December!B42)</f>
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="C42" s="6">
         <f>SUM(January:December!C42)</f>
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D42" s="6">
         <f>SUM(January:December!D42)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
       <c r="B43" s="7">
         <f>SUM(January:December!B43)</f>
-        <v>898</v>
+        <v>1137</v>
       </c>
       <c r="C43" s="7">
         <f>SUM(January:December!C43)</f>
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="D43" s="7">
         <f>SUM(January:December!D43)</f>
-        <v>71</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B44" s="2">
         <f>SUM(January:December!B44)</f>
-        <v>1073</v>
+        <v>1221</v>
       </c>
       <c r="C44" s="2">
         <f>SUM(January:December!C44)</f>
-        <v>304</v>
+        <v>367</v>
       </c>
       <c r="D44" s="2">
         <f>SUM(January:December!D44)</f>
-        <v>648</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
       <c r="B45" s="3">
         <f>SUM(January:December!B45)</f>
-        <v>1552</v>
+        <v>1999</v>
       </c>
       <c r="C45" s="3">
         <f>SUM(January:December!C45)</f>
-        <v>633</v>
+        <v>780</v>
       </c>
       <c r="D45" s="3">
         <f>SUM(January:December!D45)</f>
-        <v>146</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
       <c r="B46" s="2">
         <f>SUM(January:December!B46)</f>
-        <v>7208</v>
+        <v>9034</v>
       </c>
       <c r="C46" s="2">
         <f>SUM(January:December!C46)</f>
-        <v>1818</v>
+        <v>2222</v>
       </c>
       <c r="D46" s="2">
         <f>SUM(January:December!D46)</f>
-        <v>1543</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
       <c r="B47" s="3">
         <f>SUM(January:December!B47)</f>
-        <v>15164</v>
+        <v>18083</v>
       </c>
       <c r="C47" s="3">
         <f>SUM(January:December!C47)</f>
-        <v>2112</v>
+        <v>2593</v>
       </c>
       <c r="D47" s="3">
         <f>SUM(January:December!D47)</f>
-        <v>2454</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2906</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
       <c r="B48" s="2">
         <f>SUM(January:December!B48)</f>
-        <v>5991</v>
+        <v>7614</v>
       </c>
       <c r="C48" s="2">
         <f>SUM(January:December!C48)</f>
-        <v>1710</v>
+        <v>2153</v>
       </c>
       <c r="D48" s="2">
         <f>SUM(January:December!D48)</f>
-        <v>684</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
       <c r="B49" s="3">
         <f>SUM(January:December!B49)</f>
-        <v>3649</v>
+        <v>4551</v>
       </c>
       <c r="C49" s="3">
         <f>SUM(January:December!C49)</f>
-        <v>818</v>
+        <v>992</v>
       </c>
       <c r="D49" s="3">
         <f>SUM(January:December!D49)</f>
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B50" s="2">
         <f>SUM(January:December!B50)</f>
-        <v>16433</v>
+        <v>20178</v>
       </c>
       <c r="C50" s="2">
         <f>SUM(January:December!C50)</f>
-        <v>1580</v>
+        <v>2035</v>
       </c>
       <c r="D50" s="2">
         <f>SUM(January:December!D50)</f>
-        <v>2640</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3265</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B51" s="3">
         <f>SUM(January:December!B51)</f>
-        <v>1812</v>
+        <v>2354</v>
       </c>
       <c r="C51" s="3">
         <f>SUM(January:December!C51)</f>
-        <v>504</v>
+        <v>618</v>
       </c>
       <c r="D51" s="3">
         <f>SUM(January:December!D51)</f>
-        <v>451</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
       <c r="B52" s="2">
         <f>SUM(January:December!B52)</f>
-        <v>5435</v>
+        <v>6693</v>
       </c>
       <c r="C52" s="2">
         <f>SUM(January:December!C52)</f>
-        <v>1083</v>
+        <v>1331</v>
       </c>
       <c r="D52" s="2">
         <f>SUM(January:December!D52)</f>
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B53" s="3">
         <f>SUM(January:December!B53)</f>
-        <v>789</v>
+        <v>1001</v>
       </c>
       <c r="C53" s="3">
         <f>SUM(January:December!C53)</f>
-        <v>703</v>
+        <v>867</v>
       </c>
       <c r="D53" s="3">
         <f>SUM(January:December!D53)</f>
-        <v>339</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
       <c r="B54" s="2">
         <f>SUM(January:December!B54)</f>
-        <v>941</v>
+        <v>1271</v>
       </c>
       <c r="C54" s="2">
         <f>SUM(January:December!C54)</f>
-        <v>779</v>
+        <v>952</v>
       </c>
       <c r="D54" s="2">
         <f>SUM(January:December!D54)</f>
-        <v>78</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
       <c r="B55" s="3">
         <f>SUM(January:December!B55)</f>
-        <v>2965</v>
+        <v>3668</v>
       </c>
       <c r="C55" s="3">
         <f>SUM(January:December!C55)</f>
-        <v>646</v>
+        <v>765</v>
       </c>
       <c r="D55" s="3">
         <f>SUM(January:December!D55)</f>
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
       <c r="B56" s="4">
         <f>SUM(January:December!B56)</f>
-        <v>4977</v>
+        <v>6207</v>
       </c>
       <c r="C56" s="4">
         <f>SUM(January:December!C56)</f>
-        <v>2184</v>
+        <v>2645</v>
       </c>
       <c r="D56" s="4">
         <f>SUM(January:December!D56)</f>
-        <v>778</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
       <c r="B57" s="7">
         <f>SUM(January:December!B57)</f>
-        <v>9463</v>
+        <v>12288</v>
       </c>
       <c r="C57" s="7">
         <f>SUM(January:December!C57)</f>
-        <v>656</v>
+        <v>832</v>
       </c>
       <c r="D57" s="7">
         <f>SUM(January:December!D57)</f>
-        <v>385</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
       <c r="B58" s="8">
         <f>SUM(January:December!B58)</f>
-        <v>342462</v>
+        <v>421933</v>
       </c>
       <c r="C58" s="8">
         <f>SUM(January:December!C58)</f>
-        <v>54929</v>
+        <v>67459</v>
       </c>
       <c r="D58" s="8">
         <f>SUM(January:December!D58)</f>
-        <v>52577</v>
+        <v>65135</v>
       </c>
     </row>
   </sheetData>
@@ -3557,13 +3557,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -3587,7 +3587,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -3595,7 +3595,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -3603,7 +3603,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -3611,7 +3611,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -3619,7 +3619,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -3627,7 +3627,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -3635,7 +3635,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -3643,7 +3643,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -3651,7 +3651,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -3659,7 +3659,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -3667,7 +3667,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -3675,7 +3675,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -3683,7 +3683,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -3691,7 +3691,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -3699,7 +3699,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -3707,7 +3707,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -3715,7 +3715,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -3723,7 +3723,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -3731,7 +3731,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -3739,7 +3739,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -3747,7 +3747,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -3755,7 +3755,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -3763,7 +3763,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -3771,7 +3771,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -3779,7 +3779,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -3787,7 +3787,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -3795,7 +3795,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -3803,7 +3803,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -3811,7 +3811,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -3819,7 +3819,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -3827,7 +3827,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -3835,7 +3835,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -3843,7 +3843,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -3851,7 +3851,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -3859,7 +3859,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -3867,7 +3867,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -3875,7 +3875,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -3883,7 +3883,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -3891,7 +3891,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -3899,7 +3899,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -3907,7 +3907,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -3915,7 +3915,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -3923,7 +3923,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -3931,7 +3931,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -3939,7 +3939,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -3947,7 +3947,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -3955,7 +3955,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -3963,7 +3963,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -3971,7 +3971,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -3979,7 +3979,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -3987,7 +3987,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -3995,7 +3995,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -4003,7 +4003,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -4011,7 +4011,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -4019,7 +4019,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -4027,7 +4027,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -4044,13 +4044,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -4074,7 +4074,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -4082,7 +4082,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -4090,7 +4090,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -4098,7 +4098,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -4106,7 +4106,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -4114,7 +4114,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -4122,7 +4122,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -4130,7 +4130,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -4138,7 +4138,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -4146,7 +4146,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -4154,7 +4154,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -4162,7 +4162,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -4170,7 +4170,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -4178,7 +4178,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -4186,7 +4186,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -4194,7 +4194,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -4202,7 +4202,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -4210,7 +4210,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -4218,7 +4218,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -4226,7 +4226,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -4234,7 +4234,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -4242,7 +4242,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -4250,7 +4250,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -4258,7 +4258,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -4266,7 +4266,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -4274,7 +4274,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -4282,7 +4282,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -4290,7 +4290,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -4298,7 +4298,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -4306,7 +4306,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -4314,7 +4314,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -4322,7 +4322,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -4330,7 +4330,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -4338,7 +4338,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -4346,7 +4346,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -4354,7 +4354,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -4362,7 +4362,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -4370,7 +4370,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -4378,7 +4378,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -4386,7 +4386,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -4394,7 +4394,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -4402,7 +4402,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -4410,7 +4410,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -4418,7 +4418,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -4426,7 +4426,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -4434,7 +4434,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -4442,7 +4442,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -4450,7 +4450,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -4458,7 +4458,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -4466,7 +4466,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -4474,7 +4474,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -4482,7 +4482,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -4490,7 +4490,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -4498,7 +4498,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -4506,7 +4506,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -4514,7 +4514,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -4531,13 +4531,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -4561,7 +4561,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -4569,7 +4569,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -4577,7 +4577,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -4585,7 +4585,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -4593,7 +4593,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -4601,7 +4601,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -4609,7 +4609,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -4617,7 +4617,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -4625,7 +4625,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -4633,7 +4633,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -4641,7 +4641,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -4649,7 +4649,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -4657,7 +4657,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -4665,7 +4665,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -4673,7 +4673,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -4681,7 +4681,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -4689,7 +4689,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -4697,7 +4697,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -4705,7 +4705,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -4713,7 +4713,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -4721,7 +4721,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -4729,7 +4729,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -4737,7 +4737,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -4745,7 +4745,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -4753,7 +4753,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -4761,7 +4761,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -4769,7 +4769,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -4777,7 +4777,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -4785,7 +4785,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -4793,7 +4793,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -4801,7 +4801,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -4809,7 +4809,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -4817,7 +4817,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -4825,7 +4825,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -4833,7 +4833,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -4841,7 +4841,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -4849,7 +4849,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -4857,7 +4857,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -4865,7 +4865,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -4873,7 +4873,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -4881,7 +4881,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -4889,7 +4889,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -4897,7 +4897,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -4905,7 +4905,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -4913,7 +4913,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -4921,7 +4921,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -4929,7 +4929,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -4937,7 +4937,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -4945,7 +4945,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -4953,7 +4953,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -4961,7 +4961,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -4969,7 +4969,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -4977,7 +4977,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -4985,7 +4985,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -4993,7 +4993,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -5001,7 +5001,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -5018,13 +5018,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -5048,7 +5048,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -5056,7 +5056,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -5064,7 +5064,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -5072,7 +5072,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -5080,7 +5080,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -5088,7 +5088,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -5096,7 +5096,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -5104,7 +5104,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -5112,7 +5112,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -5120,7 +5120,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -5128,7 +5128,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -5136,7 +5136,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -5144,7 +5144,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -5152,7 +5152,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -5160,7 +5160,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -5168,7 +5168,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -5176,7 +5176,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -5184,7 +5184,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -5192,7 +5192,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -5200,7 +5200,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -5208,7 +5208,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -5216,7 +5216,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -5224,7 +5224,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -5232,7 +5232,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -5240,7 +5240,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -5248,7 +5248,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -5256,7 +5256,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -5264,7 +5264,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -5272,7 +5272,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -5280,7 +5280,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -5288,7 +5288,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -5296,7 +5296,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -5304,7 +5304,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -5312,7 +5312,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -5320,7 +5320,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -5328,7 +5328,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -5336,7 +5336,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -5344,7 +5344,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -5352,7 +5352,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -5360,7 +5360,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -5368,7 +5368,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -5376,7 +5376,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -5384,7 +5384,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -5392,7 +5392,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -5400,7 +5400,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -5408,7 +5408,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -5416,7 +5416,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -5424,7 +5424,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -5432,7 +5432,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -5440,7 +5440,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -5448,7 +5448,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -5456,7 +5456,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -5464,7 +5464,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -5472,7 +5472,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -5480,7 +5480,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -5488,7 +5488,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -5504,13 +5504,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -5524,7 +5524,7 @@
         <v>46053</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -5538,7 +5538,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -5566,7 +5566,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -5580,7 +5580,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -5594,7 +5594,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -5608,7 +5608,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -5622,7 +5622,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -5636,7 +5636,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -5650,7 +5650,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -5678,7 +5678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -5692,7 +5692,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -5706,7 +5706,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -5720,7 +5720,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -5734,7 +5734,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -5748,7 +5748,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -5762,7 +5762,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -5776,7 +5776,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -5790,7 +5790,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -5804,7 +5804,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -5818,7 +5818,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -5832,7 +5832,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -5846,7 +5846,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -5860,7 +5860,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -5874,7 +5874,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -5888,7 +5888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -5902,7 +5902,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -5916,7 +5916,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -5930,7 +5930,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -5944,7 +5944,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -5958,7 +5958,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -5986,7 +5986,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -6000,7 +6000,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -6014,7 +6014,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -6028,7 +6028,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -6042,7 +6042,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -6056,7 +6056,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -6070,7 +6070,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -6084,7 +6084,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -6098,7 +6098,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -6112,7 +6112,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -6126,7 +6126,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -6140,7 +6140,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -6154,7 +6154,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -6168,7 +6168,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -6182,7 +6182,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -6196,7 +6196,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -6210,7 +6210,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -6224,7 +6224,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -6238,7 +6238,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -6252,7 +6252,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -6266,7 +6266,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -6280,7 +6280,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -6294,7 +6294,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -6308,7 +6308,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -6331,13 +6331,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -6351,7 +6351,7 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -6365,7 +6365,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -6379,7 +6379,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -6393,7 +6393,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -6407,7 +6407,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -6421,7 +6421,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -6435,7 +6435,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -6449,7 +6449,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -6463,7 +6463,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -6477,7 +6477,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -6491,7 +6491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -6505,7 +6505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -6519,7 +6519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -6533,7 +6533,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -6547,7 +6547,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -6561,7 +6561,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -6575,7 +6575,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -6589,7 +6589,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -6603,7 +6603,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -6617,7 +6617,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -6631,7 +6631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -6645,7 +6645,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -6659,7 +6659,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -6673,7 +6673,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -6687,7 +6687,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -6701,7 +6701,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -6715,7 +6715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -6729,7 +6729,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -6757,7 +6757,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -6771,7 +6771,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -6785,7 +6785,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -6799,7 +6799,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -6813,7 +6813,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -6827,7 +6827,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -6841,7 +6841,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -6855,7 +6855,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -6869,7 +6869,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -6883,7 +6883,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -6897,7 +6897,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -6911,7 +6911,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -6925,7 +6925,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -6939,7 +6939,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -6953,7 +6953,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -6967,7 +6967,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -6981,7 +6981,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -6995,7 +6995,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -7009,7 +7009,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -7023,7 +7023,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -7037,7 +7037,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -7051,7 +7051,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -7065,7 +7065,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -7079,7 +7079,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -7093,7 +7093,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -7107,7 +7107,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -7121,7 +7121,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -7135,7 +7135,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -7158,13 +7158,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D59"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -7178,7 +7178,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -7192,7 +7192,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -7206,7 +7206,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -7220,7 +7220,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -7234,7 +7234,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -7248,7 +7248,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -7262,7 +7262,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -7276,7 +7276,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -7290,7 +7290,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -7304,7 +7304,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -7318,7 +7318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -7332,7 +7332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -7346,7 +7346,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -7360,7 +7360,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -7374,7 +7374,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -7388,7 +7388,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -7402,7 +7402,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -7416,7 +7416,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -7430,7 +7430,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -7444,7 +7444,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -7458,7 +7458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -7472,7 +7472,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -7486,7 +7486,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -7500,7 +7500,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -7514,7 +7514,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -7528,7 +7528,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -7542,7 +7542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -7556,7 +7556,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -7570,7 +7570,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -7584,7 +7584,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -7598,7 +7598,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -7612,7 +7612,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -7626,7 +7626,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -7640,7 +7640,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -7654,7 +7654,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -7668,7 +7668,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -7682,7 +7682,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -7696,7 +7696,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -7710,7 +7710,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -7724,7 +7724,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -7738,7 +7738,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -7752,7 +7752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -7766,7 +7766,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -7780,7 +7780,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -7794,7 +7794,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -7808,7 +7808,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -7822,7 +7822,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -7836,7 +7836,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -7850,7 +7850,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -7864,7 +7864,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -7878,7 +7878,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -7892,7 +7892,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -7906,7 +7906,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -7920,7 +7920,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -7934,7 +7934,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -7948,7 +7948,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -7962,7 +7962,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -7976,7 +7976,7 @@
         <v>13832</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>61</v>
       </c>
@@ -7999,24 +7999,28 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D61"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="19"/>
+      <c r="B1" s="19">
+        <v>46113</v>
+      </c>
       <c r="C1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="21"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D1" s="21">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -8030,453 +8034,794 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B3" s="3">
+        <v>5254</v>
+      </c>
+      <c r="C3" s="3">
+        <v>863</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>2831</v>
+      </c>
+      <c r="C4" s="2">
+        <v>349</v>
+      </c>
+      <c r="D4" s="2">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B5" s="3">
+        <v>8105</v>
+      </c>
+      <c r="C5" s="3">
+        <v>780</v>
+      </c>
+      <c r="D5" s="3">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>127</v>
+      </c>
+      <c r="C6" s="2">
+        <v>90</v>
+      </c>
+      <c r="D6" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="3">
+        <v>5965</v>
+      </c>
+      <c r="C7" s="3">
+        <v>785</v>
+      </c>
+      <c r="D7" s="3">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <v>1011</v>
+      </c>
+      <c r="C8" s="2">
+        <v>124</v>
+      </c>
+      <c r="D8" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="3">
+        <v>402</v>
+      </c>
+      <c r="C9" s="3">
+        <v>133</v>
+      </c>
+      <c r="D9" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
+        <v>232</v>
+      </c>
+      <c r="C10" s="2">
+        <v>43</v>
+      </c>
+      <c r="D10" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="3">
+        <v>59</v>
+      </c>
+      <c r="C11" s="3">
+        <v>13</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B13" s="4">
+        <v>57</v>
+      </c>
+      <c r="C13" s="4">
+        <v>37</v>
+      </c>
+      <c r="D13" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B14" s="5">
+        <v>209</v>
+      </c>
+      <c r="C14" s="5">
+        <v>81</v>
+      </c>
+      <c r="D14" s="5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B15" s="4">
+        <v>685</v>
+      </c>
+      <c r="C15" s="4">
+        <v>210</v>
+      </c>
+      <c r="D15" s="4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B16" s="5">
+        <v>279</v>
+      </c>
+      <c r="C16" s="5">
+        <v>167</v>
+      </c>
+      <c r="D16" s="5">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B17" s="3">
+        <v>327</v>
+      </c>
+      <c r="C17" s="3">
+        <v>93</v>
+      </c>
+      <c r="D17" s="3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B18" s="2">
+        <v>1664</v>
+      </c>
+      <c r="C18" s="2">
+        <v>310</v>
+      </c>
+      <c r="D18" s="2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="3">
+        <v>203</v>
+      </c>
+      <c r="C19" s="3">
+        <v>54</v>
+      </c>
+      <c r="D19" s="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="2">
+        <v>1998</v>
+      </c>
+      <c r="C20" s="2">
+        <v>230</v>
+      </c>
+      <c r="D20" s="2">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B21" s="3">
+        <v>20</v>
+      </c>
+      <c r="C21" s="3">
+        <v>26</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B22" s="2">
+        <v>1877</v>
+      </c>
+      <c r="C22" s="2">
+        <v>308</v>
+      </c>
+      <c r="D22" s="2">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B23" s="3">
+        <v>374</v>
+      </c>
+      <c r="C23" s="3">
+        <v>125</v>
+      </c>
+      <c r="D23" s="3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B24" s="2">
+        <v>2971</v>
+      </c>
+      <c r="C24" s="2">
+        <v>437</v>
+      </c>
+      <c r="D24" s="2">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B25" s="3">
+        <v>11327</v>
+      </c>
+      <c r="C25" s="3">
+        <v>995</v>
+      </c>
+      <c r="D25" s="3">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B26" s="2">
+        <v>604</v>
+      </c>
+      <c r="C26" s="2">
+        <v>212</v>
+      </c>
+      <c r="D26" s="2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B27" s="3">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B28" s="2">
+        <v>599</v>
+      </c>
+      <c r="C28" s="2">
+        <v>93</v>
+      </c>
+      <c r="D28" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B29" s="3">
+        <v>387</v>
+      </c>
+      <c r="C29" s="3">
+        <v>84</v>
+      </c>
+      <c r="D29" s="3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B30" s="2">
+        <v>2770</v>
+      </c>
+      <c r="C30" s="2">
+        <v>283</v>
+      </c>
+      <c r="D30" s="2">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B31" s="3">
+        <v>85</v>
+      </c>
+      <c r="C31" s="3">
+        <v>18</v>
+      </c>
+      <c r="D31" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B32" s="2">
+        <v>393</v>
+      </c>
+      <c r="C32" s="2">
+        <v>199</v>
+      </c>
+      <c r="D32" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B33" s="3">
+        <v>1518</v>
+      </c>
+      <c r="C33" s="3">
+        <v>359</v>
+      </c>
+      <c r="D33" s="3">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B34" s="2">
+        <v>1046</v>
+      </c>
+      <c r="C34" s="2">
+        <v>195</v>
+      </c>
+      <c r="D34" s="2">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B35" s="3">
+        <v>544</v>
+      </c>
+      <c r="C35" s="3">
+        <v>66</v>
+      </c>
+      <c r="D35" s="3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B36" s="2">
+        <v>3565</v>
+      </c>
+      <c r="C36" s="2">
+        <v>944</v>
+      </c>
+      <c r="D36" s="2">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B37" s="3">
+        <v>821</v>
+      </c>
+      <c r="C37" s="3">
+        <v>336</v>
+      </c>
+      <c r="D37" s="3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B38" s="2">
+        <v>3385</v>
+      </c>
+      <c r="C38" s="2">
+        <v>193</v>
+      </c>
+      <c r="D38" s="2">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B39" s="3">
+        <v>297</v>
+      </c>
+      <c r="C39" s="3">
+        <v>124</v>
+      </c>
+      <c r="D39" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B40" s="6">
+        <v>560</v>
+      </c>
+      <c r="C40" s="6">
+        <v>57</v>
+      </c>
+      <c r="D40" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B41" s="7">
+        <v>2000</v>
+      </c>
+      <c r="C41" s="7">
+        <v>98</v>
+      </c>
+      <c r="D41" s="7">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B42" s="6">
+        <v>26</v>
+      </c>
+      <c r="C42" s="6">
+        <v>18</v>
+      </c>
+      <c r="D42" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B43" s="7">
+        <v>239</v>
+      </c>
+      <c r="C43" s="7">
+        <v>13</v>
+      </c>
+      <c r="D43" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B44" s="2">
+        <v>148</v>
+      </c>
+      <c r="C44" s="2">
+        <v>63</v>
+      </c>
+      <c r="D44" s="2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B45" s="3">
+        <v>447</v>
+      </c>
+      <c r="C45" s="3">
+        <v>147</v>
+      </c>
+      <c r="D45" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B46" s="2">
+        <v>1826</v>
+      </c>
+      <c r="C46" s="2">
+        <v>404</v>
+      </c>
+      <c r="D46" s="2">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B47" s="3">
+        <v>2919</v>
+      </c>
+      <c r="C47" s="3">
+        <v>481</v>
+      </c>
+      <c r="D47" s="3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B48" s="2">
+        <v>1623</v>
+      </c>
+      <c r="C48" s="2">
+        <v>443</v>
+      </c>
+      <c r="D48" s="2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B49" s="3">
+        <v>902</v>
+      </c>
+      <c r="C49" s="3">
+        <v>174</v>
+      </c>
+      <c r="D49" s="3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B50" s="2">
+        <v>3745</v>
+      </c>
+      <c r="C50" s="2">
+        <v>455</v>
+      </c>
+      <c r="D50" s="2">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B51" s="3">
+        <v>542</v>
+      </c>
+      <c r="C51" s="3">
+        <v>114</v>
+      </c>
+      <c r="D51" s="3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B52" s="2">
+        <v>1258</v>
+      </c>
+      <c r="C52" s="2">
+        <v>248</v>
+      </c>
+      <c r="D52" s="2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B53" s="3">
+        <v>212</v>
+      </c>
+      <c r="C53" s="3">
+        <v>164</v>
+      </c>
+      <c r="D53" s="3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B54" s="2">
+        <v>330</v>
+      </c>
+      <c r="C54" s="2">
+        <v>173</v>
+      </c>
+      <c r="D54" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B55" s="3">
+        <v>703</v>
+      </c>
+      <c r="C55" s="3">
+        <v>119</v>
+      </c>
+      <c r="D55" s="3">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B56" s="4">
+        <v>1230</v>
+      </c>
+      <c r="C56" s="4">
+        <v>461</v>
+      </c>
+      <c r="D56" s="4">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B57" s="7">
+        <v>2825</v>
+      </c>
+      <c r="C57" s="7">
+        <v>176</v>
+      </c>
+      <c r="D57" s="7">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
+      <c r="B58" s="8">
+        <v>79471</v>
+      </c>
+      <c r="C58" s="8">
+        <v>12530</v>
+      </c>
+      <c r="D58" s="8">
+        <v>12558</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B61">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:D2" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
@@ -8487,13 +8832,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -8507,7 +8852,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -8521,7 +8866,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -8535,7 +8880,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -8549,7 +8894,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -8563,7 +8908,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -8577,7 +8922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -8591,7 +8936,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -8605,7 +8950,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -8619,7 +8964,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -8633,7 +8978,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -8647,7 +8992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -8661,7 +9006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -8675,7 +9020,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -8689,7 +9034,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -8703,7 +9048,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -8717,7 +9062,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -8731,7 +9076,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -8745,7 +9090,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -8759,7 +9104,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -8773,7 +9118,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -8787,7 +9132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -8801,7 +9146,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -8815,7 +9160,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -8829,7 +9174,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -8843,7 +9188,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -8857,7 +9202,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -8871,7 +9216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -8885,7 +9230,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -8899,7 +9244,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -8913,7 +9258,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -8927,7 +9272,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -8941,7 +9286,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -8955,7 +9300,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -8969,7 +9314,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -8983,7 +9328,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -8997,7 +9342,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -9011,7 +9356,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -9025,7 +9370,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -9039,7 +9384,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -9053,7 +9398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -9067,7 +9412,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -9081,7 +9426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -9095,7 +9440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -9109,7 +9454,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -9123,7 +9468,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -9137,7 +9482,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -9151,7 +9496,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -9165,7 +9510,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -9179,7 +9524,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -9193,7 +9538,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -9207,7 +9552,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -9221,7 +9566,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -9235,7 +9580,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -9249,7 +9594,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -9263,7 +9608,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -9277,7 +9622,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -9291,7 +9636,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -9314,13 +9659,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -9330,7 +9675,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -9344,7 +9689,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -9352,7 +9697,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -9360,7 +9705,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -9368,7 +9713,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -9376,7 +9721,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -9384,7 +9729,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -9392,7 +9737,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -9400,7 +9745,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -9408,7 +9753,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -9416,7 +9761,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -9424,7 +9769,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -9432,7 +9777,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -9440,7 +9785,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -9448,7 +9793,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -9456,7 +9801,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -9464,7 +9809,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -9472,7 +9817,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -9480,7 +9825,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -9488,7 +9833,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -9496,7 +9841,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -9504,7 +9849,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -9512,7 +9857,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -9520,7 +9865,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -9528,7 +9873,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -9536,7 +9881,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -9544,7 +9889,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -9552,7 +9897,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -9560,7 +9905,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -9568,7 +9913,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -9576,7 +9921,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -9584,7 +9929,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -9592,7 +9937,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -9600,7 +9945,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -9608,7 +9953,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -9616,7 +9961,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -9624,7 +9969,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -9632,7 +9977,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -9640,7 +9985,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -9648,7 +9993,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -9656,7 +10001,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -9664,7 +10009,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -9672,7 +10017,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -9680,7 +10025,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -9688,7 +10033,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -9696,7 +10041,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -9704,7 +10049,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -9712,7 +10057,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -9720,7 +10065,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -9728,7 +10073,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -9736,7 +10081,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -9744,7 +10089,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -9752,7 +10097,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -9760,7 +10105,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -9768,7 +10113,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -9776,7 +10121,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -9784,7 +10129,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -9801,13 +10146,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -9817,7 +10162,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -9831,7 +10176,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -9839,7 +10184,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -9847,7 +10192,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -9855,7 +10200,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -9863,7 +10208,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -9871,7 +10216,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -9879,7 +10224,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -9887,7 +10232,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -9895,7 +10240,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -9903,7 +10248,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -9911,7 +10256,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -9919,7 +10264,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -9927,7 +10272,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -9935,7 +10280,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -9943,7 +10288,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -9951,7 +10296,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -9959,7 +10304,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -9967,7 +10312,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -9975,7 +10320,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -9983,7 +10328,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -9991,7 +10336,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -9999,7 +10344,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -10007,7 +10352,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -10015,7 +10360,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -10023,7 +10368,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -10031,7 +10376,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -10039,7 +10384,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -10047,7 +10392,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -10055,7 +10400,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -10063,7 +10408,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -10071,7 +10416,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -10079,7 +10424,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -10087,7 +10432,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -10095,7 +10440,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -10103,7 +10448,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -10111,7 +10456,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -10119,7 +10464,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -10127,7 +10472,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -10135,7 +10480,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -10143,7 +10488,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -10151,7 +10496,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -10159,7 +10504,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -10167,7 +10512,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -10175,7 +10520,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -10183,7 +10528,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -10191,7 +10536,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -10199,7 +10544,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -10207,7 +10552,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -10215,7 +10560,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -10223,7 +10568,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -10231,7 +10576,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -10239,7 +10584,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -10247,7 +10592,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -10255,7 +10600,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -10263,7 +10608,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -10271,7 +10616,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -10288,13 +10633,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -10304,7 +10649,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -10318,7 +10663,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -10326,7 +10671,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -10334,7 +10679,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -10342,7 +10687,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -10350,7 +10695,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -10358,7 +10703,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -10366,7 +10711,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -10374,7 +10719,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -10382,7 +10727,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -10390,7 +10735,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -10398,7 +10743,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -10406,7 +10751,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -10414,7 +10759,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -10422,7 +10767,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -10430,7 +10775,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -10438,7 +10783,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -10446,7 +10791,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -10454,7 +10799,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -10462,7 +10807,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -10470,7 +10815,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -10478,7 +10823,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -10486,7 +10831,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -10494,7 +10839,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -10502,7 +10847,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -10510,7 +10855,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -10518,7 +10863,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -10526,7 +10871,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -10534,7 +10879,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -10542,7 +10887,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -10550,7 +10895,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -10558,7 +10903,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -10566,7 +10911,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -10574,7 +10919,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -10582,7 +10927,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -10590,7 +10935,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -10598,7 +10943,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -10606,7 +10951,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -10614,7 +10959,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -10622,7 +10967,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -10630,7 +10975,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -10638,7 +10983,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -10646,7 +10991,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -10654,7 +10999,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -10662,7 +11007,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -10670,7 +11015,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -10678,7 +11023,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -10686,7 +11031,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -10694,7 +11039,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -10702,7 +11047,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -10710,7 +11055,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -10718,7 +11063,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -10726,7 +11071,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -10734,7 +11079,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -10742,7 +11087,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -10750,7 +11095,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -10758,7 +11103,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>

--- a/statistics_files/nekls_executive_board/2026/2026_next_statistics.xlsx
+++ b/statistics_files/nekls_executive_board/2026/2026_next_statistics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\nekls_executive_board\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F01E27A-D295-488E-88DF-3A823DF519A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6748CD7-CC2E-4F32-AC28-381A70CDE13C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Annual totals" sheetId="1" r:id="rId1"/>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="D1" s="21">
         <f>MAX(January:December!D1)</f>
-        <v>46173</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2116,15 +2116,15 @@
       </c>
       <c r="B3" s="3">
         <f>SUM(January:December!B3)</f>
-        <v>27824</v>
+        <v>34705</v>
       </c>
       <c r="C3" s="3">
         <f>SUM(January:December!C3)</f>
-        <v>4253</v>
+        <v>5068</v>
       </c>
       <c r="D3" s="3">
         <f>SUM(January:December!D3)</f>
-        <v>5077</v>
+        <v>6123</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2133,15 +2133,15 @@
       </c>
       <c r="B4" s="2">
         <f>SUM(January:December!B4)</f>
-        <v>16170</v>
+        <v>20342</v>
       </c>
       <c r="C4" s="2">
         <f>SUM(January:December!C4)</f>
-        <v>1544</v>
+        <v>1788</v>
       </c>
       <c r="D4" s="2">
         <f>SUM(January:December!D4)</f>
-        <v>2295</v>
+        <v>2872</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2150,15 +2150,15 @@
       </c>
       <c r="B5" s="3">
         <f>SUM(January:December!B5)</f>
-        <v>43028</v>
+        <v>53605</v>
       </c>
       <c r="C5" s="3">
         <f>SUM(January:December!C5)</f>
-        <v>4008</v>
+        <v>4755</v>
       </c>
       <c r="D5" s="3">
         <f>SUM(January:December!D5)</f>
-        <v>3864</v>
+        <v>4722</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2167,15 +2167,15 @@
       </c>
       <c r="B6" s="2">
         <f>SUM(January:December!B6)</f>
-        <v>575</v>
+        <v>999</v>
       </c>
       <c r="C6" s="2">
         <f>SUM(January:December!C6)</f>
-        <v>398</v>
+        <v>476</v>
       </c>
       <c r="D6" s="2">
         <f>SUM(January:December!D6)</f>
-        <v>48</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2184,15 +2184,15 @@
       </c>
       <c r="B7" s="3">
         <f>SUM(January:December!B7)</f>
-        <v>30436</v>
+        <v>38047</v>
       </c>
       <c r="C7" s="3">
         <f>SUM(January:December!C7)</f>
-        <v>4163</v>
+        <v>4885</v>
       </c>
       <c r="D7" s="3">
         <f>SUM(January:December!D7)</f>
-        <v>3640</v>
+        <v>4374</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2201,15 +2201,15 @@
       </c>
       <c r="B8" s="2">
         <f>SUM(January:December!B8)</f>
-        <v>4622</v>
+        <v>5255</v>
       </c>
       <c r="C8" s="2">
         <f>SUM(January:December!C8)</f>
-        <v>682</v>
+        <v>823</v>
       </c>
       <c r="D8" s="2">
         <f>SUM(January:December!D8)</f>
-        <v>710</v>
+        <v>822</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2218,15 +2218,15 @@
       </c>
       <c r="B9" s="3">
         <f>SUM(January:December!B9)</f>
-        <v>2574</v>
+        <v>3209</v>
       </c>
       <c r="C9" s="3">
         <f>SUM(January:December!C9)</f>
-        <v>621</v>
+        <v>758</v>
       </c>
       <c r="D9" s="3">
         <f>SUM(January:December!D9)</f>
-        <v>481</v>
+        <v>554</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2235,15 +2235,15 @@
       </c>
       <c r="B10" s="2">
         <f>SUM(January:December!B10)</f>
-        <v>1225</v>
+        <v>1641</v>
       </c>
       <c r="C10" s="2">
         <f>SUM(January:December!C10)</f>
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="D10" s="2">
         <f>SUM(January:December!D10)</f>
-        <v>106</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2252,11 +2252,11 @@
       </c>
       <c r="B11" s="3">
         <f>SUM(January:December!B11)</f>
-        <v>232</v>
+        <v>317</v>
       </c>
       <c r="C11" s="3">
         <f>SUM(January:December!C11)</f>
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D11" s="3">
         <f>SUM(January:December!D11)</f>
@@ -2286,15 +2286,15 @@
       </c>
       <c r="B13" s="4">
         <f>SUM(January:December!B13)</f>
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="C13" s="4">
         <f>SUM(January:December!C13)</f>
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="D13" s="4">
         <f>SUM(January:December!D13)</f>
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2303,15 +2303,15 @@
       </c>
       <c r="B14" s="5">
         <f>SUM(January:December!B14)</f>
-        <v>882</v>
+        <v>1072</v>
       </c>
       <c r="C14" s="5">
         <f>SUM(January:December!C14)</f>
-        <v>496</v>
+        <v>577</v>
       </c>
       <c r="D14" s="5">
         <f>SUM(January:December!D14)</f>
-        <v>273</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2320,15 +2320,15 @@
       </c>
       <c r="B15" s="4">
         <f>SUM(January:December!B15)</f>
-        <v>3655</v>
+        <v>4360</v>
       </c>
       <c r="C15" s="4">
         <f>SUM(January:December!C15)</f>
-        <v>1096</v>
+        <v>1362</v>
       </c>
       <c r="D15" s="4">
         <f>SUM(January:December!D15)</f>
-        <v>640</v>
+        <v>742</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2337,15 +2337,15 @@
       </c>
       <c r="B16" s="5">
         <f>SUM(January:December!B16)</f>
-        <v>1488</v>
+        <v>1924</v>
       </c>
       <c r="C16" s="5">
         <f>SUM(January:December!C16)</f>
-        <v>1119</v>
+        <v>1327</v>
       </c>
       <c r="D16" s="5">
         <f>SUM(January:December!D16)</f>
-        <v>226</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2354,15 +2354,15 @@
       </c>
       <c r="B17" s="3">
         <f>SUM(January:December!B17)</f>
-        <v>1432</v>
+        <v>1795</v>
       </c>
       <c r="C17" s="3">
         <f>SUM(January:December!C17)</f>
-        <v>646</v>
+        <v>760</v>
       </c>
       <c r="D17" s="3">
         <f>SUM(January:December!D17)</f>
-        <v>237</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2371,15 +2371,15 @@
       </c>
       <c r="B18" s="2">
         <f>SUM(January:December!B18)</f>
-        <v>9348</v>
+        <v>12123</v>
       </c>
       <c r="C18" s="2">
         <f>SUM(January:December!C18)</f>
-        <v>1641</v>
+        <v>1979</v>
       </c>
       <c r="D18" s="2">
         <f>SUM(January:December!D18)</f>
-        <v>2256</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2388,15 +2388,15 @@
       </c>
       <c r="B19" s="3">
         <f>SUM(January:December!B19)</f>
-        <v>929</v>
+        <v>1115</v>
       </c>
       <c r="C19" s="3">
         <f>SUM(January:December!C19)</f>
-        <v>332</v>
+        <v>393</v>
       </c>
       <c r="D19" s="3">
         <f>SUM(January:December!D19)</f>
-        <v>238</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2405,15 +2405,15 @@
       </c>
       <c r="B20" s="2">
         <f>SUM(January:December!B20)</f>
-        <v>10443</v>
+        <v>12992</v>
       </c>
       <c r="C20" s="2">
         <f>SUM(January:December!C20)</f>
-        <v>1188</v>
+        <v>1450</v>
       </c>
       <c r="D20" s="2">
         <f>SUM(January:December!D20)</f>
-        <v>2011</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2422,11 +2422,11 @@
       </c>
       <c r="B21" s="3">
         <f>SUM(January:December!B21)</f>
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C21" s="3">
         <f>SUM(January:December!C21)</f>
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="D21" s="3">
         <f>SUM(January:December!D21)</f>
@@ -2439,15 +2439,15 @@
       </c>
       <c r="B22" s="2">
         <f>SUM(January:December!B22)</f>
-        <v>9974</v>
+        <v>12369</v>
       </c>
       <c r="C22" s="2">
         <f>SUM(January:December!C22)</f>
-        <v>1554</v>
+        <v>1841</v>
       </c>
       <c r="D22" s="2">
         <f>SUM(January:December!D22)</f>
-        <v>1966</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2456,15 +2456,15 @@
       </c>
       <c r="B23" s="3">
         <f>SUM(January:December!B23)</f>
-        <v>1703</v>
+        <v>2198</v>
       </c>
       <c r="C23" s="3">
         <f>SUM(January:December!C23)</f>
-        <v>859</v>
+        <v>1018</v>
       </c>
       <c r="D23" s="3">
         <f>SUM(January:December!D23)</f>
-        <v>352</v>
+        <v>404</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2473,15 +2473,15 @@
       </c>
       <c r="B24" s="2">
         <f>SUM(January:December!B24)</f>
-        <v>13093</v>
+        <v>16551</v>
       </c>
       <c r="C24" s="2">
         <f>SUM(January:December!C24)</f>
-        <v>2062</v>
+        <v>2633</v>
       </c>
       <c r="D24" s="2">
         <f>SUM(January:December!D24)</f>
-        <v>2369</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2490,15 +2490,15 @@
       </c>
       <c r="B25" s="3">
         <f>SUM(January:December!B25)</f>
-        <v>58820</v>
+        <v>72843</v>
       </c>
       <c r="C25" s="3">
         <f>SUM(January:December!C25)</f>
-        <v>5279</v>
+        <v>6224</v>
       </c>
       <c r="D25" s="3">
         <f>SUM(January:December!D25)</f>
-        <v>6403</v>
+        <v>7650</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2507,15 +2507,15 @@
       </c>
       <c r="B26" s="2">
         <f>SUM(January:December!B26)</f>
-        <v>2906</v>
+        <v>3628</v>
       </c>
       <c r="C26" s="2">
         <f>SUM(January:December!C26)</f>
-        <v>1156</v>
+        <v>1463</v>
       </c>
       <c r="D26" s="2">
         <f>SUM(January:December!D26)</f>
-        <v>590</v>
+        <v>714</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2541,15 +2541,15 @@
       </c>
       <c r="B28" s="2">
         <f>SUM(January:December!B28)</f>
-        <v>3058</v>
+        <v>3934</v>
       </c>
       <c r="C28" s="2">
         <f>SUM(January:December!C28)</f>
-        <v>606</v>
+        <v>773</v>
       </c>
       <c r="D28" s="2">
         <f>SUM(January:December!D28)</f>
-        <v>714</v>
+        <v>894</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2558,15 +2558,15 @@
       </c>
       <c r="B29" s="3">
         <f>SUM(January:December!B29)</f>
-        <v>2228</v>
+        <v>2860</v>
       </c>
       <c r="C29" s="3">
         <f>SUM(January:December!C29)</f>
-        <v>434</v>
+        <v>520</v>
       </c>
       <c r="D29" s="3">
         <f>SUM(January:December!D29)</f>
-        <v>575</v>
+        <v>722</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2575,15 +2575,15 @@
       </c>
       <c r="B30" s="2">
         <f>SUM(January:December!B30)</f>
-        <v>13447</v>
+        <v>17429</v>
       </c>
       <c r="C30" s="2">
         <f>SUM(January:December!C30)</f>
-        <v>1736</v>
+        <v>2108</v>
       </c>
       <c r="D30" s="2">
         <f>SUM(January:December!D30)</f>
-        <v>2564</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2592,15 +2592,15 @@
       </c>
       <c r="B31" s="3">
         <f>SUM(January:December!B31)</f>
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="C31" s="3">
         <f>SUM(January:December!C31)</f>
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="D31" s="3">
         <f>SUM(January:December!D31)</f>
-        <v>115</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2609,15 +2609,15 @@
       </c>
       <c r="B32" s="2">
         <f>SUM(January:December!B32)</f>
-        <v>2257</v>
+        <v>2617</v>
       </c>
       <c r="C32" s="2">
         <f>SUM(January:December!C32)</f>
-        <v>994</v>
+        <v>1220</v>
       </c>
       <c r="D32" s="2">
         <f>SUM(January:December!D32)</f>
-        <v>446</v>
+        <v>505</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -2626,15 +2626,15 @@
       </c>
       <c r="B33" s="3">
         <f>SUM(January:December!B33)</f>
-        <v>8166</v>
+        <v>10338</v>
       </c>
       <c r="C33" s="3">
         <f>SUM(January:December!C33)</f>
-        <v>1956</v>
+        <v>2354</v>
       </c>
       <c r="D33" s="3">
         <f>SUM(January:December!D33)</f>
-        <v>1689</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2643,15 +2643,15 @@
       </c>
       <c r="B34" s="2">
         <f>SUM(January:December!B34)</f>
-        <v>5641</v>
+        <v>7529</v>
       </c>
       <c r="C34" s="2">
         <f>SUM(January:December!C34)</f>
-        <v>1180</v>
+        <v>1432</v>
       </c>
       <c r="D34" s="2">
         <f>SUM(January:December!D34)</f>
-        <v>1250</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2660,15 +2660,15 @@
       </c>
       <c r="B35" s="3">
         <f>SUM(January:December!B35)</f>
-        <v>3145</v>
+        <v>3855</v>
       </c>
       <c r="C35" s="3">
         <f>SUM(January:December!C35)</f>
-        <v>416</v>
+        <v>508</v>
       </c>
       <c r="D35" s="3">
         <f>SUM(January:December!D35)</f>
-        <v>581</v>
+        <v>690</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2677,15 +2677,15 @@
       </c>
       <c r="B36" s="2">
         <f>SUM(January:December!B36)</f>
-        <v>28428</v>
+        <v>38241</v>
       </c>
       <c r="C36" s="2">
         <f>SUM(January:December!C36)</f>
-        <v>5488</v>
+        <v>6799</v>
       </c>
       <c r="D36" s="2">
         <f>SUM(January:December!D36)</f>
-        <v>4229</v>
+        <v>5082</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2694,15 +2694,15 @@
       </c>
       <c r="B37" s="3">
         <f>SUM(January:December!B37)</f>
-        <v>4552</v>
+        <v>5763</v>
       </c>
       <c r="C37" s="3">
         <f>SUM(January:December!C37)</f>
-        <v>2123</v>
+        <v>2575</v>
       </c>
       <c r="D37" s="3">
         <f>SUM(January:December!D37)</f>
-        <v>666</v>
+        <v>790</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2711,15 +2711,15 @@
       </c>
       <c r="B38" s="2">
         <f>SUM(January:December!B38)</f>
-        <v>17901</v>
+        <v>22995</v>
       </c>
       <c r="C38" s="2">
         <f>SUM(January:December!C38)</f>
-        <v>1390</v>
+        <v>1651</v>
       </c>
       <c r="D38" s="2">
         <f>SUM(January:December!D38)</f>
-        <v>2046</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2728,15 +2728,15 @@
       </c>
       <c r="B39" s="3">
         <f>SUM(January:December!B39)</f>
-        <v>1271</v>
+        <v>1923</v>
       </c>
       <c r="C39" s="3">
         <f>SUM(January:December!C39)</f>
-        <v>742</v>
+        <v>876</v>
       </c>
       <c r="D39" s="3">
         <f>SUM(January:December!D39)</f>
-        <v>159</v>
+        <v>236</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="C40" s="6">
         <f>SUM(January:December!C40)</f>
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D40" s="6">
         <f>SUM(January:December!D40)</f>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="B42" s="6">
         <f>SUM(January:December!B42)</f>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C42" s="6">
         <f>SUM(January:December!C42)</f>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="D42" s="6">
         <f>SUM(January:December!D42)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2813,15 +2813,15 @@
       </c>
       <c r="B44" s="2">
         <f>SUM(January:December!B44)</f>
-        <v>1221</v>
+        <v>1435</v>
       </c>
       <c r="C44" s="2">
         <f>SUM(January:December!C44)</f>
-        <v>367</v>
+        <v>428</v>
       </c>
       <c r="D44" s="2">
         <f>SUM(January:December!D44)</f>
-        <v>749</v>
+        <v>820</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2830,15 +2830,15 @@
       </c>
       <c r="B45" s="3">
         <f>SUM(January:December!B45)</f>
-        <v>1999</v>
+        <v>2577</v>
       </c>
       <c r="C45" s="3">
         <f>SUM(January:December!C45)</f>
-        <v>780</v>
+        <v>917</v>
       </c>
       <c r="D45" s="3">
         <f>SUM(January:December!D45)</f>
-        <v>196</v>
+        <v>243</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2847,15 +2847,15 @@
       </c>
       <c r="B46" s="2">
         <f>SUM(January:December!B46)</f>
-        <v>9034</v>
+        <v>11061</v>
       </c>
       <c r="C46" s="2">
         <f>SUM(January:December!C46)</f>
-        <v>2222</v>
+        <v>2697</v>
       </c>
       <c r="D46" s="2">
         <f>SUM(January:December!D46)</f>
-        <v>1931</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2864,15 +2864,15 @@
       </c>
       <c r="B47" s="3">
         <f>SUM(January:December!B47)</f>
-        <v>18083</v>
+        <v>24245</v>
       </c>
       <c r="C47" s="3">
         <f>SUM(January:December!C47)</f>
-        <v>2593</v>
+        <v>2957</v>
       </c>
       <c r="D47" s="3">
         <f>SUM(January:December!D47)</f>
-        <v>2906</v>
+        <v>3435</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2881,15 +2881,15 @@
       </c>
       <c r="B48" s="2">
         <f>SUM(January:December!B48)</f>
-        <v>7614</v>
+        <v>10414</v>
       </c>
       <c r="C48" s="2">
         <f>SUM(January:December!C48)</f>
-        <v>2153</v>
+        <v>2558</v>
       </c>
       <c r="D48" s="2">
         <f>SUM(January:December!D48)</f>
-        <v>852</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -2898,15 +2898,15 @@
       </c>
       <c r="B49" s="3">
         <f>SUM(January:December!B49)</f>
-        <v>4551</v>
+        <v>5463</v>
       </c>
       <c r="C49" s="3">
         <f>SUM(January:December!C49)</f>
-        <v>992</v>
+        <v>1155</v>
       </c>
       <c r="D49" s="3">
         <f>SUM(January:December!D49)</f>
-        <v>1219</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2915,15 +2915,15 @@
       </c>
       <c r="B50" s="2">
         <f>SUM(January:December!B50)</f>
-        <v>20178</v>
+        <v>25588</v>
       </c>
       <c r="C50" s="2">
         <f>SUM(January:December!C50)</f>
-        <v>2035</v>
+        <v>2453</v>
       </c>
       <c r="D50" s="2">
         <f>SUM(January:December!D50)</f>
-        <v>3265</v>
+        <v>4027</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -2932,15 +2932,15 @@
       </c>
       <c r="B51" s="3">
         <f>SUM(January:December!B51)</f>
-        <v>2354</v>
+        <v>3074</v>
       </c>
       <c r="C51" s="3">
         <f>SUM(January:December!C51)</f>
-        <v>618</v>
+        <v>730</v>
       </c>
       <c r="D51" s="3">
         <f>SUM(January:December!D51)</f>
-        <v>564</v>
+        <v>662</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -2949,15 +2949,15 @@
       </c>
       <c r="B52" s="2">
         <f>SUM(January:December!B52)</f>
-        <v>6693</v>
+        <v>8094</v>
       </c>
       <c r="C52" s="2">
         <f>SUM(January:December!C52)</f>
-        <v>1331</v>
+        <v>1625</v>
       </c>
       <c r="D52" s="2">
         <f>SUM(January:December!D52)</f>
-        <v>1829</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -2966,15 +2966,15 @@
       </c>
       <c r="B53" s="3">
         <f>SUM(January:December!B53)</f>
-        <v>1001</v>
+        <v>1189</v>
       </c>
       <c r="C53" s="3">
         <f>SUM(January:December!C53)</f>
-        <v>867</v>
+        <v>1038</v>
       </c>
       <c r="D53" s="3">
         <f>SUM(January:December!D53)</f>
-        <v>434</v>
+        <v>473</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -2983,15 +2983,15 @@
       </c>
       <c r="B54" s="2">
         <f>SUM(January:December!B54)</f>
-        <v>1271</v>
+        <v>1427</v>
       </c>
       <c r="C54" s="2">
         <f>SUM(January:December!C54)</f>
-        <v>952</v>
+        <v>1131</v>
       </c>
       <c r="D54" s="2">
         <f>SUM(January:December!D54)</f>
-        <v>98</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -3000,15 +3000,15 @@
       </c>
       <c r="B55" s="3">
         <f>SUM(January:December!B55)</f>
-        <v>3668</v>
+        <v>4619</v>
       </c>
       <c r="C55" s="3">
         <f>SUM(January:December!C55)</f>
-        <v>765</v>
+        <v>914</v>
       </c>
       <c r="D55" s="3">
         <f>SUM(January:December!D55)</f>
-        <v>1679</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -3017,15 +3017,15 @@
       </c>
       <c r="B56" s="4">
         <f>SUM(January:December!B56)</f>
-        <v>6207</v>
+        <v>7575</v>
       </c>
       <c r="C56" s="4">
         <f>SUM(January:December!C56)</f>
-        <v>2645</v>
+        <v>3197</v>
       </c>
       <c r="D56" s="4">
         <f>SUM(January:December!D56)</f>
-        <v>958</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -3034,15 +3034,15 @@
       </c>
       <c r="B57" s="7">
         <f>SUM(January:December!B57)</f>
-        <v>12288</v>
+        <v>12289</v>
       </c>
       <c r="C57" s="7">
         <f>SUM(January:December!C57)</f>
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D57" s="7">
         <f>SUM(January:December!D57)</f>
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -3051,15 +3051,15 @@
       </c>
       <c r="B58" s="8">
         <f>SUM(January:December!B58)</f>
-        <v>421933</v>
+        <v>530642</v>
       </c>
       <c r="C58" s="8">
         <f>SUM(January:December!C58)</f>
-        <v>67459</v>
+        <v>80782</v>
       </c>
       <c r="D58" s="8">
         <f>SUM(January:December!D58)</f>
-        <v>65135</v>
+        <v>78003</v>
       </c>
     </row>
   </sheetData>
@@ -9669,11 +9669,15 @@
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="19"/>
+      <c r="B1" s="19">
+        <v>46174</v>
+      </c>
       <c r="C1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="21"/>
+      <c r="D1" s="21">
+        <v>46203</v>
+      </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
@@ -9693,449 +9697,785 @@
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="B3" s="3">
+        <v>6881</v>
+      </c>
+      <c r="C3" s="3">
+        <v>815</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1046</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="B4" s="2">
+        <v>4172</v>
+      </c>
+      <c r="C4" s="2">
+        <v>244</v>
+      </c>
+      <c r="D4" s="2">
+        <v>577</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="B5" s="3">
+        <v>10577</v>
+      </c>
+      <c r="C5" s="3">
+        <v>747</v>
+      </c>
+      <c r="D5" s="3">
+        <v>858</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="B6" s="2">
+        <v>424</v>
+      </c>
+      <c r="C6" s="2">
+        <v>78</v>
+      </c>
+      <c r="D6" s="2">
+        <v>38</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="B7" s="3">
+        <v>7611</v>
+      </c>
+      <c r="C7" s="3">
+        <v>722</v>
+      </c>
+      <c r="D7" s="3">
+        <v>734</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="B8" s="2">
+        <v>633</v>
+      </c>
+      <c r="C8" s="2">
+        <v>141</v>
+      </c>
+      <c r="D8" s="2">
+        <v>112</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="B9" s="3">
+        <v>635</v>
+      </c>
+      <c r="C9" s="3">
+        <v>137</v>
+      </c>
+      <c r="D9" s="3">
+        <v>73</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="B10" s="2">
+        <v>416</v>
+      </c>
+      <c r="C10" s="2">
+        <v>36</v>
+      </c>
+      <c r="D10" s="2">
+        <v>36</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
+      <c r="B11" s="3">
+        <v>85</v>
+      </c>
+      <c r="C11" s="3">
+        <v>11</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
+      <c r="B13" s="4">
+        <v>37</v>
+      </c>
+      <c r="C13" s="4">
+        <v>43</v>
+      </c>
+      <c r="D13" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="B14" s="5">
+        <v>190</v>
+      </c>
+      <c r="C14" s="5">
+        <v>81</v>
+      </c>
+      <c r="D14" s="5">
+        <v>33</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
+      <c r="B15" s="4">
+        <v>705</v>
+      </c>
+      <c r="C15" s="4">
+        <v>266</v>
+      </c>
+      <c r="D15" s="4">
+        <v>102</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
+      <c r="B16" s="5">
+        <v>436</v>
+      </c>
+      <c r="C16" s="5">
+        <v>208</v>
+      </c>
+      <c r="D16" s="5">
+        <v>74</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
+      <c r="B17" s="3">
+        <v>363</v>
+      </c>
+      <c r="C17" s="3">
+        <v>114</v>
+      </c>
+      <c r="D17" s="3">
+        <v>39</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="B18" s="2">
+        <v>2775</v>
+      </c>
+      <c r="C18" s="2">
+        <v>338</v>
+      </c>
+      <c r="D18" s="2">
+        <v>533</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
+      <c r="B19" s="3">
+        <v>186</v>
+      </c>
+      <c r="C19" s="3">
+        <v>61</v>
+      </c>
+      <c r="D19" s="3">
+        <v>37</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
+      <c r="B20" s="2">
+        <v>2549</v>
+      </c>
+      <c r="C20" s="2">
+        <v>262</v>
+      </c>
+      <c r="D20" s="2">
+        <v>269</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
+      <c r="B21" s="3">
+        <v>4</v>
+      </c>
+      <c r="C21" s="3">
+        <v>30</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
+      <c r="B22" s="2">
+        <v>2395</v>
+      </c>
+      <c r="C22" s="2">
+        <v>287</v>
+      </c>
+      <c r="D22" s="2">
+        <v>441</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
+      <c r="B23" s="3">
+        <v>495</v>
+      </c>
+      <c r="C23" s="3">
+        <v>159</v>
+      </c>
+      <c r="D23" s="3">
+        <v>52</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
+      <c r="B24" s="2">
+        <v>3458</v>
+      </c>
+      <c r="C24" s="2">
+        <v>571</v>
+      </c>
+      <c r="D24" s="2">
+        <v>461</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
+      <c r="B25" s="3">
+        <v>14023</v>
+      </c>
+      <c r="C25" s="3">
+        <v>945</v>
+      </c>
+      <c r="D25" s="3">
+        <v>1247</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
+      <c r="B26" s="2">
+        <v>722</v>
+      </c>
+      <c r="C26" s="2">
+        <v>307</v>
+      </c>
+      <c r="D26" s="2">
+        <v>124</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
+      <c r="B27" s="3">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
+      <c r="B28" s="2">
+        <v>876</v>
+      </c>
+      <c r="C28" s="2">
+        <v>167</v>
+      </c>
+      <c r="D28" s="2">
+        <v>180</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
+      <c r="B29" s="3">
+        <v>632</v>
+      </c>
+      <c r="C29" s="3">
+        <v>86</v>
+      </c>
+      <c r="D29" s="3">
+        <v>147</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
+      <c r="B30" s="2">
+        <v>3982</v>
+      </c>
+      <c r="C30" s="2">
+        <v>372</v>
+      </c>
+      <c r="D30" s="2">
+        <v>581</v>
+      </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
+      <c r="B31" s="3">
+        <v>27</v>
+      </c>
+      <c r="C31" s="3">
+        <v>40</v>
+      </c>
+      <c r="D31" s="3">
+        <v>20</v>
+      </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
+      <c r="B32" s="2">
+        <v>360</v>
+      </c>
+      <c r="C32" s="2">
+        <v>226</v>
+      </c>
+      <c r="D32" s="2">
+        <v>59</v>
+      </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
+      <c r="B33" s="3">
+        <v>2172</v>
+      </c>
+      <c r="C33" s="3">
+        <v>398</v>
+      </c>
+      <c r="D33" s="3">
+        <v>305</v>
+      </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
+      <c r="B34" s="2">
+        <v>1888</v>
+      </c>
+      <c r="C34" s="2">
+        <v>252</v>
+      </c>
+      <c r="D34" s="2">
+        <v>253</v>
+      </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
+      <c r="B35" s="3">
+        <v>710</v>
+      </c>
+      <c r="C35" s="3">
+        <v>92</v>
+      </c>
+      <c r="D35" s="3">
+        <v>109</v>
+      </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
+      <c r="B36" s="2">
+        <v>9813</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1311</v>
+      </c>
+      <c r="D36" s="2">
+        <v>853</v>
+      </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
+      <c r="B37" s="3">
+        <v>1211</v>
+      </c>
+      <c r="C37" s="3">
+        <v>452</v>
+      </c>
+      <c r="D37" s="3">
+        <v>124</v>
+      </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
+      <c r="B38" s="2">
+        <v>5094</v>
+      </c>
+      <c r="C38" s="2">
+        <v>261</v>
+      </c>
+      <c r="D38" s="2">
+        <v>427</v>
+      </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
+      <c r="B39" s="3">
+        <v>652</v>
+      </c>
+      <c r="C39" s="3">
+        <v>134</v>
+      </c>
+      <c r="D39" s="3">
+        <v>77</v>
+      </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
+      <c r="B40" s="6">
+        <v>0</v>
+      </c>
+      <c r="C40" s="6">
+        <v>1</v>
+      </c>
+      <c r="D40" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
+      <c r="B41" s="7">
+        <v>0</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0</v>
+      </c>
+      <c r="D41" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
+      <c r="B42" s="6">
+        <v>1</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
+      <c r="B43" s="7">
+        <v>0</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0</v>
+      </c>
+      <c r="D43" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
+      <c r="B44" s="2">
+        <v>214</v>
+      </c>
+      <c r="C44" s="2">
+        <v>61</v>
+      </c>
+      <c r="D44" s="2">
+        <v>71</v>
+      </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
+      <c r="B45" s="3">
+        <v>578</v>
+      </c>
+      <c r="C45" s="3">
+        <v>137</v>
+      </c>
+      <c r="D45" s="3">
+        <v>47</v>
+      </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
+      <c r="B46" s="2">
+        <v>2027</v>
+      </c>
+      <c r="C46" s="2">
+        <v>475</v>
+      </c>
+      <c r="D46" s="2">
+        <v>370</v>
+      </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
+      <c r="B47" s="3">
+        <v>6162</v>
+      </c>
+      <c r="C47" s="3">
+        <v>364</v>
+      </c>
+      <c r="D47" s="3">
+        <v>529</v>
+      </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
+      <c r="B48" s="2">
+        <v>2800</v>
+      </c>
+      <c r="C48" s="2">
+        <v>405</v>
+      </c>
+      <c r="D48" s="2">
+        <v>211</v>
+      </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
+      <c r="B49" s="3">
+        <v>912</v>
+      </c>
+      <c r="C49" s="3">
+        <v>163</v>
+      </c>
+      <c r="D49" s="3">
+        <v>201</v>
+      </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
+      <c r="B50" s="2">
+        <v>5410</v>
+      </c>
+      <c r="C50" s="2">
+        <v>418</v>
+      </c>
+      <c r="D50" s="2">
+        <v>762</v>
+      </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
+      <c r="B51" s="3">
+        <v>720</v>
+      </c>
+      <c r="C51" s="3">
+        <v>112</v>
+      </c>
+      <c r="D51" s="3">
+        <v>98</v>
+      </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
+      <c r="B52" s="2">
+        <v>1401</v>
+      </c>
+      <c r="C52" s="2">
+        <v>294</v>
+      </c>
+      <c r="D52" s="2">
+        <v>244</v>
+      </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
+      <c r="B53" s="3">
+        <v>188</v>
+      </c>
+      <c r="C53" s="3">
+        <v>171</v>
+      </c>
+      <c r="D53" s="3">
+        <v>39</v>
+      </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
+      <c r="B54" s="2">
+        <v>156</v>
+      </c>
+      <c r="C54" s="2">
+        <v>179</v>
+      </c>
+      <c r="D54" s="2">
+        <v>19</v>
+      </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
+      <c r="B55" s="3">
+        <v>951</v>
+      </c>
+      <c r="C55" s="3">
+        <v>149</v>
+      </c>
+      <c r="D55" s="3">
+        <v>251</v>
+      </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
+      <c r="B56" s="4">
+        <v>1368</v>
+      </c>
+      <c r="C56" s="4">
+        <v>552</v>
+      </c>
+      <c r="D56" s="4">
+        <v>174</v>
+      </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
+      <c r="B57" s="7">
+        <v>1</v>
+      </c>
+      <c r="C57" s="7">
+        <v>1</v>
+      </c>
+      <c r="D57" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
+      <c r="B58" s="8">
+        <v>108709</v>
+      </c>
+      <c r="C58" s="8">
+        <v>13323</v>
+      </c>
+      <c r="D58" s="8">
+        <v>12868</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:D2" xr:uid="{00000000-0009-0000-0000-000006000000}"/>

--- a/statistics_files/nekls_executive_board/2026/2026_next_statistics.xlsx
+++ b/statistics_files/nekls_executive_board/2026/2026_next_statistics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\nekls_executive_board\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6748CD7-CC2E-4F32-AC28-381A70CDE13C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{977CB467-9A10-4206-A10D-138C68963F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="D1" s="21">
         <f>MAX(January:December!D1)</f>
-        <v>46203</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2116,15 +2116,15 @@
       </c>
       <c r="B3" s="3">
         <f>SUM(January:December!B3)</f>
-        <v>34705</v>
+        <v>41302</v>
       </c>
       <c r="C3" s="3">
         <f>SUM(January:December!C3)</f>
-        <v>5068</v>
+        <v>5953</v>
       </c>
       <c r="D3" s="3">
         <f>SUM(January:December!D3)</f>
-        <v>6123</v>
+        <v>7303</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2133,15 +2133,15 @@
       </c>
       <c r="B4" s="2">
         <f>SUM(January:December!B4)</f>
-        <v>20342</v>
+        <v>24556</v>
       </c>
       <c r="C4" s="2">
         <f>SUM(January:December!C4)</f>
-        <v>1788</v>
+        <v>2029</v>
       </c>
       <c r="D4" s="2">
         <f>SUM(January:December!D4)</f>
-        <v>2872</v>
+        <v>3474</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2150,15 +2150,15 @@
       </c>
       <c r="B5" s="3">
         <f>SUM(January:December!B5)</f>
-        <v>53605</v>
+        <v>63569</v>
       </c>
       <c r="C5" s="3">
         <f>SUM(January:December!C5)</f>
-        <v>4755</v>
+        <v>5624</v>
       </c>
       <c r="D5" s="3">
         <f>SUM(January:December!D5)</f>
-        <v>4722</v>
+        <v>5626</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2167,15 +2167,15 @@
       </c>
       <c r="B6" s="2">
         <f>SUM(January:December!B6)</f>
-        <v>999</v>
+        <v>1280</v>
       </c>
       <c r="C6" s="2">
         <f>SUM(January:December!C6)</f>
-        <v>476</v>
+        <v>551</v>
       </c>
       <c r="D6" s="2">
         <f>SUM(January:December!D6)</f>
-        <v>86</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2184,15 +2184,15 @@
       </c>
       <c r="B7" s="3">
         <f>SUM(January:December!B7)</f>
-        <v>38047</v>
+        <v>45754</v>
       </c>
       <c r="C7" s="3">
         <f>SUM(January:December!C7)</f>
-        <v>4885</v>
+        <v>5615</v>
       </c>
       <c r="D7" s="3">
         <f>SUM(January:December!D7)</f>
-        <v>4374</v>
+        <v>4992</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2201,15 +2201,15 @@
       </c>
       <c r="B8" s="2">
         <f>SUM(January:December!B8)</f>
-        <v>5255</v>
+        <v>5975</v>
       </c>
       <c r="C8" s="2">
         <f>SUM(January:December!C8)</f>
-        <v>823</v>
+        <v>965</v>
       </c>
       <c r="D8" s="2">
         <f>SUM(January:December!D8)</f>
-        <v>822</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2218,15 +2218,15 @@
       </c>
       <c r="B9" s="3">
         <f>SUM(January:December!B9)</f>
-        <v>3209</v>
+        <v>3780</v>
       </c>
       <c r="C9" s="3">
         <f>SUM(January:December!C9)</f>
-        <v>758</v>
+        <v>893</v>
       </c>
       <c r="D9" s="3">
         <f>SUM(January:December!D9)</f>
-        <v>554</v>
+        <v>704</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2235,15 +2235,15 @@
       </c>
       <c r="B10" s="2">
         <f>SUM(January:December!B10)</f>
-        <v>1641</v>
+        <v>2117</v>
       </c>
       <c r="C10" s="2">
         <f>SUM(January:December!C10)</f>
-        <v>230</v>
+        <v>285</v>
       </c>
       <c r="D10" s="2">
         <f>SUM(January:December!D10)</f>
-        <v>142</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2252,11 +2252,11 @@
       </c>
       <c r="B11" s="3">
         <f>SUM(January:December!B11)</f>
-        <v>317</v>
+        <v>382</v>
       </c>
       <c r="C11" s="3">
         <f>SUM(January:December!C11)</f>
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="D11" s="3">
         <f>SUM(January:December!D11)</f>
@@ -2286,15 +2286,15 @@
       </c>
       <c r="B13" s="4">
         <f>SUM(January:December!B13)</f>
-        <v>219</v>
+        <v>271</v>
       </c>
       <c r="C13" s="4">
         <f>SUM(January:December!C13)</f>
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="D13" s="4">
         <f>SUM(January:December!D13)</f>
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2303,15 +2303,15 @@
       </c>
       <c r="B14" s="5">
         <f>SUM(January:December!B14)</f>
-        <v>1072</v>
+        <v>1244</v>
       </c>
       <c r="C14" s="5">
         <f>SUM(January:December!C14)</f>
-        <v>577</v>
+        <v>691</v>
       </c>
       <c r="D14" s="5">
         <f>SUM(January:December!D14)</f>
-        <v>306</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2320,15 +2320,15 @@
       </c>
       <c r="B15" s="4">
         <f>SUM(January:December!B15)</f>
-        <v>4360</v>
+        <v>5100</v>
       </c>
       <c r="C15" s="4">
         <f>SUM(January:December!C15)</f>
-        <v>1362</v>
+        <v>1592</v>
       </c>
       <c r="D15" s="4">
         <f>SUM(January:December!D15)</f>
-        <v>742</v>
+        <v>854</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2337,15 +2337,15 @@
       </c>
       <c r="B16" s="5">
         <f>SUM(January:December!B16)</f>
-        <v>1924</v>
+        <v>2304</v>
       </c>
       <c r="C16" s="5">
         <f>SUM(January:December!C16)</f>
-        <v>1327</v>
+        <v>1556</v>
       </c>
       <c r="D16" s="5">
         <f>SUM(January:December!D16)</f>
-        <v>300</v>
+        <v>374</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2354,15 +2354,15 @@
       </c>
       <c r="B17" s="3">
         <f>SUM(January:December!B17)</f>
-        <v>1795</v>
+        <v>2126</v>
       </c>
       <c r="C17" s="3">
         <f>SUM(January:December!C17)</f>
-        <v>760</v>
+        <v>880</v>
       </c>
       <c r="D17" s="3">
         <f>SUM(January:December!D17)</f>
-        <v>276</v>
+        <v>318</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2371,15 +2371,15 @@
       </c>
       <c r="B18" s="2">
         <f>SUM(January:December!B18)</f>
-        <v>12123</v>
+        <v>14589</v>
       </c>
       <c r="C18" s="2">
         <f>SUM(January:December!C18)</f>
-        <v>1979</v>
+        <v>2259</v>
       </c>
       <c r="D18" s="2">
         <f>SUM(January:December!D18)</f>
-        <v>2789</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2388,15 +2388,15 @@
       </c>
       <c r="B19" s="3">
         <f>SUM(January:December!B19)</f>
-        <v>1115</v>
+        <v>1300</v>
       </c>
       <c r="C19" s="3">
         <f>SUM(January:December!C19)</f>
-        <v>393</v>
+        <v>472</v>
       </c>
       <c r="D19" s="3">
         <f>SUM(January:December!D19)</f>
-        <v>275</v>
+        <v>308</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2405,15 +2405,15 @@
       </c>
       <c r="B20" s="2">
         <f>SUM(January:December!B20)</f>
-        <v>12992</v>
+        <v>15671</v>
       </c>
       <c r="C20" s="2">
         <f>SUM(January:December!C20)</f>
-        <v>1450</v>
+        <v>1705</v>
       </c>
       <c r="D20" s="2">
         <f>SUM(January:December!D20)</f>
-        <v>2280</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2422,11 +2422,11 @@
       </c>
       <c r="B21" s="3">
         <f>SUM(January:December!B21)</f>
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="C21" s="3">
         <f>SUM(January:December!C21)</f>
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="D21" s="3">
         <f>SUM(January:December!D21)</f>
@@ -2439,15 +2439,15 @@
       </c>
       <c r="B22" s="2">
         <f>SUM(January:December!B22)</f>
-        <v>12369</v>
+        <v>14615</v>
       </c>
       <c r="C22" s="2">
         <f>SUM(January:December!C22)</f>
-        <v>1841</v>
+        <v>2137</v>
       </c>
       <c r="D22" s="2">
         <f>SUM(January:December!D22)</f>
-        <v>2407</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2456,15 +2456,15 @@
       </c>
       <c r="B23" s="3">
         <f>SUM(January:December!B23)</f>
-        <v>2198</v>
+        <v>2632</v>
       </c>
       <c r="C23" s="3">
         <f>SUM(January:December!C23)</f>
-        <v>1018</v>
+        <v>1182</v>
       </c>
       <c r="D23" s="3">
         <f>SUM(January:December!D23)</f>
-        <v>404</v>
+        <v>456</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2473,15 +2473,15 @@
       </c>
       <c r="B24" s="2">
         <f>SUM(January:December!B24)</f>
-        <v>16551</v>
+        <v>20296</v>
       </c>
       <c r="C24" s="2">
         <f>SUM(January:December!C24)</f>
-        <v>2633</v>
+        <v>3008</v>
       </c>
       <c r="D24" s="2">
         <f>SUM(January:December!D24)</f>
-        <v>2830</v>
+        <v>3390</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2490,15 +2490,15 @@
       </c>
       <c r="B25" s="3">
         <f>SUM(January:December!B25)</f>
-        <v>72843</v>
+        <v>86910</v>
       </c>
       <c r="C25" s="3">
         <f>SUM(January:December!C25)</f>
-        <v>6224</v>
+        <v>7179</v>
       </c>
       <c r="D25" s="3">
         <f>SUM(January:December!D25)</f>
-        <v>7650</v>
+        <v>8967</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2507,15 +2507,15 @@
       </c>
       <c r="B26" s="2">
         <f>SUM(January:December!B26)</f>
-        <v>3628</v>
+        <v>4207</v>
       </c>
       <c r="C26" s="2">
         <f>SUM(January:December!C26)</f>
-        <v>1463</v>
+        <v>1720</v>
       </c>
       <c r="D26" s="2">
         <f>SUM(January:December!D26)</f>
-        <v>714</v>
+        <v>850</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2541,15 +2541,15 @@
       </c>
       <c r="B28" s="2">
         <f>SUM(January:December!B28)</f>
-        <v>3934</v>
+        <v>4689</v>
       </c>
       <c r="C28" s="2">
         <f>SUM(January:December!C28)</f>
-        <v>773</v>
+        <v>918</v>
       </c>
       <c r="D28" s="2">
         <f>SUM(January:December!D28)</f>
-        <v>894</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2558,15 +2558,15 @@
       </c>
       <c r="B29" s="3">
         <f>SUM(January:December!B29)</f>
-        <v>2860</v>
+        <v>3388</v>
       </c>
       <c r="C29" s="3">
         <f>SUM(January:December!C29)</f>
-        <v>520</v>
+        <v>594</v>
       </c>
       <c r="D29" s="3">
         <f>SUM(January:December!D29)</f>
-        <v>722</v>
+        <v>847</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2575,15 +2575,15 @@
       </c>
       <c r="B30" s="2">
         <f>SUM(January:December!B30)</f>
-        <v>17429</v>
+        <v>20868</v>
       </c>
       <c r="C30" s="2">
         <f>SUM(January:December!C30)</f>
-        <v>2108</v>
+        <v>2456</v>
       </c>
       <c r="D30" s="2">
         <f>SUM(January:December!D30)</f>
-        <v>3145</v>
+        <v>3757</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2592,15 +2592,15 @@
       </c>
       <c r="B31" s="3">
         <f>SUM(January:December!B31)</f>
-        <v>244</v>
+        <v>348</v>
       </c>
       <c r="C31" s="3">
         <f>SUM(January:December!C31)</f>
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="D31" s="3">
         <f>SUM(January:December!D31)</f>
-        <v>135</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2609,15 +2609,15 @@
       </c>
       <c r="B32" s="2">
         <f>SUM(January:December!B32)</f>
-        <v>2617</v>
+        <v>2935</v>
       </c>
       <c r="C32" s="2">
         <f>SUM(January:December!C32)</f>
-        <v>1220</v>
+        <v>1503</v>
       </c>
       <c r="D32" s="2">
         <f>SUM(January:December!D32)</f>
-        <v>505</v>
+        <v>545</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -2626,15 +2626,15 @@
       </c>
       <c r="B33" s="3">
         <f>SUM(January:December!B33)</f>
-        <v>10338</v>
+        <v>12398</v>
       </c>
       <c r="C33" s="3">
         <f>SUM(January:December!C33)</f>
-        <v>2354</v>
+        <v>2712</v>
       </c>
       <c r="D33" s="3">
         <f>SUM(January:December!D33)</f>
-        <v>1994</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2643,15 +2643,15 @@
       </c>
       <c r="B34" s="2">
         <f>SUM(January:December!B34)</f>
-        <v>7529</v>
+        <v>9047</v>
       </c>
       <c r="C34" s="2">
         <f>SUM(January:December!C34)</f>
-        <v>1432</v>
+        <v>1700</v>
       </c>
       <c r="D34" s="2">
         <f>SUM(January:December!D34)</f>
-        <v>1503</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2660,15 +2660,15 @@
       </c>
       <c r="B35" s="3">
         <f>SUM(January:December!B35)</f>
-        <v>3855</v>
+        <v>4673</v>
       </c>
       <c r="C35" s="3">
         <f>SUM(January:December!C35)</f>
-        <v>508</v>
+        <v>607</v>
       </c>
       <c r="D35" s="3">
         <f>SUM(January:December!D35)</f>
-        <v>690</v>
+        <v>824</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2677,15 +2677,15 @@
       </c>
       <c r="B36" s="2">
         <f>SUM(January:December!B36)</f>
-        <v>38241</v>
+        <v>46568</v>
       </c>
       <c r="C36" s="2">
         <f>SUM(January:December!C36)</f>
-        <v>6799</v>
+        <v>8010</v>
       </c>
       <c r="D36" s="2">
         <f>SUM(January:December!D36)</f>
-        <v>5082</v>
+        <v>5959</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2694,15 +2694,15 @@
       </c>
       <c r="B37" s="3">
         <f>SUM(January:December!B37)</f>
-        <v>5763</v>
+        <v>6853</v>
       </c>
       <c r="C37" s="3">
         <f>SUM(January:December!C37)</f>
-        <v>2575</v>
+        <v>3012</v>
       </c>
       <c r="D37" s="3">
         <f>SUM(January:December!D37)</f>
-        <v>790</v>
+        <v>928</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2711,15 +2711,15 @@
       </c>
       <c r="B38" s="2">
         <f>SUM(January:December!B38)</f>
-        <v>22995</v>
+        <v>27866</v>
       </c>
       <c r="C38" s="2">
         <f>SUM(January:December!C38)</f>
-        <v>1651</v>
+        <v>1831</v>
       </c>
       <c r="D38" s="2">
         <f>SUM(January:December!D38)</f>
-        <v>2473</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2728,15 +2728,15 @@
       </c>
       <c r="B39" s="3">
         <f>SUM(January:December!B39)</f>
-        <v>1923</v>
+        <v>2357</v>
       </c>
       <c r="C39" s="3">
         <f>SUM(January:December!C39)</f>
-        <v>876</v>
+        <v>973</v>
       </c>
       <c r="D39" s="3">
         <f>SUM(January:December!D39)</f>
-        <v>236</v>
+        <v>259</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="C40" s="6">
         <f>SUM(January:December!C40)</f>
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D40" s="6">
         <f>SUM(January:December!D40)</f>
@@ -2813,15 +2813,15 @@
       </c>
       <c r="B44" s="2">
         <f>SUM(January:December!B44)</f>
-        <v>1435</v>
+        <v>1671</v>
       </c>
       <c r="C44" s="2">
         <f>SUM(January:December!C44)</f>
-        <v>428</v>
+        <v>492</v>
       </c>
       <c r="D44" s="2">
         <f>SUM(January:December!D44)</f>
-        <v>820</v>
+        <v>929</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2830,15 +2830,15 @@
       </c>
       <c r="B45" s="3">
         <f>SUM(January:December!B45)</f>
-        <v>2577</v>
+        <v>3059</v>
       </c>
       <c r="C45" s="3">
         <f>SUM(January:December!C45)</f>
-        <v>917</v>
+        <v>1067</v>
       </c>
       <c r="D45" s="3">
         <f>SUM(January:December!D45)</f>
-        <v>243</v>
+        <v>279</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2847,15 +2847,15 @@
       </c>
       <c r="B46" s="2">
         <f>SUM(January:December!B46)</f>
-        <v>11061</v>
+        <v>13277</v>
       </c>
       <c r="C46" s="2">
         <f>SUM(January:December!C46)</f>
-        <v>2697</v>
+        <v>3173</v>
       </c>
       <c r="D46" s="2">
         <f>SUM(January:December!D46)</f>
-        <v>2301</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2864,15 +2864,15 @@
       </c>
       <c r="B47" s="3">
         <f>SUM(January:December!B47)</f>
-        <v>24245</v>
+        <v>28992</v>
       </c>
       <c r="C47" s="3">
         <f>SUM(January:December!C47)</f>
-        <v>2957</v>
+        <v>3441</v>
       </c>
       <c r="D47" s="3">
         <f>SUM(January:December!D47)</f>
-        <v>3435</v>
+        <v>3988</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2881,15 +2881,15 @@
       </c>
       <c r="B48" s="2">
         <f>SUM(January:December!B48)</f>
-        <v>10414</v>
+        <v>12850</v>
       </c>
       <c r="C48" s="2">
         <f>SUM(January:December!C48)</f>
-        <v>2558</v>
+        <v>2974</v>
       </c>
       <c r="D48" s="2">
         <f>SUM(January:December!D48)</f>
-        <v>1063</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -2898,15 +2898,15 @@
       </c>
       <c r="B49" s="3">
         <f>SUM(January:December!B49)</f>
-        <v>5463</v>
+        <v>6493</v>
       </c>
       <c r="C49" s="3">
         <f>SUM(January:December!C49)</f>
-        <v>1155</v>
+        <v>1283</v>
       </c>
       <c r="D49" s="3">
         <f>SUM(January:December!D49)</f>
-        <v>1420</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2915,15 +2915,15 @@
       </c>
       <c r="B50" s="2">
         <f>SUM(January:December!B50)</f>
-        <v>25588</v>
+        <v>30247</v>
       </c>
       <c r="C50" s="2">
         <f>SUM(January:December!C50)</f>
-        <v>2453</v>
+        <v>2836</v>
       </c>
       <c r="D50" s="2">
         <f>SUM(January:December!D50)</f>
-        <v>4027</v>
+        <v>4722</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -2932,15 +2932,15 @@
       </c>
       <c r="B51" s="3">
         <f>SUM(January:December!B51)</f>
-        <v>3074</v>
+        <v>3524</v>
       </c>
       <c r="C51" s="3">
         <f>SUM(January:December!C51)</f>
-        <v>730</v>
+        <v>806</v>
       </c>
       <c r="D51" s="3">
         <f>SUM(January:December!D51)</f>
-        <v>662</v>
+        <v>739</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -2949,15 +2949,15 @@
       </c>
       <c r="B52" s="2">
         <f>SUM(January:December!B52)</f>
-        <v>8094</v>
+        <v>9228</v>
       </c>
       <c r="C52" s="2">
         <f>SUM(January:December!C52)</f>
-        <v>1625</v>
+        <v>1875</v>
       </c>
       <c r="D52" s="2">
         <f>SUM(January:December!D52)</f>
-        <v>2073</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -2966,15 +2966,15 @@
       </c>
       <c r="B53" s="3">
         <f>SUM(January:December!B53)</f>
-        <v>1189</v>
+        <v>1323</v>
       </c>
       <c r="C53" s="3">
         <f>SUM(January:December!C53)</f>
-        <v>1038</v>
+        <v>1179</v>
       </c>
       <c r="D53" s="3">
         <f>SUM(January:December!D53)</f>
-        <v>473</v>
+        <v>501</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -2983,15 +2983,15 @@
       </c>
       <c r="B54" s="2">
         <f>SUM(January:December!B54)</f>
-        <v>1427</v>
+        <v>1560</v>
       </c>
       <c r="C54" s="2">
         <f>SUM(January:December!C54)</f>
-        <v>1131</v>
+        <v>1316</v>
       </c>
       <c r="D54" s="2">
         <f>SUM(January:December!D54)</f>
-        <v>117</v>
+        <v>141</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -3000,15 +3000,15 @@
       </c>
       <c r="B55" s="3">
         <f>SUM(January:December!B55)</f>
-        <v>4619</v>
+        <v>5288</v>
       </c>
       <c r="C55" s="3">
         <f>SUM(January:December!C55)</f>
-        <v>914</v>
+        <v>1094</v>
       </c>
       <c r="D55" s="3">
         <f>SUM(January:December!D55)</f>
-        <v>1930</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -3017,15 +3017,15 @@
       </c>
       <c r="B56" s="4">
         <f>SUM(January:December!B56)</f>
-        <v>7575</v>
+        <v>8919</v>
       </c>
       <c r="C56" s="4">
         <f>SUM(January:December!C56)</f>
-        <v>3197</v>
+        <v>3748</v>
       </c>
       <c r="D56" s="4">
         <f>SUM(January:December!D56)</f>
-        <v>1132</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C57" s="7">
         <f>SUM(January:December!C57)</f>
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D57" s="7">
         <f>SUM(January:December!D57)</f>
@@ -3051,15 +3051,15 @@
       </c>
       <c r="B58" s="8">
         <f>SUM(January:December!B58)</f>
-        <v>530642</v>
+        <v>631913</v>
       </c>
       <c r="C58" s="8">
         <f>SUM(January:December!C58)</f>
-        <v>80782</v>
+        <v>93792</v>
       </c>
       <c r="D58" s="8">
         <f>SUM(January:December!D58)</f>
-        <v>78003</v>
+        <v>91372</v>
       </c>
     </row>
   </sheetData>
@@ -10496,11 +10496,15 @@
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="19"/>
+      <c r="B1" s="19">
+        <v>46204</v>
+      </c>
       <c r="C1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="21"/>
+      <c r="D1" s="21">
+        <v>46234</v>
+      </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
@@ -10520,449 +10524,785 @@
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="B3" s="3">
+        <v>6597</v>
+      </c>
+      <c r="C3" s="3">
+        <v>885</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1180</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="B4" s="2">
+        <v>4214</v>
+      </c>
+      <c r="C4" s="2">
+        <v>241</v>
+      </c>
+      <c r="D4" s="2">
+        <v>602</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="B5" s="3">
+        <v>9964</v>
+      </c>
+      <c r="C5" s="3">
+        <v>869</v>
+      </c>
+      <c r="D5" s="3">
+        <v>904</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="B6" s="2">
+        <v>281</v>
+      </c>
+      <c r="C6" s="2">
+        <v>75</v>
+      </c>
+      <c r="D6" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="B7" s="3">
+        <v>7707</v>
+      </c>
+      <c r="C7" s="3">
+        <v>730</v>
+      </c>
+      <c r="D7" s="3">
+        <v>618</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="B8" s="2">
+        <v>720</v>
+      </c>
+      <c r="C8" s="2">
+        <v>142</v>
+      </c>
+      <c r="D8" s="2">
+        <v>210</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="B9" s="3">
+        <v>571</v>
+      </c>
+      <c r="C9" s="3">
+        <v>135</v>
+      </c>
+      <c r="D9" s="3">
+        <v>150</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="B10" s="2">
+        <v>476</v>
+      </c>
+      <c r="C10" s="2">
+        <v>55</v>
+      </c>
+      <c r="D10" s="2">
+        <v>18</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
+      <c r="B11" s="3">
+        <v>65</v>
+      </c>
+      <c r="C11" s="3">
+        <v>22</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
+      <c r="B13" s="4">
+        <v>52</v>
+      </c>
+      <c r="C13" s="4">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4">
+        <v>8</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="B14" s="5">
+        <v>172</v>
+      </c>
+      <c r="C14" s="5">
+        <v>114</v>
+      </c>
+      <c r="D14" s="5">
+        <v>34</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
+      <c r="B15" s="4">
+        <v>740</v>
+      </c>
+      <c r="C15" s="4">
+        <v>230</v>
+      </c>
+      <c r="D15" s="4">
+        <v>112</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
+      <c r="B16" s="5">
+        <v>380</v>
+      </c>
+      <c r="C16" s="5">
+        <v>229</v>
+      </c>
+      <c r="D16" s="5">
+        <v>74</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
+      <c r="B17" s="3">
+        <v>331</v>
+      </c>
+      <c r="C17" s="3">
+        <v>120</v>
+      </c>
+      <c r="D17" s="3">
+        <v>42</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="B18" s="2">
+        <v>2466</v>
+      </c>
+      <c r="C18" s="2">
+        <v>280</v>
+      </c>
+      <c r="D18" s="2">
+        <v>511</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
+      <c r="B19" s="3">
+        <v>185</v>
+      </c>
+      <c r="C19" s="3">
+        <v>79</v>
+      </c>
+      <c r="D19" s="3">
+        <v>33</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
+      <c r="B20" s="2">
+        <v>2679</v>
+      </c>
+      <c r="C20" s="2">
+        <v>255</v>
+      </c>
+      <c r="D20" s="2">
+        <v>314</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
+      <c r="B21" s="3">
+        <v>12</v>
+      </c>
+      <c r="C21" s="3">
+        <v>31</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
+      <c r="B22" s="2">
+        <v>2246</v>
+      </c>
+      <c r="C22" s="2">
+        <v>296</v>
+      </c>
+      <c r="D22" s="2">
+        <v>417</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
+      <c r="B23" s="3">
+        <v>434</v>
+      </c>
+      <c r="C23" s="3">
+        <v>164</v>
+      </c>
+      <c r="D23" s="3">
+        <v>52</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
+      <c r="B24" s="2">
+        <v>3745</v>
+      </c>
+      <c r="C24" s="2">
+        <v>375</v>
+      </c>
+      <c r="D24" s="2">
+        <v>560</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
+      <c r="B25" s="3">
+        <v>14067</v>
+      </c>
+      <c r="C25" s="3">
+        <v>955</v>
+      </c>
+      <c r="D25" s="3">
+        <v>1317</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
+      <c r="B26" s="2">
+        <v>579</v>
+      </c>
+      <c r="C26" s="2">
+        <v>257</v>
+      </c>
+      <c r="D26" s="2">
+        <v>136</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
+      <c r="B27" s="3">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
+      <c r="B28" s="2">
+        <v>755</v>
+      </c>
+      <c r="C28" s="2">
+        <v>145</v>
+      </c>
+      <c r="D28" s="2">
+        <v>160</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
+      <c r="B29" s="3">
+        <v>528</v>
+      </c>
+      <c r="C29" s="3">
+        <v>74</v>
+      </c>
+      <c r="D29" s="3">
+        <v>125</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
+      <c r="B30" s="2">
+        <v>3439</v>
+      </c>
+      <c r="C30" s="2">
+        <v>348</v>
+      </c>
+      <c r="D30" s="2">
+        <v>612</v>
+      </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
+      <c r="B31" s="3">
+        <v>104</v>
+      </c>
+      <c r="C31" s="3">
+        <v>14</v>
+      </c>
+      <c r="D31" s="3">
+        <v>42</v>
+      </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
+      <c r="B32" s="2">
+        <v>318</v>
+      </c>
+      <c r="C32" s="2">
+        <v>283</v>
+      </c>
+      <c r="D32" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
+      <c r="B33" s="3">
+        <v>2060</v>
+      </c>
+      <c r="C33" s="3">
+        <v>358</v>
+      </c>
+      <c r="D33" s="3">
+        <v>400</v>
+      </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
+      <c r="B34" s="2">
+        <v>1518</v>
+      </c>
+      <c r="C34" s="2">
+        <v>268</v>
+      </c>
+      <c r="D34" s="2">
+        <v>235</v>
+      </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
+      <c r="B35" s="3">
+        <v>818</v>
+      </c>
+      <c r="C35" s="3">
+        <v>99</v>
+      </c>
+      <c r="D35" s="3">
+        <v>134</v>
+      </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
+      <c r="B36" s="2">
+        <v>8327</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1211</v>
+      </c>
+      <c r="D36" s="2">
+        <v>877</v>
+      </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
+      <c r="B37" s="3">
+        <v>1090</v>
+      </c>
+      <c r="C37" s="3">
+        <v>437</v>
+      </c>
+      <c r="D37" s="3">
+        <v>138</v>
+      </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
+      <c r="B38" s="2">
+        <v>4871</v>
+      </c>
+      <c r="C38" s="2">
+        <v>180</v>
+      </c>
+      <c r="D38" s="2">
+        <v>457</v>
+      </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
+      <c r="B39" s="3">
+        <v>434</v>
+      </c>
+      <c r="C39" s="3">
+        <v>97</v>
+      </c>
+      <c r="D39" s="3">
+        <v>23</v>
+      </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
+      <c r="B40" s="6">
+        <v>0</v>
+      </c>
+      <c r="C40" s="6">
+        <v>1</v>
+      </c>
+      <c r="D40" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
+      <c r="B41" s="7">
+        <v>0</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0</v>
+      </c>
+      <c r="D41" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
+      <c r="B42" s="6">
+        <v>0</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0</v>
+      </c>
+      <c r="D42" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
+      <c r="B43" s="7">
+        <v>0</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0</v>
+      </c>
+      <c r="D43" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
+      <c r="B44" s="2">
+        <v>236</v>
+      </c>
+      <c r="C44" s="2">
+        <v>64</v>
+      </c>
+      <c r="D44" s="2">
+        <v>109</v>
+      </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
+      <c r="B45" s="3">
+        <v>482</v>
+      </c>
+      <c r="C45" s="3">
+        <v>150</v>
+      </c>
+      <c r="D45" s="3">
+        <v>36</v>
+      </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
+      <c r="B46" s="2">
+        <v>2216</v>
+      </c>
+      <c r="C46" s="2">
+        <v>476</v>
+      </c>
+      <c r="D46" s="2">
+        <v>353</v>
+      </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
+      <c r="B47" s="3">
+        <v>4747</v>
+      </c>
+      <c r="C47" s="3">
+        <v>484</v>
+      </c>
+      <c r="D47" s="3">
+        <v>553</v>
+      </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
+      <c r="B48" s="2">
+        <v>2436</v>
+      </c>
+      <c r="C48" s="2">
+        <v>416</v>
+      </c>
+      <c r="D48" s="2">
+        <v>185</v>
+      </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
+      <c r="B49" s="3">
+        <v>1030</v>
+      </c>
+      <c r="C49" s="3">
+        <v>128</v>
+      </c>
+      <c r="D49" s="3">
+        <v>181</v>
+      </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
+      <c r="B50" s="2">
+        <v>4659</v>
+      </c>
+      <c r="C50" s="2">
+        <v>383</v>
+      </c>
+      <c r="D50" s="2">
+        <v>695</v>
+      </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
+      <c r="B51" s="3">
+        <v>450</v>
+      </c>
+      <c r="C51" s="3">
+        <v>76</v>
+      </c>
+      <c r="D51" s="3">
+        <v>77</v>
+      </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
+      <c r="B52" s="2">
+        <v>1134</v>
+      </c>
+      <c r="C52" s="2">
+        <v>250</v>
+      </c>
+      <c r="D52" s="2">
+        <v>250</v>
+      </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
+      <c r="B53" s="3">
+        <v>134</v>
+      </c>
+      <c r="C53" s="3">
+        <v>141</v>
+      </c>
+      <c r="D53" s="3">
+        <v>28</v>
+      </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
+      <c r="B54" s="2">
+        <v>133</v>
+      </c>
+      <c r="C54" s="2">
+        <v>185</v>
+      </c>
+      <c r="D54" s="2">
+        <v>24</v>
+      </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
+      <c r="B55" s="3">
+        <v>669</v>
+      </c>
+      <c r="C55" s="3">
+        <v>180</v>
+      </c>
+      <c r="D55" s="3">
+        <v>333</v>
+      </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
+      <c r="B56" s="4">
+        <v>1344</v>
+      </c>
+      <c r="C56" s="4">
+        <v>551</v>
+      </c>
+      <c r="D56" s="4">
+        <v>183</v>
+      </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
+      <c r="B57" s="7">
+        <v>0</v>
+      </c>
+      <c r="C57" s="7">
+        <v>1</v>
+      </c>
+      <c r="D57" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
+      <c r="B58" s="8">
+        <v>101271</v>
+      </c>
+      <c r="C58" s="8">
+        <v>13010</v>
+      </c>
+      <c r="D58" s="8">
+        <v>13369</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:D2" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
